--- a/p6/0580_BOQ_Cost_Mapping.xlsx
+++ b/p6/0580_BOQ_Cost_Mapping.xlsx
@@ -2525,7 +2525,7 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>PRJ-M1150</t>
+          <t>NRY-E1120</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -3645,7 +3645,7 @@
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>PRJ-M1150</t>
+          <t>HMK-E1120</t>
         </is>
       </c>
       <c r="B135" s="8" t="inlineStr">
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -4685,7 +4685,7 @@
     <row r="187">
       <c r="A187" s="8" t="inlineStr">
         <is>
-          <t>ERY-E1010</t>
+          <t>ERY-E1120</t>
         </is>
       </c>
       <c r="B187" s="8" t="inlineStr">
@@ -4695,11 +4695,11 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="D187" s="8" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -5925,7 +5925,7 @@
     <row r="249">
       <c r="A249" s="8" t="inlineStr">
         <is>
-          <t>HJD-E1010</t>
+          <t>HJD-E1120</t>
         </is>
       </c>
       <c r="B249" s="8" t="inlineStr">
@@ -5935,11 +5935,11 @@
       </c>
       <c r="C249" s="8" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="D249" s="8" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -7165,7 +7165,7 @@
     <row r="311">
       <c r="A311" s="8" t="inlineStr">
         <is>
-          <t>EDM-E1010</t>
+          <t>EDM-E1120</t>
         </is>
       </c>
       <c r="B311" s="8" t="inlineStr">
@@ -7175,11 +7175,11 @@
       </c>
       <c r="C311" s="8" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="D311" s="8" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -8405,7 +8405,7 @@
     <row r="373">
       <c r="A373" s="8" t="inlineStr">
         <is>
-          <t>NQS-E1010</t>
+          <t>NQS-E1120</t>
         </is>
       </c>
       <c r="B373" s="8" t="inlineStr">
@@ -8415,11 +8415,11 @@
       </c>
       <c r="C373" s="8" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="D373" s="8" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -9645,7 +9645,7 @@
     <row r="435">
       <c r="A435" s="8" t="inlineStr">
         <is>
-          <t>EHF-E1010</t>
+          <t>EHF-E1120</t>
         </is>
       </c>
       <c r="B435" s="8" t="inlineStr">
@@ -9655,11 +9655,11 @@
       </c>
       <c r="C435" s="8" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="D435" s="8" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="436">
@@ -10885,7 +10885,7 @@
     <row r="497">
       <c r="A497" s="8" t="inlineStr">
         <is>
-          <t>NMJ-E1010</t>
+          <t>NMJ-E1120</t>
         </is>
       </c>
       <c r="B497" s="8" t="inlineStr">
@@ -10895,11 +10895,11 @@
       </c>
       <c r="C497" s="8" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="D497" s="8" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="498">
@@ -12125,7 +12125,7 @@
     <row r="559">
       <c r="A559" s="8" t="inlineStr">
         <is>
-          <t>HKA-E1010</t>
+          <t>HKA-E1120</t>
         </is>
       </c>
       <c r="B559" s="8" t="inlineStr">
@@ -12135,11 +12135,11 @@
       </c>
       <c r="C559" s="8" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="D559" s="8" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="560">
@@ -13365,7 +13365,7 @@
     <row r="621">
       <c r="A621" s="8" t="inlineStr">
         <is>
-          <t>HMD-E1010</t>
+          <t>HMD-E1120</t>
         </is>
       </c>
       <c r="B621" s="8" t="inlineStr">
@@ -13375,11 +13375,11 @@
       </c>
       <c r="C621" s="8" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="D621" s="8" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="622">
@@ -14605,7 +14605,7 @@
     <row r="683">
       <c r="A683" s="8" t="inlineStr">
         <is>
-          <t>EAB-E1010</t>
+          <t>EAB-E1120</t>
         </is>
       </c>
       <c r="B683" s="8" t="inlineStr">
@@ -14615,11 +14615,11 @@
       </c>
       <c r="C683" s="8" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="D683" s="8" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="684">
@@ -15845,7 +15845,7 @@
     <row r="745">
       <c r="A745" s="8" t="inlineStr">
         <is>
-          <t>NHL-E1010</t>
+          <t>NHL-E1120</t>
         </is>
       </c>
       <c r="B745" s="8" t="inlineStr">
@@ -15855,11 +15855,11 @@
       </c>
       <c r="C745" s="8" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="D745" s="8" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="746">
@@ -17085,7 +17085,7 @@
     <row r="807">
       <c r="A807" s="8" t="inlineStr">
         <is>
-          <t>NJF-E1010</t>
+          <t>NJF-E1120</t>
         </is>
       </c>
       <c r="B807" s="8" t="inlineStr">
@@ -17095,11 +17095,11 @@
       </c>
       <c r="C807" s="8" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="D807" s="8" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="808">
@@ -18325,7 +18325,7 @@
     <row r="869">
       <c r="A869" s="8" t="inlineStr">
         <is>
-          <t>NQR-E1010</t>
+          <t>NQR-E1120</t>
         </is>
       </c>
       <c r="B869" s="8" t="inlineStr">
@@ -18335,11 +18335,11 @@
       </c>
       <c r="C869" s="8" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="D869" s="8" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="870">
@@ -32304,10 +32304,10 @@
         <v/>
       </c>
       <c r="T28" s="20" t="n">
-        <v>46447</v>
+        <v>46509</v>
       </c>
       <c r="U28" s="20" t="n">
-        <v>46467</v>
+        <v>46520</v>
       </c>
       <c r="V28" s="8" t="n">
         <v>10</v>
@@ -32397,10 +32397,10 @@
         <v/>
       </c>
       <c r="T29" s="20" t="n">
-        <v>46468</v>
+        <v>46530</v>
       </c>
       <c r="U29" s="20" t="n">
-        <v>46488</v>
+        <v>46548</v>
       </c>
       <c r="V29" s="8" t="n">
         <v>15</v>
@@ -33141,10 +33141,10 @@
         <v/>
       </c>
       <c r="T37" s="20" t="n">
-        <v>46489</v>
+        <v>46551</v>
       </c>
       <c r="U37" s="20" t="n">
-        <v>46574</v>
+        <v>46629</v>
       </c>
       <c r="V37" s="8" t="n">
         <v>57</v>
@@ -33234,10 +33234,10 @@
         <v/>
       </c>
       <c r="T38" s="20" t="n">
-        <v>46547</v>
+        <v>46602</v>
       </c>
       <c r="U38" s="20" t="n">
-        <v>46609</v>
+        <v>46665</v>
       </c>
       <c r="V38" s="8" t="n">
         <v>45</v>
@@ -35652,10 +35652,10 @@
         <v/>
       </c>
       <c r="T64" s="20" t="n">
-        <v>46447</v>
+        <v>46509</v>
       </c>
       <c r="U64" s="20" t="n">
-        <v>46467</v>
+        <v>46520</v>
       </c>
       <c r="V64" s="8" t="n">
         <v>10</v>
@@ -35745,10 +35745,10 @@
         <v/>
       </c>
       <c r="T65" s="20" t="n">
-        <v>46468</v>
+        <v>46530</v>
       </c>
       <c r="U65" s="20" t="n">
-        <v>46488</v>
+        <v>46548</v>
       </c>
       <c r="V65" s="8" t="n">
         <v>15</v>
@@ -36489,10 +36489,10 @@
         <v/>
       </c>
       <c r="T73" s="20" t="n">
-        <v>46489</v>
+        <v>46551</v>
       </c>
       <c r="U73" s="20" t="n">
-        <v>46561</v>
+        <v>46616</v>
       </c>
       <c r="V73" s="8" t="n">
         <v>48</v>
@@ -36582,10 +36582,10 @@
         <v/>
       </c>
       <c r="T74" s="20" t="n">
-        <v>46539</v>
+        <v>46594</v>
       </c>
       <c r="U74" s="20" t="n">
-        <v>46589</v>
+        <v>46644</v>
       </c>
       <c r="V74" s="8" t="n">
         <v>37</v>
@@ -38907,10 +38907,10 @@
         <v/>
       </c>
       <c r="T99" s="20" t="n">
-        <v>46447</v>
+        <v>46509</v>
       </c>
       <c r="U99" s="20" t="n">
-        <v>46460</v>
+        <v>46513</v>
       </c>
       <c r="V99" s="8" t="n">
         <v>5</v>
@@ -39000,10 +39000,10 @@
         <v/>
       </c>
       <c r="T100" s="20" t="n">
-        <v>46461</v>
+        <v>46516</v>
       </c>
       <c r="U100" s="20" t="n">
-        <v>46474</v>
+        <v>46534</v>
       </c>
       <c r="V100" s="8" t="n">
         <v>10</v>
@@ -39744,10 +39744,10 @@
         <v/>
       </c>
       <c r="T108" s="20" t="n">
-        <v>46475</v>
+        <v>46537</v>
       </c>
       <c r="U108" s="20" t="n">
-        <v>46558</v>
+        <v>46611</v>
       </c>
       <c r="V108" s="8" t="n">
         <v>55</v>
@@ -39837,10 +39837,10 @@
         <v/>
       </c>
       <c r="T109" s="20" t="n">
-        <v>46531</v>
+        <v>46586</v>
       </c>
       <c r="U109" s="20" t="n">
-        <v>46589</v>
+        <v>46644</v>
       </c>
       <c r="V109" s="8" t="n">
         <v>43</v>
@@ -42162,10 +42162,10 @@
         <v/>
       </c>
       <c r="T134" s="20" t="n">
-        <v>46512</v>
+        <v>46569</v>
       </c>
       <c r="U134" s="20" t="n">
-        <v>46518</v>
+        <v>46575</v>
       </c>
       <c r="V134" s="8" t="n">
         <v>5</v>
@@ -42255,10 +42255,10 @@
         <v/>
       </c>
       <c r="T135" s="20" t="n">
-        <v>46519</v>
+        <v>46576</v>
       </c>
       <c r="U135" s="20" t="n">
-        <v>46539</v>
+        <v>46589</v>
       </c>
       <c r="V135" s="8" t="n">
         <v>10</v>
@@ -42999,10 +42999,10 @@
         <v/>
       </c>
       <c r="T143" s="20" t="n">
-        <v>46540</v>
+        <v>46590</v>
       </c>
       <c r="U143" s="20" t="n">
-        <v>46601</v>
+        <v>46651</v>
       </c>
       <c r="V143" s="8" t="n">
         <v>44</v>
@@ -43092,10 +43092,10 @@
         <v/>
       </c>
       <c r="T144" s="20" t="n">
-        <v>46580</v>
+        <v>46630</v>
       </c>
       <c r="U144" s="20" t="n">
-        <v>46628</v>
+        <v>46679</v>
       </c>
       <c r="V144" s="8" t="n">
         <v>35</v>
@@ -45417,10 +45417,10 @@
         <v/>
       </c>
       <c r="T169" s="20" t="n">
-        <v>46615</v>
+        <v>46677</v>
       </c>
       <c r="U169" s="20" t="n">
-        <v>46621</v>
+        <v>46681</v>
       </c>
       <c r="V169" s="8" t="n">
         <v>5</v>
@@ -45510,10 +45510,10 @@
         <v/>
       </c>
       <c r="T170" s="20" t="n">
-        <v>46622</v>
+        <v>46684</v>
       </c>
       <c r="U170" s="20" t="n">
-        <v>46635</v>
+        <v>46695</v>
       </c>
       <c r="V170" s="8" t="n">
         <v>10</v>
@@ -46254,10 +46254,10 @@
         <v/>
       </c>
       <c r="T178" s="20" t="n">
-        <v>46636</v>
+        <v>46698</v>
       </c>
       <c r="U178" s="20" t="n">
-        <v>46713</v>
+        <v>46772</v>
       </c>
       <c r="V178" s="8" t="n">
         <v>55</v>
@@ -46347,10 +46347,10 @@
         <v/>
       </c>
       <c r="T179" s="20" t="n">
-        <v>46686</v>
+        <v>46747</v>
       </c>
       <c r="U179" s="20" t="n">
-        <v>46744</v>
+        <v>46812</v>
       </c>
       <c r="V179" s="8" t="n">
         <v>43</v>
@@ -48672,10 +48672,10 @@
         <v/>
       </c>
       <c r="T204" s="20" t="n">
-        <v>46670</v>
+        <v>46733</v>
       </c>
       <c r="U204" s="20" t="n">
-        <v>46674</v>
+        <v>46737</v>
       </c>
       <c r="V204" s="8" t="n">
         <v>5</v>
@@ -48765,10 +48765,10 @@
         <v/>
       </c>
       <c r="T205" s="20" t="n">
-        <v>46677</v>
+        <v>46740</v>
       </c>
       <c r="U205" s="20" t="n">
-        <v>46688</v>
+        <v>46751</v>
       </c>
       <c r="V205" s="8" t="n">
         <v>10</v>
@@ -49509,10 +49509,10 @@
         <v/>
       </c>
       <c r="T213" s="20" t="n">
-        <v>46691</v>
+        <v>46754</v>
       </c>
       <c r="U213" s="20" t="n">
-        <v>46769</v>
+        <v>46839</v>
       </c>
       <c r="V213" s="8" t="n">
         <v>57</v>
@@ -49602,10 +49602,10 @@
         <v/>
       </c>
       <c r="T214" s="20" t="n">
-        <v>46742</v>
+        <v>46812</v>
       </c>
       <c r="U214" s="20" t="n">
-        <v>46811</v>
+        <v>46881</v>
       </c>
       <c r="V214" s="8" t="n">
         <v>45</v>
@@ -51927,10 +51927,10 @@
         <v/>
       </c>
       <c r="T239" s="20" t="n">
-        <v>46670</v>
+        <v>46733</v>
       </c>
       <c r="U239" s="20" t="n">
-        <v>46674</v>
+        <v>46737</v>
       </c>
       <c r="V239" s="8" t="n">
         <v>5</v>
@@ -52020,10 +52020,10 @@
         <v/>
       </c>
       <c r="T240" s="20" t="n">
-        <v>46677</v>
+        <v>46740</v>
       </c>
       <c r="U240" s="20" t="n">
-        <v>46688</v>
+        <v>46751</v>
       </c>
       <c r="V240" s="8" t="n">
         <v>10</v>
@@ -52764,10 +52764,10 @@
         <v/>
       </c>
       <c r="T248" s="20" t="n">
-        <v>46691</v>
+        <v>46754</v>
       </c>
       <c r="U248" s="20" t="n">
-        <v>46763</v>
+        <v>46833</v>
       </c>
       <c r="V248" s="8" t="n">
         <v>53</v>
@@ -52857,10 +52857,10 @@
         <v/>
       </c>
       <c r="T249" s="20" t="n">
-        <v>46737</v>
+        <v>46800</v>
       </c>
       <c r="U249" s="20" t="n">
-        <v>46793</v>
+        <v>46863</v>
       </c>
       <c r="V249" s="8" t="n">
         <v>41</v>
@@ -55182,10 +55182,10 @@
         <v/>
       </c>
       <c r="T274" s="20" t="n">
-        <v>46716</v>
+        <v>46782</v>
       </c>
       <c r="U274" s="20" t="n">
-        <v>46722</v>
+        <v>46786</v>
       </c>
       <c r="V274" s="8" t="n">
         <v>5</v>
@@ -55275,10 +55275,10 @@
         <v/>
       </c>
       <c r="T275" s="20" t="n">
-        <v>46723</v>
+        <v>46789</v>
       </c>
       <c r="U275" s="20" t="n">
-        <v>46736</v>
+        <v>46800</v>
       </c>
       <c r="V275" s="8" t="n">
         <v>10</v>
@@ -56019,10 +56019,10 @@
         <v/>
       </c>
       <c r="T283" s="20" t="n">
-        <v>46737</v>
+        <v>46810</v>
       </c>
       <c r="U283" s="20" t="n">
-        <v>46824</v>
+        <v>46895</v>
       </c>
       <c r="V283" s="8" t="n">
         <v>57</v>
@@ -56112,10 +56112,10 @@
         <v/>
       </c>
       <c r="T284" s="20" t="n">
-        <v>46790</v>
+        <v>46861</v>
       </c>
       <c r="U284" s="20" t="n">
-        <v>46859</v>
+        <v>46930</v>
       </c>
       <c r="V284" s="8" t="n">
         <v>45</v>
@@ -58437,10 +58437,10 @@
         <v/>
       </c>
       <c r="T309" s="20" t="n">
-        <v>46842</v>
+        <v>46898</v>
       </c>
       <c r="U309" s="20" t="n">
-        <v>46848</v>
+        <v>46904</v>
       </c>
       <c r="V309" s="8" t="n">
         <v>5</v>
@@ -58530,10 +58530,10 @@
         <v/>
       </c>
       <c r="T310" s="20" t="n">
-        <v>46849</v>
+        <v>46905</v>
       </c>
       <c r="U310" s="20" t="n">
-        <v>46862</v>
+        <v>46918</v>
       </c>
       <c r="V310" s="8" t="n">
         <v>10</v>
@@ -59274,10 +59274,10 @@
         <v/>
       </c>
       <c r="T318" s="20" t="n">
-        <v>46863</v>
+        <v>46919</v>
       </c>
       <c r="U318" s="20" t="n">
-        <v>46904</v>
+        <v>46953</v>
       </c>
       <c r="V318" s="8" t="n">
         <v>25</v>
@@ -59367,10 +59367,10 @@
         <v/>
       </c>
       <c r="T319" s="20" t="n">
-        <v>46894</v>
+        <v>46943</v>
       </c>
       <c r="U319" s="20" t="n">
-        <v>46919</v>
+        <v>46968</v>
       </c>
       <c r="V319" s="8" t="n">
         <v>20</v>
@@ -61692,10 +61692,10 @@
         <v/>
       </c>
       <c r="T344" s="20" t="n">
-        <v>46842</v>
+        <v>46898</v>
       </c>
       <c r="U344" s="20" t="n">
-        <v>46848</v>
+        <v>46904</v>
       </c>
       <c r="V344" s="8" t="n">
         <v>5</v>
@@ -61785,10 +61785,10 @@
         <v/>
       </c>
       <c r="T345" s="20" t="n">
-        <v>46849</v>
+        <v>46905</v>
       </c>
       <c r="U345" s="20" t="n">
-        <v>46862</v>
+        <v>46918</v>
       </c>
       <c r="V345" s="8" t="n">
         <v>10</v>
@@ -62529,10 +62529,10 @@
         <v/>
       </c>
       <c r="T353" s="20" t="n">
-        <v>46863</v>
+        <v>46919</v>
       </c>
       <c r="U353" s="20" t="n">
-        <v>46912</v>
+        <v>46961</v>
       </c>
       <c r="V353" s="8" t="n">
         <v>31</v>
@@ -62622,10 +62622,10 @@
         <v/>
       </c>
       <c r="T354" s="20" t="n">
-        <v>46898</v>
+        <v>46947</v>
       </c>
       <c r="U354" s="20" t="n">
-        <v>46931</v>
+        <v>46980</v>
       </c>
       <c r="V354" s="8" t="n">
         <v>24</v>
@@ -64947,10 +64947,10 @@
         <v/>
       </c>
       <c r="T379" s="20" t="n">
-        <v>46897</v>
+        <v>46954</v>
       </c>
       <c r="U379" s="20" t="n">
-        <v>46903</v>
+        <v>46960</v>
       </c>
       <c r="V379" s="8" t="n">
         <v>5</v>
@@ -65040,10 +65040,10 @@
         <v/>
       </c>
       <c r="T380" s="20" t="n">
-        <v>46904</v>
+        <v>46961</v>
       </c>
       <c r="U380" s="20" t="n">
-        <v>46917</v>
+        <v>46974</v>
       </c>
       <c r="V380" s="8" t="n">
         <v>10</v>
@@ -65784,10 +65784,10 @@
         <v/>
       </c>
       <c r="T388" s="20" t="n">
-        <v>46918</v>
+        <v>46975</v>
       </c>
       <c r="U388" s="20" t="n">
-        <v>46967</v>
+        <v>47024</v>
       </c>
       <c r="V388" s="8" t="n">
         <v>36</v>
@@ -65877,10 +65877,10 @@
         <v/>
       </c>
       <c r="T389" s="20" t="n">
-        <v>46951</v>
+        <v>47008</v>
       </c>
       <c r="U389" s="20" t="n">
-        <v>46988</v>
+        <v>47045</v>
       </c>
       <c r="V389" s="8" t="n">
         <v>28</v>
@@ -68202,10 +68202,10 @@
         <v/>
       </c>
       <c r="T414" s="20" t="n">
-        <v>46922</v>
+        <v>46978</v>
       </c>
       <c r="U414" s="20" t="n">
-        <v>46926</v>
+        <v>46982</v>
       </c>
       <c r="V414" s="8" t="n">
         <v>5</v>
@@ -68295,10 +68295,10 @@
         <v/>
       </c>
       <c r="T415" s="20" t="n">
-        <v>46929</v>
+        <v>46985</v>
       </c>
       <c r="U415" s="20" t="n">
-        <v>46940</v>
+        <v>46996</v>
       </c>
       <c r="V415" s="8" t="n">
         <v>10</v>
@@ -69039,10 +69039,10 @@
         <v/>
       </c>
       <c r="T423" s="20" t="n">
-        <v>46943</v>
+        <v>46999</v>
       </c>
       <c r="U423" s="20" t="n">
-        <v>47021</v>
+        <v>47077</v>
       </c>
       <c r="V423" s="8" t="n">
         <v>57</v>
@@ -69132,10 +69132,10 @@
         <v/>
       </c>
       <c r="T424" s="20" t="n">
-        <v>46994</v>
+        <v>47050</v>
       </c>
       <c r="U424" s="20" t="n">
-        <v>47056</v>
+        <v>47112</v>
       </c>
       <c r="V424" s="8" t="n">
         <v>45</v>
@@ -71457,10 +71457,10 @@
         <v/>
       </c>
       <c r="T449" s="20" t="n">
-        <v>46993</v>
+        <v>47055</v>
       </c>
       <c r="U449" s="20" t="n">
-        <v>46999</v>
+        <v>47059</v>
       </c>
       <c r="V449" s="8" t="n">
         <v>5</v>
@@ -71550,10 +71550,10 @@
         <v/>
       </c>
       <c r="T450" s="20" t="n">
-        <v>47000</v>
+        <v>47062</v>
       </c>
       <c r="U450" s="20" t="n">
-        <v>47013</v>
+        <v>47073</v>
       </c>
       <c r="V450" s="8" t="n">
         <v>10</v>
@@ -72294,10 +72294,10 @@
         <v/>
       </c>
       <c r="T458" s="20" t="n">
-        <v>47014</v>
+        <v>47076</v>
       </c>
       <c r="U458" s="20" t="n">
-        <v>47092</v>
+        <v>47154</v>
       </c>
       <c r="V458" s="8" t="n">
         <v>57</v>
@@ -72387,10 +72387,10 @@
         <v/>
       </c>
       <c r="T459" s="20" t="n">
-        <v>47065</v>
+        <v>47127</v>
       </c>
       <c r="U459" s="20" t="n">
-        <v>47127</v>
+        <v>47197</v>
       </c>
       <c r="V459" s="8" t="n">
         <v>45</v>
@@ -74712,10 +74712,10 @@
         <v/>
       </c>
       <c r="T484" s="20" t="n">
-        <v>47041</v>
+        <v>47104</v>
       </c>
       <c r="U484" s="20" t="n">
-        <v>47045</v>
+        <v>47108</v>
       </c>
       <c r="V484" s="8" t="n">
         <v>5</v>
@@ -74805,10 +74805,10 @@
         <v/>
       </c>
       <c r="T485" s="20" t="n">
-        <v>47048</v>
+        <v>47111</v>
       </c>
       <c r="U485" s="20" t="n">
-        <v>47059</v>
+        <v>47122</v>
       </c>
       <c r="V485" s="8" t="n">
         <v>10</v>
@@ -75549,10 +75549,10 @@
         <v/>
       </c>
       <c r="T493" s="20" t="n">
-        <v>47062</v>
+        <v>47125</v>
       </c>
       <c r="U493" s="20" t="n">
-        <v>47140</v>
+        <v>47211</v>
       </c>
       <c r="V493" s="8" t="n">
         <v>57</v>
@@ -75642,10 +75642,10 @@
         <v/>
       </c>
       <c r="T494" s="20" t="n">
-        <v>47113</v>
+        <v>47184</v>
       </c>
       <c r="U494" s="20" t="n">
-        <v>47183</v>
+        <v>47253</v>
       </c>
       <c r="V494" s="8" t="n">
         <v>45</v>
@@ -77169,7 +77169,7 @@
         <v>46447</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1206616.967042765</v>
+        <v>1149268.960982159</v>
       </c>
       <c r="C8" s="9">
         <f>SUM(B$4:B8)</f>
@@ -77180,7 +77180,7 @@
         <v/>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.01491215547197903</v>
+        <v>0.009865185775009288</v>
       </c>
       <c r="F8" s="23">
         <f>SUM(E$4:E8)</f>
@@ -77192,7 +77192,7 @@
         <v>46478</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>1736189.828750072</v>
+        <v>1628197.492027584</v>
       </c>
       <c r="C9" s="9">
         <f>SUM(B$4:B9)</f>
@@ -77203,7 +77203,7 @@
         <v/>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.01920797853359233</v>
+        <v>0.01287862486533075</v>
       </c>
       <c r="F9" s="23">
         <f>SUM(E$4:E9)</f>
@@ -77215,7 +77215,7 @@
         <v>46508</v>
       </c>
       <c r="B10" s="9" t="n">
-        <v>1435486.418335914</v>
+        <v>1359773.798666298</v>
       </c>
       <c r="C10" s="9">
         <f>SUM(B$4:B10)</f>
@@ -77226,7 +77226,7 @@
         <v/>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0.03127697796773721</v>
+        <v>0.02678590646167296</v>
       </c>
       <c r="F10" s="23">
         <f>SUM(E$4:E10)</f>
@@ -77238,7 +77238,7 @@
         <v>46539</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>1953908.69113037</v>
+        <v>1796308.819662572</v>
       </c>
       <c r="C11" s="9">
         <f>SUM(B$4:B11)</f>
@@ -77249,7 +77249,7 @@
         <v/>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.0451129400784422</v>
+        <v>0.03464160657540269</v>
       </c>
       <c r="F11" s="23">
         <f>SUM(E$4:E11)</f>
@@ -77261,7 +77261,7 @@
         <v>46569</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>1301536.665192205</v>
+        <v>1303669.89269185</v>
       </c>
       <c r="C12" s="9">
         <f>SUM(B$4:B12)</f>
@@ -77272,7 +77272,7 @@
         <v/>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.04210792094747215</v>
+        <v>0.0423125577926599</v>
       </c>
       <c r="F12" s="23">
         <f>SUM(E$4:E12)</f>
@@ -77284,7 +77284,7 @@
         <v>46600</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>1434567.071153576</v>
+        <v>1625994.299509653</v>
       </c>
       <c r="C13" s="9">
         <f>SUM(B$4:B13)</f>
@@ -77295,7 +77295,7 @@
         <v/>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.04062566597934238</v>
+        <v>0.05127385094940848</v>
       </c>
       <c r="F13" s="23">
         <f>SUM(E$4:E13)</f>
@@ -77307,7 +77307,7 @@
         <v>46631</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>1651510.041674334</v>
+        <v>1766294.476016181</v>
       </c>
       <c r="C14" s="9">
         <f>SUM(B$4:B14)</f>
@@ -77318,7 +77318,7 @@
         <v/>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.03596624505406881</v>
+        <v>0.04624741568241361</v>
       </c>
       <c r="F14" s="23">
         <f>SUM(E$4:E14)</f>
@@ -77330,7 +77330,7 @@
         <v>46661</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>1729273.516660846</v>
+        <v>1682512.409514225</v>
       </c>
       <c r="C15" s="9">
         <f>SUM(B$4:B15)</f>
@@ -77341,7 +77341,7 @@
         <v/>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0.03817357021076049</v>
+        <v>0.03804258329654849</v>
       </c>
       <c r="F15" s="23">
         <f>SUM(E$4:E15)</f>
@@ -77353,7 +77353,7 @@
         <v>46692</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>2392620.12902667</v>
+        <v>2266493.398056921</v>
       </c>
       <c r="C16" s="9">
         <f>SUM(B$4:B16)</f>
@@ -77364,7 +77364,7 @@
         <v/>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.04403924707643078</v>
+        <v>0.040261234551001</v>
       </c>
       <c r="F16" s="23">
         <f>SUM(E$4:E16)</f>
@@ -77376,7 +77376,7 @@
         <v>46722</v>
       </c>
       <c r="B17" s="9" t="n">
-        <v>2014067.062838126</v>
+        <v>1919790.529655363</v>
       </c>
       <c r="C17" s="9">
         <f>SUM(B$4:B17)</f>
@@ -77387,7 +77387,7 @@
         <v/>
       </c>
       <c r="E17" s="10" t="n">
-        <v>0.0460688563673353</v>
+        <v>0.04396941864266432</v>
       </c>
       <c r="F17" s="23">
         <f>SUM(E$4:E17)</f>
@@ -77399,7 +77399,7 @@
         <v>46753</v>
       </c>
       <c r="B18" s="9" t="n">
-        <v>2254093.084222251</v>
+        <v>2252018.442109223</v>
       </c>
       <c r="C18" s="9">
         <f>SUM(B$4:B18)</f>
@@ -77410,7 +77410,7 @@
         <v/>
       </c>
       <c r="E18" s="10" t="n">
-        <v>0.04421882690995473</v>
+        <v>0.04414193284532374</v>
       </c>
       <c r="F18" s="23">
         <f>SUM(E$4:E18)</f>
@@ -77422,7 +77422,7 @@
         <v>46784</v>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1547362.1648266</v>
+        <v>1577811.5641617</v>
       </c>
       <c r="C19" s="9">
         <f>SUM(B$4:B19)</f>
@@ -77433,7 +77433,7 @@
         <v/>
       </c>
       <c r="E19" s="10" t="n">
-        <v>0.03253845171996104</v>
+        <v>0.03387268475375258</v>
       </c>
       <c r="F19" s="23">
         <f>SUM(E$4:E19)</f>
@@ -77445,7 +77445,7 @@
         <v>46813</v>
       </c>
       <c r="B20" s="9" t="n">
-        <v>2628648.261655338</v>
+        <v>2762045.924319129</v>
       </c>
       <c r="C20" s="9">
         <f>SUM(B$4:B20)</f>
@@ -77456,7 +77456,7 @@
         <v/>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.04529831496648301</v>
+        <v>0.04891604069128763</v>
       </c>
       <c r="F20" s="23">
         <f>SUM(E$4:E20)</f>
@@ -77468,7 +77468,7 @@
         <v>46844</v>
       </c>
       <c r="B21" s="9" t="n">
-        <v>3312454.656340744</v>
+        <v>3379027.264459413</v>
       </c>
       <c r="C21" s="9">
         <f>SUM(B$4:B21)</f>
@@ -77479,7 +77479,7 @@
         <v/>
       </c>
       <c r="E21" s="10" t="n">
-        <v>0.05053857981140839</v>
+        <v>0.04714948391141734</v>
       </c>
       <c r="F21" s="23">
         <f>SUM(E$4:E21)</f>
@@ -77491,7 +77491,7 @@
         <v>46874</v>
       </c>
       <c r="B22" s="9" t="n">
-        <v>2525511.031383557</v>
+        <v>2513138.951734432</v>
       </c>
       <c r="C22" s="9">
         <f>SUM(B$4:B22)</f>
@@ -77502,7 +77502,7 @@
         <v/>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.04726796061307757</v>
+        <v>0.04005261921522792</v>
       </c>
       <c r="F22" s="23">
         <f>SUM(E$4:E22)</f>
@@ -77514,7 +77514,7 @@
         <v>46905</v>
       </c>
       <c r="B23" s="9" t="n">
-        <v>2725504.452635161</v>
+        <v>2704699.365968495</v>
       </c>
       <c r="C23" s="9">
         <f>SUM(B$4:B23)</f>
@@ -77525,7 +77525,7 @@
         <v/>
       </c>
       <c r="E23" s="10" t="n">
-        <v>0.05254287047177084</v>
+        <v>0.05173817961155595</v>
       </c>
       <c r="F23" s="23">
         <f>SUM(E$4:E23)</f>
@@ -77537,7 +77537,7 @@
         <v>46935</v>
       </c>
       <c r="B24" s="9" t="n">
-        <v>2208849.678818159</v>
+        <v>2217277.2476068</v>
       </c>
       <c r="C24" s="9">
         <f>SUM(B$4:B24)</f>
@@ -77548,7 +77548,7 @@
         <v/>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.03938885435468486</v>
+        <v>0.04932846789795158</v>
       </c>
       <c r="F24" s="23">
         <f>SUM(E$4:E24)</f>
@@ -77560,7 +77560,7 @@
         <v>46966</v>
       </c>
       <c r="B25" s="9" t="n">
-        <v>1806364.315503699</v>
+        <v>1794009.798878804</v>
       </c>
       <c r="C25" s="9">
         <f>SUM(B$4:B25)</f>
@@ -77571,7 +77571,7 @@
         <v/>
       </c>
       <c r="E25" s="10" t="n">
-        <v>0.03808806098869292</v>
+        <v>0.04022412844901042</v>
       </c>
       <c r="F25" s="23">
         <f>SUM(E$4:E25)</f>
@@ -77583,7 +77583,7 @@
         <v>46997</v>
       </c>
       <c r="B26" s="9" t="n">
-        <v>1154977.748705478</v>
+        <v>1146711.540434802</v>
       </c>
       <c r="C26" s="9">
         <f>SUM(B$4:B26)</f>
@@ -77594,7 +77594,7 @@
         <v/>
       </c>
       <c r="E26" s="10" t="n">
-        <v>0.02757175335283647</v>
+        <v>0.02698557164857578</v>
       </c>
       <c r="F26" s="23">
         <f>SUM(E$4:E26)</f>
@@ -77606,7 +77606,7 @@
         <v>47027</v>
       </c>
       <c r="B27" s="9" t="n">
-        <v>1409882.753788003</v>
+        <v>1391672.180772132</v>
       </c>
       <c r="C27" s="9">
         <f>SUM(B$4:B27)</f>
@@ -77617,7 +77617,7 @@
         <v/>
       </c>
       <c r="E27" s="10" t="n">
-        <v>0.03310759739754984</v>
+        <v>0.03215077325385727</v>
       </c>
       <c r="F27" s="23">
         <f>SUM(E$4:E27)</f>
@@ -77629,7 +77629,7 @@
         <v>47058</v>
       </c>
       <c r="B28" s="9" t="n">
-        <v>1772895.198802991</v>
+        <v>1762471.077165564</v>
       </c>
       <c r="C28" s="9">
         <f>SUM(B$4:B28)</f>
@@ -77640,7 +77640,7 @@
         <v/>
       </c>
       <c r="E28" s="10" t="n">
-        <v>0.03376821548806752</v>
+        <v>0.03381267162841844</v>
       </c>
       <c r="F28" s="23">
         <f>SUM(E$4:E28)</f>
@@ -77652,7 +77652,7 @@
         <v>47088</v>
       </c>
       <c r="B29" s="9" t="n">
-        <v>1657383.011696295</v>
+        <v>1652866.22105302</v>
       </c>
       <c r="C29" s="9">
         <f>SUM(B$4:B29)</f>
@@ -77663,7 +77663,7 @@
         <v/>
       </c>
       <c r="E29" s="10" t="n">
-        <v>0.03204975435021504</v>
+        <v>0.03240318125079989</v>
       </c>
       <c r="F29" s="23">
         <f>SUM(E$4:E29)</f>
@@ -77675,7 +77675,7 @@
         <v>47119</v>
       </c>
       <c r="B30" s="9" t="n">
-        <v>1544621.848645296</v>
+        <v>1573399.130516641</v>
       </c>
       <c r="C30" s="9">
         <f>SUM(B$4:B30)</f>
@@ -77686,7 +77686,7 @@
         <v/>
       </c>
       <c r="E30" s="10" t="n">
-        <v>0.03045369595671562</v>
+        <v>0.03158243279882086</v>
       </c>
       <c r="F30" s="23">
         <f>SUM(E$4:E30)</f>
@@ -77698,7 +77698,7 @@
         <v>47150</v>
       </c>
       <c r="B31" s="9" t="n">
-        <v>1373489.649442756</v>
+        <v>1404924.737162054</v>
       </c>
       <c r="C31" s="9">
         <f>SUM(B$4:B31)</f>
@@ -77709,7 +77709,7 @@
         <v/>
       </c>
       <c r="E31" s="10" t="n">
-        <v>0.02086956190322678</v>
+        <v>0.02189683675702795</v>
       </c>
       <c r="F31" s="23">
         <f>SUM(E$4:E31)</f>
@@ -77721,7 +77721,7 @@
         <v>47178</v>
       </c>
       <c r="B32" s="9" t="n">
-        <v>1078569.686926963</v>
+        <v>1167993.26587433</v>
       </c>
       <c r="C32" s="9">
         <f>SUM(B$4:B32)</f>
@@ -77732,7 +77732,7 @@
         <v/>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.02009785311910314</v>
+        <v>0.02294207534132536</v>
       </c>
       <c r="F32" s="23">
         <f>SUM(E$4:E32)</f>
@@ -77744,7 +77744,7 @@
         <v>47209</v>
       </c>
       <c r="B33" s="9" t="n">
-        <v>714788.0124320129</v>
+        <v>752189.6030752873</v>
       </c>
       <c r="C33" s="9">
         <f>SUM(B$4:B33)</f>
@@ -77755,7 +77755,7 @@
         <v/>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0.01467548174048175</v>
+        <v>0.01584903729603731</v>
       </c>
       <c r="F33" s="23">
         <f>SUM(E$4:E33)</f>
@@ -77767,7 +77767,7 @@
         <v>47239</v>
       </c>
       <c r="B34" s="9" t="n">
-        <v>923106.7743145761</v>
+        <v>943718.3298701313</v>
       </c>
       <c r="C34" s="9">
         <f>SUM(B$4:B34)</f>
@@ -77778,7 +77778,7 @@
         <v/>
       </c>
       <c r="E34" s="10" t="n">
-        <v>0.01448861516261515</v>
+        <v>0.01513150405150403</v>
       </c>
       <c r="F34" s="23">
         <f>SUM(E$4:E34)</f>

--- a/p6/0580_BOQ_Cost_Mapping.xlsx
+++ b/p6/0580_BOQ_Cost_Mapping.xlsx
@@ -274,12 +274,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'S_Curve'!$A$4:$A$39</f>
+              <f>'S_Curve'!$A$4:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'S_Curve'!$D$4:$D$39</f>
+              <f>'S_Curve'!$D$4:$D$38</f>
             </numRef>
           </val>
         </ser>
@@ -306,12 +306,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'S_Curve'!$A$4:$A$39</f>
+              <f>'S_Curve'!$A$4:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'S_Curve'!$F$4:$F$39</f>
+              <f>'S_Curve'!$F$4:$F$38</f>
             </numRef>
           </val>
         </ser>
@@ -819,7 +819,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Draft contract with ETECHS (22 Jan 2024): Annex 3 price table (Revised-02) and clause 15 payment milestones</t>
+          <t>Signed contract with ETECHS (1 November 2026): Annex 3 price table (Revised-02) and clause 15 payment milestones</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="D215" s="8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="216">
@@ -6499,7 +6499,7 @@
         </is>
       </c>
       <c r="D277" s="8" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="278">
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="D287" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="288">
@@ -7739,7 +7739,7 @@
         </is>
       </c>
       <c r="D339" s="8" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="340">
@@ -7939,7 +7939,7 @@
         </is>
       </c>
       <c r="D349" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="350">
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="D401" s="8" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="402">
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="D411" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="412">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="D463" s="8" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="464">
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="D525" s="8" t="n">
-        <v>265</v>
+        <v>258</v>
       </c>
     </row>
     <row r="526">
@@ -12699,7 +12699,7 @@
         </is>
       </c>
       <c r="D587" s="8" t="n">
-        <v>265</v>
+        <v>258</v>
       </c>
     </row>
     <row r="588">
@@ -13939,7 +13939,7 @@
         </is>
       </c>
       <c r="D649" s="8" t="n">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="650">
@@ -15179,7 +15179,7 @@
         </is>
       </c>
       <c r="D711" s="8" t="n">
-        <v>316</v>
+        <v>308</v>
       </c>
     </row>
     <row r="712">
@@ -16419,7 +16419,7 @@
         </is>
       </c>
       <c r="D773" s="8" t="n">
-        <v>367</v>
+        <v>358</v>
       </c>
     </row>
     <row r="774">
@@ -16619,7 +16619,7 @@
         </is>
       </c>
       <c r="D783" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="784">
@@ -17659,7 +17659,7 @@
         </is>
       </c>
       <c r="D835" s="8" t="n">
-        <v>401</v>
+        <v>391</v>
       </c>
     </row>
     <row r="836">
@@ -19690,7 +19690,7 @@
         <v>46539</v>
       </c>
       <c r="B12" s="25" t="n">
-        <v>46548</v>
+        <v>46544</v>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
@@ -19737,10 +19737,10 @@
     </row>
     <row r="13">
       <c r="A13" s="24" t="n">
-        <v>46569</v>
+        <v>46539</v>
       </c>
       <c r="B13" s="25" t="n">
-        <v>46569</v>
+        <v>46565</v>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>46631</v>
       </c>
       <c r="B16" s="25" t="n">
-        <v>46656</v>
+        <v>46651</v>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>46661</v>
       </c>
       <c r="B17" s="25" t="n">
-        <v>46677</v>
+        <v>46673</v>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         <v>46692</v>
       </c>
       <c r="B22" s="25" t="n">
-        <v>46712</v>
+        <v>46705</v>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>46692</v>
       </c>
       <c r="B23" s="25" t="n">
-        <v>46712</v>
+        <v>46705</v>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
@@ -20290,21 +20290,21 @@
         <v>46722</v>
       </c>
       <c r="B24" s="25" t="n">
-        <v>46727</v>
+        <v>46726</v>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>MS6</t>
+          <t>MS3</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Testing and commissioning (SAT)</t>
+          <t>SAR approval of engineering</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Riyadh (Thumamah) (NRY)</t>
+          <t>Al Qassim (NQS)</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -20314,16 +20314,16 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>NRY-T1100</t>
+          <t>NQS-E1210</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>MS6 SAT complete (10%) - Riyadh (Thumamah)</t>
+          <t>MS3 Engineering approved by SAR (10%) - Al Qassim</t>
         </is>
       </c>
       <c r="I24" s="9">
-        <f>Payment_Milestones!G16</f>
+        <f>Payment_Milestones!D21</f>
         <v/>
       </c>
       <c r="J24" s="9">
@@ -20340,7 +20340,7 @@
         <v>46722</v>
       </c>
       <c r="B25" s="25" t="n">
-        <v>46733</v>
+        <v>46726</v>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
@@ -20354,26 +20354,26 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Al Qassim (NQS)</t>
+          <t>Hufuf (EHF)</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>NSR</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>NQS-E1210</t>
+          <t>EHF-E1210</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>MS3 Engineering approved by SAR (10%) - Al Qassim</t>
+          <t>MS3 Engineering approved by SAR (10%) - Hufuf</t>
         </is>
       </c>
       <c r="I25" s="9">
-        <f>Payment_Milestones!D21</f>
+        <f>Payment_Milestones!D22</f>
         <v/>
       </c>
       <c r="J25" s="9">
@@ -20390,40 +20390,40 @@
         <v>46722</v>
       </c>
       <c r="B26" s="25" t="n">
-        <v>46733</v>
+        <v>46727</v>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>MS3</t>
+          <t>MS6</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>SAR approval of engineering</t>
+          <t>Testing and commissioning (SAT)</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Hufuf (EHF)</t>
+          <t>Riyadh (Thumamah) (NRY)</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>NSR</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>EHF-E1210</t>
+          <t>NRY-T1100</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>MS3 Engineering approved by SAR (10%) - Hufuf</t>
+          <t>MS6 SAT complete (10%) - Riyadh (Thumamah)</t>
         </is>
       </c>
       <c r="I26" s="9">
-        <f>Payment_Milestones!D22</f>
+        <f>Payment_Milestones!G16</f>
         <v/>
       </c>
       <c r="J26" s="9">
@@ -20437,10 +20437,10 @@
     </row>
     <row r="27">
       <c r="A27" s="24" t="n">
-        <v>46753</v>
+        <v>46722</v>
       </c>
       <c r="B27" s="25" t="n">
-        <v>46754</v>
+        <v>46748</v>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
@@ -20487,43 +20487,43 @@
     </row>
     <row r="28">
       <c r="A28" s="24" t="n">
-        <v>46753</v>
+        <v>46722</v>
       </c>
       <c r="B28" s="25" t="n">
-        <v>46758</v>
+        <v>46751</v>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>MS7</t>
+          <t>MS2</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Final acceptance and handover</t>
+          <t>Engineering submittal</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Riyadh (Malaz) (ERY)</t>
+          <t>Al Majma'ah (NMJ)</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>NSR</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>ERY-T3100</t>
+          <t>NMJ-E1200</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>MS7 Station accepted - final acceptance and handover (10%) - Riyadh (Malaz)</t>
+          <t>MS2 Engineering submittal complete (10%) - Al Majma'ah</t>
         </is>
       </c>
       <c r="I28" s="9">
-        <f>Payment_Milestones!H18</f>
+        <f>Payment_Milestones!C23</f>
         <v/>
       </c>
       <c r="J28" s="9">
@@ -20540,40 +20540,40 @@
         <v>46753</v>
       </c>
       <c r="B29" s="25" t="n">
-        <v>46761</v>
+        <v>46769</v>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>MS2</t>
+          <t>MS7</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Engineering submittal</t>
+          <t>Final acceptance and handover</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Al Majma'ah (NMJ)</t>
+          <t>Riyadh (Malaz) (ERY)</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>NSR</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>NMJ-E1200</t>
+          <t>ERY-T3100</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>MS2 Engineering submittal complete (10%) - Al Majma'ah</t>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Riyadh (Malaz)</t>
         </is>
       </c>
       <c r="I29" s="9">
-        <f>Payment_Milestones!C23</f>
+        <f>Payment_Milestones!H18</f>
         <v/>
       </c>
       <c r="J29" s="9">
@@ -20590,21 +20590,21 @@
         <v>46753</v>
       </c>
       <c r="B30" s="25" t="n">
-        <v>46777</v>
+        <v>46772</v>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>MS7</t>
+          <t>MS3</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Final acceptance and handover</t>
+          <t>SAR approval of engineering</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Riyadh (Thumamah) (NRY)</t>
+          <t>Al Majma'ah (NMJ)</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -20614,16 +20614,16 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>NRY-T3100</t>
+          <t>NMJ-E1210</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>MS7 Station accepted - final acceptance and handover (10%) - Riyadh (Thumamah)</t>
+          <t>MS3 Engineering approved by SAR (10%) - Al Majma'ah</t>
         </is>
       </c>
       <c r="I30" s="9">
-        <f>Payment_Milestones!H16</f>
+        <f>Payment_Milestones!D23</f>
         <v/>
       </c>
       <c r="J30" s="9">
@@ -20640,40 +20640,40 @@
         <v>46753</v>
       </c>
       <c r="B31" s="25" t="n">
-        <v>46782</v>
+        <v>46783</v>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>MS3</t>
+          <t>MS4</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>SAR approval of engineering</t>
+          <t>Material delivery</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Al Majma'ah (NMJ)</t>
+          <t>Dammam (EDM)</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>NSR</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>NMJ-E1210</t>
+          <t>EDM-P1100</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>MS3 Engineering approved by SAR (10%) - Al Majma'ah</t>
+          <t>MS4 Material delivered (20%) - Dammam</t>
         </is>
       </c>
       <c r="I31" s="9">
-        <f>Payment_Milestones!D23</f>
+        <f>Payment_Milestones!E20</f>
         <v/>
       </c>
       <c r="J31" s="9">
@@ -20690,40 +20690,40 @@
         <v>46784</v>
       </c>
       <c r="B32" s="25" t="n">
-        <v>46785</v>
+        <v>46786</v>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>MS4</t>
+          <t>MS7</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Material delivery</t>
+          <t>Final acceptance and handover</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Dammam (EDM)</t>
+          <t>Riyadh (Thumamah) (NRY)</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>NSR</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>EDM-P1100</t>
+          <t>NRY-T3100</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>MS4 Material delivered (20%) - Dammam</t>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Riyadh (Thumamah)</t>
         </is>
       </c>
       <c r="I32" s="9">
-        <f>Payment_Milestones!E20</f>
+        <f>Payment_Milestones!H16</f>
         <v/>
       </c>
       <c r="J32" s="9">
@@ -20787,10 +20787,10 @@
     </row>
     <row r="34">
       <c r="A34" s="24" t="n">
-        <v>46844</v>
+        <v>46813</v>
       </c>
       <c r="B34" s="25" t="n">
-        <v>46846</v>
+        <v>46839</v>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
@@ -20837,10 +20837,10 @@
     </row>
     <row r="35">
       <c r="A35" s="24" t="n">
-        <v>46844</v>
+        <v>46813</v>
       </c>
       <c r="B35" s="25" t="n">
-        <v>46846</v>
+        <v>46842</v>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
@@ -20890,40 +20890,40 @@
         <v>46844</v>
       </c>
       <c r="B36" s="25" t="n">
-        <v>46855</v>
+        <v>46849</v>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>MS5</t>
+          <t>MS4</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Installation</t>
+          <t>Material delivery</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Jeddah (HJD)</t>
+          <t>Al Qassim (NQS)</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>HHR</t>
+          <t>NSR</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>HJD-C2100</t>
+          <t>NQS-P1100</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>MS5 Installation complete (20%) - Jeddah</t>
+          <t>MS4 Material delivered (20%) - Al Qassim</t>
         </is>
       </c>
       <c r="I36" s="9">
-        <f>Payment_Milestones!F19</f>
+        <f>Payment_Milestones!E21</f>
         <v/>
       </c>
       <c r="J36" s="9">
@@ -20940,40 +20940,40 @@
         <v>46844</v>
       </c>
       <c r="B37" s="25" t="n">
-        <v>46856</v>
+        <v>46849</v>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>MS4</t>
+          <t>MS5</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Material delivery</t>
+          <t>Installation</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Al Qassim (NQS)</t>
+          <t>Jeddah (HJD)</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>NSR</t>
+          <t>HHR</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>NQS-P1100</t>
+          <t>HJD-C2100</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>MS4 Material delivered (20%) - Al Qassim</t>
+          <t>MS5 Installation complete (20%) - Jeddah</t>
         </is>
       </c>
       <c r="I37" s="9">
-        <f>Payment_Milestones!E21</f>
+        <f>Payment_Milestones!F19</f>
         <v/>
       </c>
       <c r="J37" s="9">
@@ -20990,7 +20990,7 @@
         <v>46844</v>
       </c>
       <c r="B38" s="25" t="n">
-        <v>46862</v>
+        <v>46860</v>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
@@ -21004,26 +21004,26 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Makkah (HMK)</t>
+          <t>Dammam (EDM)</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>HHR</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>HMK-T1100</t>
+          <t>EDM-T1100</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>MS6 SAT complete (10%) - Makkah</t>
+          <t>MS6 SAT complete (10%) - Dammam</t>
         </is>
       </c>
       <c r="I38" s="9">
-        <f>Payment_Milestones!G17</f>
+        <f>Payment_Milestones!G20</f>
         <v/>
       </c>
       <c r="J38" s="9">
@@ -21040,40 +21040,40 @@
         <v>46844</v>
       </c>
       <c r="B39" s="25" t="n">
-        <v>46862</v>
+        <v>46861</v>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>MS6</t>
+          <t>MS2</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Testing and commissioning (SAT)</t>
+          <t>Engineering submittal</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Dammam (EDM)</t>
+          <t>KAEC (HKA)</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>HHR</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>EDM-T1100</t>
+          <t>HKA-E1200</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>MS6 SAT complete (10%) - Dammam</t>
+          <t>MS2 Engineering submittal complete (10%) - KAEC</t>
         </is>
       </c>
       <c r="I39" s="9">
-        <f>Payment_Milestones!G20</f>
+        <f>Payment_Milestones!C24</f>
         <v/>
       </c>
       <c r="J39" s="9">
@@ -21090,7 +21090,7 @@
         <v>46844</v>
       </c>
       <c r="B40" s="25" t="n">
-        <v>46870</v>
+        <v>46861</v>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>KAEC (HKA)</t>
+          <t>Madinah (HMD)</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -21114,16 +21114,16 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>HKA-E1200</t>
+          <t>HMD-E1200</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>MS2 Engineering submittal complete (10%) - KAEC</t>
+          <t>MS2 Engineering submittal complete (10%) - Madinah</t>
         </is>
       </c>
       <c r="I40" s="9">
-        <f>Payment_Milestones!C24</f>
+        <f>Payment_Milestones!C25</f>
         <v/>
       </c>
       <c r="J40" s="9">
@@ -21140,21 +21140,21 @@
         <v>46844</v>
       </c>
       <c r="B41" s="25" t="n">
-        <v>46870</v>
+        <v>46862</v>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>MS2</t>
+          <t>MS6</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Engineering submittal</t>
+          <t>Testing and commissioning (SAT)</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Madinah (HMD)</t>
+          <t>Makkah (HMK)</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -21164,16 +21164,16 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>HMD-E1200</t>
+          <t>HMK-T1100</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>MS2 Engineering submittal complete (10%) - Madinah</t>
+          <t>MS6 SAT complete (10%) - Makkah</t>
         </is>
       </c>
       <c r="I41" s="9">
-        <f>Payment_Milestones!C25</f>
+        <f>Payment_Milestones!G17</f>
         <v/>
       </c>
       <c r="J41" s="9">
@@ -21190,7 +21190,7 @@
         <v>46874</v>
       </c>
       <c r="B42" s="25" t="n">
-        <v>46898</v>
+        <v>46889</v>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>46874</v>
       </c>
       <c r="B43" s="25" t="n">
-        <v>46898</v>
+        <v>46889</v>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>46874</v>
       </c>
       <c r="B44" s="25" t="n">
-        <v>46898</v>
+        <v>46894</v>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>46874</v>
       </c>
       <c r="B45" s="25" t="n">
-        <v>46903</v>
+        <v>46896</v>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
@@ -21387,10 +21387,10 @@
     </row>
     <row r="46">
       <c r="A46" s="24" t="n">
-        <v>46905</v>
+        <v>46874</v>
       </c>
       <c r="B46" s="25" t="n">
-        <v>46912</v>
+        <v>46904</v>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>46905</v>
       </c>
       <c r="B47" s="25" t="n">
-        <v>46919</v>
+        <v>46912</v>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>46905</v>
       </c>
       <c r="B48" s="25" t="n">
-        <v>46925</v>
+        <v>46918</v>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
@@ -21540,40 +21540,40 @@
         <v>46905</v>
       </c>
       <c r="B49" s="25" t="n">
-        <v>46932</v>
+        <v>46922</v>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>MS7</t>
+          <t>MS2</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Final acceptance and handover</t>
+          <t>Engineering submittal</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Makkah (HMK)</t>
+          <t>Abqaiq (EAB)</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>HHR</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>HMK-T3100</t>
+          <t>EAB-E1200</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>MS7 Station accepted - final acceptance and handover (10%) - Makkah</t>
+          <t>MS2 Engineering submittal complete (10%) - Abqaiq</t>
         </is>
       </c>
       <c r="I49" s="9">
-        <f>Payment_Milestones!H17</f>
+        <f>Payment_Milestones!C26</f>
         <v/>
       </c>
       <c r="J49" s="9">
@@ -21587,43 +21587,43 @@
     </row>
     <row r="50">
       <c r="A50" s="24" t="n">
-        <v>46905</v>
+        <v>46935</v>
       </c>
       <c r="B50" s="25" t="n">
-        <v>46932</v>
+        <v>46937</v>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>MS7</t>
+          <t>MS6</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Final acceptance and handover</t>
+          <t>Testing and commissioning (SAT)</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>Dammam (EDM)</t>
+          <t>Al Qassim (NQS)</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>NSR</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>EDM-T3100</t>
+          <t>NQS-T1100</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>MS7 Station accepted - final acceptance and handover (10%) - Dammam</t>
+          <t>MS6 SAT complete (10%) - Al Qassim</t>
         </is>
       </c>
       <c r="I50" s="9">
-        <f>Payment_Milestones!H20</f>
+        <f>Payment_Milestones!G21</f>
         <v/>
       </c>
       <c r="J50" s="9">
@@ -21637,24 +21637,24 @@
     </row>
     <row r="51">
       <c r="A51" s="24" t="n">
-        <v>46905</v>
+        <v>46935</v>
       </c>
       <c r="B51" s="25" t="n">
-        <v>46933</v>
+        <v>46939</v>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>MS2</t>
+          <t>MS7</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Engineering submittal</t>
+          <t>Final acceptance and handover</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Abqaiq (EAB)</t>
+          <t>Dammam (EDM)</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -21664,16 +21664,16 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>EAB-E1200</t>
+          <t>EDM-T3100</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>MS2 Engineering submittal complete (10%) - Abqaiq</t>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Dammam</t>
         </is>
       </c>
       <c r="I51" s="9">
-        <f>Payment_Milestones!C26</f>
+        <f>Payment_Milestones!H20</f>
         <v/>
       </c>
       <c r="J51" s="9">
@@ -21690,40 +21690,40 @@
         <v>46935</v>
       </c>
       <c r="B52" s="25" t="n">
-        <v>46944</v>
+        <v>46943</v>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>MS6</t>
+          <t>MS3</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Testing and commissioning (SAT)</t>
+          <t>SAR approval of engineering</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>Al Qassim (NQS)</t>
+          <t>Abqaiq (EAB)</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>NSR</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>NQS-T1100</t>
+          <t>EAB-E1210</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>MS6 SAT complete (10%) - Al Qassim</t>
+          <t>MS3 Engineering approved by SAR (10%) - Abqaiq</t>
         </is>
       </c>
       <c r="I52" s="9">
-        <f>Payment_Milestones!G21</f>
+        <f>Payment_Milestones!D26</f>
         <v/>
       </c>
       <c r="J52" s="9">
@@ -21740,40 +21740,40 @@
         <v>46935</v>
       </c>
       <c r="B53" s="25" t="n">
-        <v>46954</v>
+        <v>46943</v>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>MS3</t>
+          <t>MS7</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>SAR approval of engineering</t>
+          <t>Final acceptance and handover</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Abqaiq (EAB)</t>
+          <t>Makkah (HMK)</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>HHR</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>EAB-E1210</t>
+          <t>HMK-T3100</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>MS3 Engineering approved by SAR (10%) - Abqaiq</t>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Makkah</t>
         </is>
       </c>
       <c r="I53" s="9">
-        <f>Payment_Milestones!D26</f>
+        <f>Payment_Milestones!H17</f>
         <v/>
       </c>
       <c r="J53" s="9">
@@ -21790,7 +21790,7 @@
         <v>46935</v>
       </c>
       <c r="B54" s="25" t="n">
-        <v>46957</v>
+        <v>46946</v>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
@@ -21837,43 +21837,43 @@
     </row>
     <row r="55">
       <c r="A55" s="24" t="n">
-        <v>46935</v>
+        <v>46966</v>
       </c>
       <c r="B55" s="25" t="n">
-        <v>46961</v>
+        <v>46966</v>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>MS7</t>
+          <t>MS5</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Final acceptance and handover</t>
+          <t>Installation</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>Jeddah (HJD)</t>
+          <t>Al Majma'ah (NMJ)</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>HHR</t>
+          <t>NSR</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>HJD-T3100</t>
+          <t>NMJ-C2100</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>MS7 Station accepted - final acceptance and handover (10%) - Jeddah</t>
+          <t>MS5 Installation complete (20%) - Al Majma'ah</t>
         </is>
       </c>
       <c r="I55" s="9">
-        <f>Payment_Milestones!H19</f>
+        <f>Payment_Milestones!F23</f>
         <v/>
       </c>
       <c r="J55" s="9">
@@ -21890,40 +21890,40 @@
         <v>46966</v>
       </c>
       <c r="B56" s="25" t="n">
-        <v>46974</v>
+        <v>46966</v>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>MS5</t>
+          <t>MS7</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Installation</t>
+          <t>Final acceptance and handover</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Al Majma'ah (NMJ)</t>
+          <t>Jeddah (HJD)</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>NSR</t>
+          <t>HHR</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>NMJ-C2100</t>
+          <t>HJD-T3100</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>MS5 Installation complete (20%) - Al Majma'ah</t>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Jeddah</t>
         </is>
       </c>
       <c r="I56" s="9">
-        <f>Payment_Milestones!F23</f>
+        <f>Payment_Milestones!H19</f>
         <v/>
       </c>
       <c r="J56" s="9">
@@ -21940,7 +21940,7 @@
         <v>46966</v>
       </c>
       <c r="B57" s="25" t="n">
-        <v>46978</v>
+        <v>46967</v>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
@@ -21990,40 +21990,40 @@
         <v>46966</v>
       </c>
       <c r="B58" s="25" t="n">
-        <v>46982</v>
+        <v>46985</v>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>MS7</t>
+          <t>MS6</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Final acceptance and handover</t>
+          <t>Testing and commissioning (SAT)</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>Hufuf (EHF)</t>
+          <t>Al Majma'ah (NMJ)</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>NSR</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>EHF-T3100</t>
+          <t>NMJ-T1100</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>MS7 Station accepted - final acceptance and handover (10%) - Hufuf</t>
+          <t>MS6 SAT complete (10%) - Al Majma'ah</t>
         </is>
       </c>
       <c r="I58" s="9">
-        <f>Payment_Milestones!H22</f>
+        <f>Payment_Milestones!G23</f>
         <v/>
       </c>
       <c r="J58" s="9">
@@ -22040,40 +22040,40 @@
         <v>46966</v>
       </c>
       <c r="B59" s="25" t="n">
-        <v>46993</v>
+        <v>46986</v>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>MS6</t>
+          <t>MS7</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Testing and commissioning (SAT)</t>
+          <t>Final acceptance and handover</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Al Majma'ah (NMJ)</t>
+          <t>Hufuf (EHF)</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>NSR</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>NMJ-T1100</t>
+          <t>EHF-T3100</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>MS6 SAT complete (10%) - Al Majma'ah</t>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Hufuf</t>
         </is>
       </c>
       <c r="I59" s="9">
-        <f>Payment_Milestones!G23</f>
+        <f>Payment_Milestones!H22</f>
         <v/>
       </c>
       <c r="J59" s="9">
@@ -22090,7 +22090,7 @@
         <v>46997</v>
       </c>
       <c r="B60" s="25" t="n">
-        <v>47007</v>
+        <v>47009</v>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
@@ -22137,10 +22137,10 @@
     </row>
     <row r="61">
       <c r="A61" s="24" t="n">
-        <v>47027</v>
+        <v>46997</v>
       </c>
       <c r="B61" s="25" t="n">
-        <v>47034</v>
+        <v>47023</v>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>47027</v>
       </c>
       <c r="B62" s="25" t="n">
-        <v>47041</v>
+        <v>47030</v>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>47027</v>
       </c>
       <c r="B63" s="25" t="n">
-        <v>47042</v>
+        <v>47031</v>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>47027</v>
       </c>
       <c r="B64" s="25" t="n">
-        <v>47055</v>
+        <v>47044</v>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
@@ -22340,40 +22340,40 @@
         <v>47027</v>
       </c>
       <c r="B65" s="25" t="n">
-        <v>47056</v>
+        <v>47044</v>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>MS7</t>
+          <t>MS4</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Final acceptance and handover</t>
+          <t>Material delivery</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Al Majma'ah (NMJ)</t>
+          <t>Abqaiq (EAB)</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>NSR</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>NMJ-T3100</t>
+          <t>EAB-P1100</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>MS7 Station accepted - final acceptance and handover (10%) - Al Majma'ah</t>
+          <t>MS4 Material delivered (20%) - Abqaiq</t>
         </is>
       </c>
       <c r="I65" s="9">
-        <f>Payment_Milestones!H23</f>
+        <f>Payment_Milestones!E26</f>
         <v/>
       </c>
       <c r="J65" s="9">
@@ -22394,36 +22394,36 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>MS4</t>
+          <t>MS7</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Material delivery</t>
+          <t>Final acceptance and handover</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Abqaiq (EAB)</t>
+          <t>Al Majma'ah (NMJ)</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>NSR</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>EAB-P1100</t>
+          <t>NMJ-T3100</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>MS4 Material delivered (20%) - Abqaiq</t>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Al Majma'ah</t>
         </is>
       </c>
       <c r="I66" s="9">
-        <f>Payment_Milestones!E26</f>
+        <f>Payment_Milestones!H23</f>
         <v/>
       </c>
       <c r="J66" s="9">
@@ -22440,7 +22440,7 @@
         <v>47058</v>
       </c>
       <c r="B67" s="25" t="n">
-        <v>47083</v>
+        <v>47069</v>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
@@ -22487,10 +22487,10 @@
     </row>
     <row r="68">
       <c r="A68" s="24" t="n">
-        <v>47088</v>
+        <v>47058</v>
       </c>
       <c r="B68" s="25" t="n">
-        <v>47093</v>
+        <v>47080</v>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
@@ -22537,10 +22537,10 @@
     </row>
     <row r="69">
       <c r="A69" s="24" t="n">
-        <v>47088</v>
+        <v>47058</v>
       </c>
       <c r="B69" s="25" t="n">
-        <v>47094</v>
+        <v>47085</v>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>47088</v>
       </c>
       <c r="B70" s="25" t="n">
-        <v>47104</v>
+        <v>47090</v>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>47088</v>
       </c>
       <c r="B71" s="25" t="n">
-        <v>47108</v>
+        <v>47097</v>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>47119</v>
       </c>
       <c r="B72" s="25" t="n">
-        <v>47136</v>
+        <v>47127</v>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>47119</v>
       </c>
       <c r="B73" s="25" t="n">
-        <v>47141</v>
+        <v>47132</v>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
@@ -22787,10 +22787,10 @@
     </row>
     <row r="74">
       <c r="A74" s="24" t="n">
-        <v>47150</v>
+        <v>47119</v>
       </c>
       <c r="B74" s="25" t="n">
-        <v>47156</v>
+        <v>47147</v>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>47150</v>
       </c>
       <c r="B75" s="25" t="n">
-        <v>47174</v>
+        <v>47155</v>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
@@ -22887,10 +22887,10 @@
     </row>
     <row r="76">
       <c r="A76" s="24" t="n">
-        <v>47178</v>
+        <v>47150</v>
       </c>
       <c r="B76" s="25" t="n">
-        <v>47178</v>
+        <v>47168</v>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
@@ -22937,10 +22937,10 @@
     </row>
     <row r="77">
       <c r="A77" s="24" t="n">
-        <v>47178</v>
+        <v>47150</v>
       </c>
       <c r="B77" s="25" t="n">
-        <v>47181</v>
+        <v>47169</v>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
@@ -22987,43 +22987,43 @@
     </row>
     <row r="78">
       <c r="A78" s="24" t="n">
-        <v>47178</v>
+        <v>47150</v>
       </c>
       <c r="B78" s="25" t="n">
-        <v>47181</v>
+        <v>47174</v>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>MS7</t>
+          <t>MS6</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Final acceptance and handover</t>
+          <t>Testing and commissioning (SAT)</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Abqaiq (EAB)</t>
+          <t>Hail (NHL)</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>NSR</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>EAB-T3100</t>
+          <t>NHL-T1100</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>MS7 Station accepted - final acceptance and handover (10%) - Abqaiq</t>
+          <t>MS6 SAT complete (10%) - Hail</t>
         </is>
       </c>
       <c r="I78" s="9">
-        <f>Payment_Milestones!H26</f>
+        <f>Payment_Milestones!G27</f>
         <v/>
       </c>
       <c r="J78" s="9">
@@ -23037,43 +23037,43 @@
     </row>
     <row r="79">
       <c r="A79" s="24" t="n">
-        <v>47178</v>
+        <v>47150</v>
       </c>
       <c r="B79" s="25" t="n">
-        <v>47183</v>
+        <v>47177</v>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>MS6</t>
+          <t>MS7</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>Testing and commissioning (SAT)</t>
+          <t>Final acceptance and handover</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Hail (NHL)</t>
+          <t>Abqaiq (EAB)</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>NSR</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>NHL-T1100</t>
+          <t>EAB-T3100</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>MS6 SAT complete (10%) - Hail</t>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Abqaiq</t>
         </is>
       </c>
       <c r="I79" s="9">
-        <f>Payment_Milestones!G27</f>
+        <f>Payment_Milestones!H26</f>
         <v/>
       </c>
       <c r="J79" s="9">
@@ -23090,7 +23090,7 @@
         <v>47209</v>
       </c>
       <c r="B80" s="25" t="n">
-        <v>47237</v>
+        <v>47216</v>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
@@ -23140,40 +23140,40 @@
         <v>47239</v>
       </c>
       <c r="B81" s="25" t="n">
-        <v>47244</v>
+        <v>47239</v>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>MS7</t>
+          <t>MS5</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Final acceptance and handover</t>
+          <t>Installation</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>KAEC (HKA)</t>
+          <t>Al Jouf (NJF)</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>HHR</t>
+          <t>NSR</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>HKA-T3100</t>
+          <t>NJF-C2100</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>MS7 Station accepted - final acceptance and handover (10%) - KAEC</t>
+          <t>MS5 Installation complete (20%) - Al Jouf</t>
         </is>
       </c>
       <c r="I81" s="9">
-        <f>Payment_Milestones!H24</f>
+        <f>Payment_Milestones!F28</f>
         <v/>
       </c>
       <c r="J81" s="9">
@@ -23190,40 +23190,40 @@
         <v>47239</v>
       </c>
       <c r="B82" s="25" t="n">
-        <v>47248</v>
+        <v>47244</v>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>MS5</t>
+          <t>MS7</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Installation</t>
+          <t>Final acceptance and handover</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Al Jouf (NJF)</t>
+          <t>KAEC (HKA)</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>NSR</t>
+          <t>HHR</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>NJF-C2100</t>
+          <t>HKA-T3100</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>MS5 Installation complete (20%) - Al Jouf</t>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - KAEC</t>
         </is>
       </c>
       <c r="I82" s="9">
-        <f>Payment_Milestones!F28</f>
+        <f>Payment_Milestones!H24</f>
         <v/>
       </c>
       <c r="J82" s="9">
@@ -23340,7 +23340,7 @@
         <v>47239</v>
       </c>
       <c r="B85" s="25" t="n">
-        <v>47267</v>
+        <v>47258</v>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
@@ -23390,7 +23390,7 @@
         <v>47270</v>
       </c>
       <c r="B86" s="25" t="n">
-        <v>47297</v>
+        <v>47283</v>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>47300</v>
       </c>
       <c r="B87" s="25" t="n">
-        <v>47316</v>
+        <v>47302</v>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>47362</v>
       </c>
       <c r="B89" s="25" t="n">
-        <v>47379</v>
+        <v>47374</v>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
@@ -30909,10 +30909,10 @@
         <v/>
       </c>
       <c r="T13" s="20" t="n">
-        <v>47379</v>
+        <v>47374</v>
       </c>
       <c r="U13" s="20" t="n">
-        <v>47393</v>
+        <v>47388</v>
       </c>
       <c r="V13" s="8" t="n">
         <v>10</v>
@@ -34167,10 +34167,10 @@
         <v>46756</v>
       </c>
       <c r="U48" s="20" t="n">
-        <v>46776</v>
+        <v>46785</v>
       </c>
       <c r="V48" s="8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
@@ -35831,7 +35831,7 @@
         </is>
       </c>
       <c r="R66" s="9" t="n">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="S66" s="19">
         <f>R66/1000</f>
@@ -37515,10 +37515,10 @@
         <v>46911</v>
       </c>
       <c r="U84" s="20" t="n">
-        <v>46931</v>
+        <v>46940</v>
       </c>
       <c r="V84" s="8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85">
@@ -40770,10 +40770,10 @@
         <v>46737</v>
       </c>
       <c r="U119" s="20" t="n">
-        <v>46757</v>
+        <v>46768</v>
       </c>
       <c r="V119" s="8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="120">
@@ -40860,10 +40860,10 @@
         <v/>
       </c>
       <c r="T120" s="20" t="n">
-        <v>46447</v>
+        <v>46443</v>
       </c>
       <c r="U120" s="20" t="n">
-        <v>46482</v>
+        <v>46478</v>
       </c>
       <c r="V120" s="8" t="n">
         <v>21</v>
@@ -40953,10 +40953,10 @@
         <v/>
       </c>
       <c r="T121" s="20" t="n">
-        <v>46483</v>
+        <v>46481</v>
       </c>
       <c r="U121" s="20" t="n">
-        <v>46503</v>
+        <v>46499</v>
       </c>
       <c r="V121" s="8" t="n">
         <v>15</v>
@@ -41046,10 +41046,10 @@
         <v/>
       </c>
       <c r="T122" s="20" t="n">
-        <v>46483</v>
+        <v>46481</v>
       </c>
       <c r="U122" s="20" t="n">
-        <v>46490</v>
+        <v>46488</v>
       </c>
       <c r="V122" s="8" t="n">
         <v>6</v>
@@ -41139,10 +41139,10 @@
         <v/>
       </c>
       <c r="T123" s="20" t="n">
-        <v>46491</v>
+        <v>46489</v>
       </c>
       <c r="U123" s="20" t="n">
-        <v>46511</v>
+        <v>46509</v>
       </c>
       <c r="V123" s="8" t="n">
         <v>15</v>
@@ -41225,20 +41225,20 @@
         </is>
       </c>
       <c r="R124" s="9" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="S124" s="19">
         <f>R124/1000</f>
         <v/>
       </c>
       <c r="T124" s="20" t="n">
-        <v>46491</v>
+        <v>46489</v>
       </c>
       <c r="U124" s="20" t="n">
-        <v>46505</v>
+        <v>46502</v>
       </c>
       <c r="V124" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125">
@@ -41318,17 +41318,17 @@
         </is>
       </c>
       <c r="R125" s="9" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="S125" s="19">
         <f>R125/1000</f>
         <v/>
       </c>
       <c r="T125" s="20" t="n">
-        <v>46506</v>
+        <v>46503</v>
       </c>
       <c r="U125" s="20" t="n">
-        <v>46533</v>
+        <v>46530</v>
       </c>
       <c r="V125" s="8" t="n">
         <v>15</v>
@@ -41411,20 +41411,20 @@
         </is>
       </c>
       <c r="R126" s="9" t="n">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="S126" s="19">
         <f>R126/1000</f>
         <v/>
       </c>
       <c r="T126" s="20" t="n">
-        <v>46506</v>
+        <v>46503</v>
       </c>
       <c r="U126" s="20" t="n">
-        <v>46537</v>
+        <v>46531</v>
       </c>
       <c r="V126" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127">
@@ -41504,17 +41504,17 @@
         </is>
       </c>
       <c r="R127" s="9" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="S127" s="19">
         <f>R127/1000</f>
         <v/>
       </c>
       <c r="T127" s="20" t="n">
-        <v>46538</v>
+        <v>46532</v>
       </c>
       <c r="U127" s="20" t="n">
-        <v>46558</v>
+        <v>46552</v>
       </c>
       <c r="V127" s="8" t="n">
         <v>15</v>
@@ -41604,10 +41604,10 @@
         <v/>
       </c>
       <c r="T128" s="20" t="n">
-        <v>46538</v>
+        <v>46532</v>
       </c>
       <c r="U128" s="20" t="n">
-        <v>46547</v>
+        <v>46541</v>
       </c>
       <c r="V128" s="8" t="n">
         <v>8</v>
@@ -41697,10 +41697,10 @@
         <v/>
       </c>
       <c r="T129" s="20" t="n">
-        <v>46548</v>
+        <v>46544</v>
       </c>
       <c r="U129" s="20" t="n">
-        <v>46568</v>
+        <v>46562</v>
       </c>
       <c r="V129" s="8" t="n">
         <v>15</v>
@@ -41783,20 +41783,20 @@
         </is>
       </c>
       <c r="R130" s="9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S130" s="19">
         <f>R130/1000</f>
         <v/>
       </c>
       <c r="T130" s="20" t="n">
-        <v>46516</v>
+        <v>46511</v>
       </c>
       <c r="U130" s="20" t="n">
-        <v>46547</v>
+        <v>46541</v>
       </c>
       <c r="V130" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="131">
@@ -41876,17 +41876,17 @@
         </is>
       </c>
       <c r="R131" s="9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S131" s="19">
         <f>R131/1000</f>
         <v/>
       </c>
       <c r="T131" s="20" t="n">
-        <v>46548</v>
+        <v>46544</v>
       </c>
       <c r="U131" s="20" t="n">
-        <v>46568</v>
+        <v>46562</v>
       </c>
       <c r="V131" s="8" t="n">
         <v>15</v>
@@ -41976,10 +41976,10 @@
         <v/>
       </c>
       <c r="T132" s="20" t="n">
-        <v>46855</v>
+        <v>46849</v>
       </c>
       <c r="U132" s="20" t="n">
-        <v>46918</v>
+        <v>46912</v>
       </c>
       <c r="V132" s="8" t="n">
         <v>41</v>
@@ -42069,10 +42069,10 @@
         <v/>
       </c>
       <c r="T133" s="20" t="n">
-        <v>46919</v>
+        <v>46915</v>
       </c>
       <c r="U133" s="20" t="n">
-        <v>46939</v>
+        <v>46933</v>
       </c>
       <c r="V133" s="8" t="n">
         <v>15</v>
@@ -42162,10 +42162,10 @@
         <v/>
       </c>
       <c r="T134" s="20" t="n">
+        <v>46565</v>
+      </c>
+      <c r="U134" s="20" t="n">
         <v>46569</v>
-      </c>
-      <c r="U134" s="20" t="n">
-        <v>46575</v>
       </c>
       <c r="V134" s="8" t="n">
         <v>5</v>
@@ -42255,10 +42255,10 @@
         <v/>
       </c>
       <c r="T135" s="20" t="n">
-        <v>46576</v>
+        <v>46572</v>
       </c>
       <c r="U135" s="20" t="n">
-        <v>46589</v>
+        <v>46583</v>
       </c>
       <c r="V135" s="8" t="n">
         <v>10</v>
@@ -42348,10 +42348,10 @@
         <v/>
       </c>
       <c r="T136" s="20" t="n">
-        <v>46569</v>
+        <v>46565</v>
       </c>
       <c r="U136" s="20" t="n">
-        <v>46681</v>
+        <v>46677</v>
       </c>
       <c r="V136" s="8" t="n">
         <v>80</v>
@@ -42441,10 +42441,10 @@
         <v/>
       </c>
       <c r="T137" s="20" t="n">
-        <v>46569</v>
+        <v>46565</v>
       </c>
       <c r="U137" s="20" t="n">
-        <v>46681</v>
+        <v>46677</v>
       </c>
       <c r="V137" s="8" t="n">
         <v>80</v>
@@ -42534,10 +42534,10 @@
         <v/>
       </c>
       <c r="T138" s="20" t="n">
-        <v>46569</v>
+        <v>46565</v>
       </c>
       <c r="U138" s="20" t="n">
-        <v>46681</v>
+        <v>46677</v>
       </c>
       <c r="V138" s="8" t="n">
         <v>80</v>
@@ -42627,10 +42627,10 @@
         <v/>
       </c>
       <c r="T139" s="20" t="n">
-        <v>46569</v>
+        <v>46565</v>
       </c>
       <c r="U139" s="20" t="n">
-        <v>46681</v>
+        <v>46677</v>
       </c>
       <c r="V139" s="8" t="n">
         <v>80</v>
@@ -42720,10 +42720,10 @@
         <v/>
       </c>
       <c r="T140" s="20" t="n">
-        <v>46684</v>
+        <v>46678</v>
       </c>
       <c r="U140" s="20" t="n">
-        <v>46695</v>
+        <v>46691</v>
       </c>
       <c r="V140" s="8" t="n">
         <v>10</v>
@@ -42813,10 +42813,10 @@
         <v/>
       </c>
       <c r="T141" s="20" t="n">
-        <v>46698</v>
+        <v>46692</v>
       </c>
       <c r="U141" s="20" t="n">
-        <v>46744</v>
+        <v>46740</v>
       </c>
       <c r="V141" s="8" t="n">
         <v>35</v>
@@ -42906,10 +42906,10 @@
         <v/>
       </c>
       <c r="T142" s="20" t="n">
+        <v>46741</v>
+      </c>
+      <c r="U142" s="20" t="n">
         <v>46747</v>
-      </c>
-      <c r="U142" s="20" t="n">
-        <v>46751</v>
       </c>
       <c r="V142" s="8" t="n">
         <v>5</v>
@@ -42999,10 +42999,10 @@
         <v/>
       </c>
       <c r="T143" s="20" t="n">
-        <v>46590</v>
+        <v>46586</v>
       </c>
       <c r="U143" s="20" t="n">
-        <v>46651</v>
+        <v>46645</v>
       </c>
       <c r="V143" s="8" t="n">
         <v>44</v>
@@ -43092,10 +43092,10 @@
         <v/>
       </c>
       <c r="T144" s="20" t="n">
-        <v>46630</v>
+        <v>46624</v>
       </c>
       <c r="U144" s="20" t="n">
-        <v>46679</v>
+        <v>46673</v>
       </c>
       <c r="V144" s="8" t="n">
         <v>35</v>
@@ -43185,10 +43185,10 @@
         <v/>
       </c>
       <c r="T145" s="20" t="n">
-        <v>46754</v>
+        <v>46748</v>
       </c>
       <c r="U145" s="20" t="n">
-        <v>46779</v>
+        <v>46775</v>
       </c>
       <c r="V145" s="8" t="n">
         <v>20</v>
@@ -43278,10 +43278,10 @@
         <v/>
       </c>
       <c r="T146" s="20" t="n">
-        <v>46763</v>
+        <v>46757</v>
       </c>
       <c r="U146" s="20" t="n">
-        <v>46817</v>
+        <v>46811</v>
       </c>
       <c r="V146" s="8" t="n">
         <v>34</v>
@@ -43371,10 +43371,10 @@
         <v/>
       </c>
       <c r="T147" s="20" t="n">
-        <v>46818</v>
+        <v>46812</v>
       </c>
       <c r="U147" s="20" t="n">
-        <v>46854</v>
+        <v>46848</v>
       </c>
       <c r="V147" s="8" t="n">
         <v>27</v>
@@ -43464,10 +43464,10 @@
         <v/>
       </c>
       <c r="T148" s="20" t="n">
-        <v>46782</v>
+        <v>46776</v>
       </c>
       <c r="U148" s="20" t="n">
-        <v>46820</v>
+        <v>46814</v>
       </c>
       <c r="V148" s="8" t="n">
         <v>24</v>
@@ -43557,10 +43557,10 @@
         <v/>
       </c>
       <c r="T149" s="20" t="n">
-        <v>46791</v>
+        <v>46785</v>
       </c>
       <c r="U149" s="20" t="n">
-        <v>46825</v>
+        <v>46819</v>
       </c>
       <c r="V149" s="8" t="n">
         <v>20</v>
@@ -43650,10 +43650,10 @@
         <v/>
       </c>
       <c r="T150" s="20" t="n">
-        <v>46855</v>
+        <v>46849</v>
       </c>
       <c r="U150" s="20" t="n">
-        <v>46868</v>
+        <v>46862</v>
       </c>
       <c r="V150" s="8" t="n">
         <v>10</v>
@@ -43743,10 +43743,10 @@
         <v/>
       </c>
       <c r="T151" s="20" t="n">
-        <v>46869</v>
+        <v>46863</v>
       </c>
       <c r="U151" s="20" t="n">
-        <v>46897</v>
+        <v>46891</v>
       </c>
       <c r="V151" s="8" t="n">
         <v>16</v>
@@ -43836,10 +43836,10 @@
         <v/>
       </c>
       <c r="T152" s="20" t="n">
-        <v>46898</v>
+        <v>46894</v>
       </c>
       <c r="U152" s="20" t="n">
-        <v>46911</v>
+        <v>46905</v>
       </c>
       <c r="V152" s="8" t="n">
         <v>10</v>
@@ -43929,10 +43929,10 @@
         <v/>
       </c>
       <c r="T153" s="20" t="n">
-        <v>46898</v>
+        <v>46894</v>
       </c>
       <c r="U153" s="20" t="n">
-        <v>46939</v>
+        <v>46933</v>
       </c>
       <c r="V153" s="8" t="n">
         <v>30</v>
@@ -44022,13 +44022,13 @@
         <v/>
       </c>
       <c r="T154" s="20" t="n">
-        <v>46940</v>
+        <v>46936</v>
       </c>
       <c r="U154" s="20" t="n">
-        <v>46960</v>
+        <v>46965</v>
       </c>
       <c r="V154" s="8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="155">
@@ -44115,10 +44115,10 @@
         <v/>
       </c>
       <c r="T155" s="20" t="n">
-        <v>46555</v>
+        <v>46551</v>
       </c>
       <c r="U155" s="20" t="n">
-        <v>46566</v>
+        <v>46560</v>
       </c>
       <c r="V155" s="8" t="n">
         <v>8</v>
@@ -44208,10 +44208,10 @@
         <v/>
       </c>
       <c r="T156" s="20" t="n">
-        <v>46567</v>
+        <v>46561</v>
       </c>
       <c r="U156" s="20" t="n">
-        <v>46587</v>
+        <v>46581</v>
       </c>
       <c r="V156" s="8" t="n">
         <v>15</v>
@@ -44294,20 +44294,20 @@
         </is>
       </c>
       <c r="R157" s="9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S157" s="19">
         <f>R157/1000</f>
         <v/>
       </c>
       <c r="T157" s="20" t="n">
-        <v>46567</v>
+        <v>46561</v>
       </c>
       <c r="U157" s="20" t="n">
-        <v>46579</v>
+        <v>46574</v>
       </c>
       <c r="V157" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="158">
@@ -44387,17 +44387,17 @@
         </is>
       </c>
       <c r="R158" s="9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="S158" s="19">
         <f>R158/1000</f>
         <v/>
       </c>
       <c r="T158" s="20" t="n">
-        <v>46580</v>
+        <v>46575</v>
       </c>
       <c r="U158" s="20" t="n">
-        <v>46600</v>
+        <v>46595</v>
       </c>
       <c r="V158" s="8" t="n">
         <v>15</v>
@@ -44487,10 +44487,10 @@
         <v/>
       </c>
       <c r="T159" s="20" t="n">
-        <v>46580</v>
+        <v>46575</v>
       </c>
       <c r="U159" s="20" t="n">
-        <v>46601</v>
+        <v>46596</v>
       </c>
       <c r="V159" s="8" t="n">
         <v>16</v>
@@ -44580,10 +44580,10 @@
         <v/>
       </c>
       <c r="T160" s="20" t="n">
-        <v>46602</v>
+        <v>46597</v>
       </c>
       <c r="U160" s="20" t="n">
-        <v>46622</v>
+        <v>46617</v>
       </c>
       <c r="V160" s="8" t="n">
         <v>15</v>
@@ -44666,20 +44666,20 @@
         </is>
       </c>
       <c r="R161" s="9" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="S161" s="19">
         <f>R161/1000</f>
         <v/>
       </c>
       <c r="T161" s="20" t="n">
-        <v>46602</v>
+        <v>46597</v>
       </c>
       <c r="U161" s="20" t="n">
-        <v>46636</v>
+        <v>46632</v>
       </c>
       <c r="V161" s="8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="162">
@@ -44759,17 +44759,17 @@
         </is>
       </c>
       <c r="R162" s="9" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S162" s="19">
         <f>R162/1000</f>
         <v/>
       </c>
       <c r="T162" s="20" t="n">
-        <v>46637</v>
+        <v>46635</v>
       </c>
       <c r="U162" s="20" t="n">
-        <v>46658</v>
+        <v>46656</v>
       </c>
       <c r="V162" s="8" t="n">
         <v>15</v>
@@ -44859,10 +44859,10 @@
         <v/>
       </c>
       <c r="T163" s="20" t="n">
-        <v>46637</v>
+        <v>46635</v>
       </c>
       <c r="U163" s="20" t="n">
-        <v>46652</v>
+        <v>46650</v>
       </c>
       <c r="V163" s="8" t="n">
         <v>12</v>
@@ -44952,10 +44952,10 @@
         <v/>
       </c>
       <c r="T164" s="20" t="n">
-        <v>46656</v>
+        <v>46651</v>
       </c>
       <c r="U164" s="20" t="n">
-        <v>46674</v>
+        <v>46672</v>
       </c>
       <c r="V164" s="8" t="n">
         <v>15</v>
@@ -45045,10 +45045,10 @@
         <v/>
       </c>
       <c r="T165" s="20" t="n">
-        <v>46615</v>
+        <v>46611</v>
       </c>
       <c r="U165" s="20" t="n">
-        <v>46652</v>
+        <v>46650</v>
       </c>
       <c r="V165" s="8" t="n">
         <v>28</v>
@@ -45138,10 +45138,10 @@
         <v/>
       </c>
       <c r="T166" s="20" t="n">
-        <v>46656</v>
+        <v>46651</v>
       </c>
       <c r="U166" s="20" t="n">
-        <v>46674</v>
+        <v>46672</v>
       </c>
       <c r="V166" s="8" t="n">
         <v>15</v>
@@ -45231,10 +45231,10 @@
         <v/>
       </c>
       <c r="T167" s="20" t="n">
-        <v>46846</v>
+        <v>46842</v>
       </c>
       <c r="U167" s="20" t="n">
-        <v>46889</v>
+        <v>46887</v>
       </c>
       <c r="V167" s="8" t="n">
         <v>27</v>
@@ -45324,10 +45324,10 @@
         <v/>
       </c>
       <c r="T168" s="20" t="n">
-        <v>46890</v>
+        <v>46888</v>
       </c>
       <c r="U168" s="20" t="n">
-        <v>46910</v>
+        <v>46908</v>
       </c>
       <c r="V168" s="8" t="n">
         <v>15</v>
@@ -45417,10 +45417,10 @@
         <v/>
       </c>
       <c r="T169" s="20" t="n">
-        <v>46677</v>
+        <v>46673</v>
       </c>
       <c r="U169" s="20" t="n">
-        <v>46681</v>
+        <v>46679</v>
       </c>
       <c r="V169" s="8" t="n">
         <v>5</v>
@@ -45510,10 +45510,10 @@
         <v/>
       </c>
       <c r="T170" s="20" t="n">
-        <v>46684</v>
+        <v>46680</v>
       </c>
       <c r="U170" s="20" t="n">
-        <v>46695</v>
+        <v>46693</v>
       </c>
       <c r="V170" s="8" t="n">
         <v>10</v>
@@ -45603,10 +45603,10 @@
         <v/>
       </c>
       <c r="T171" s="20" t="n">
-        <v>46677</v>
+        <v>46673</v>
       </c>
       <c r="U171" s="20" t="n">
-        <v>46735</v>
+        <v>46733</v>
       </c>
       <c r="V171" s="8" t="n">
         <v>43</v>
@@ -45696,10 +45696,10 @@
         <v/>
       </c>
       <c r="T172" s="20" t="n">
-        <v>46677</v>
+        <v>46673</v>
       </c>
       <c r="U172" s="20" t="n">
-        <v>46735</v>
+        <v>46733</v>
       </c>
       <c r="V172" s="8" t="n">
         <v>43</v>
@@ -45789,10 +45789,10 @@
         <v/>
       </c>
       <c r="T173" s="20" t="n">
-        <v>46677</v>
+        <v>46673</v>
       </c>
       <c r="U173" s="20" t="n">
-        <v>46735</v>
+        <v>46733</v>
       </c>
       <c r="V173" s="8" t="n">
         <v>43</v>
@@ -45882,10 +45882,10 @@
         <v/>
       </c>
       <c r="T174" s="20" t="n">
-        <v>46677</v>
+        <v>46673</v>
       </c>
       <c r="U174" s="20" t="n">
-        <v>46735</v>
+        <v>46733</v>
       </c>
       <c r="V174" s="8" t="n">
         <v>43</v>
@@ -45975,10 +45975,10 @@
         <v/>
       </c>
       <c r="T175" s="20" t="n">
-        <v>46736</v>
+        <v>46734</v>
       </c>
       <c r="U175" s="20" t="n">
-        <v>46749</v>
+        <v>46747</v>
       </c>
       <c r="V175" s="8" t="n">
         <v>10</v>
@@ -46068,10 +46068,10 @@
         <v/>
       </c>
       <c r="T176" s="20" t="n">
-        <v>46750</v>
+        <v>46748</v>
       </c>
       <c r="U176" s="20" t="n">
-        <v>46777</v>
+        <v>46775</v>
       </c>
       <c r="V176" s="8" t="n">
         <v>20</v>
@@ -46161,10 +46161,10 @@
         <v/>
       </c>
       <c r="T177" s="20" t="n">
-        <v>46778</v>
+        <v>46776</v>
       </c>
       <c r="U177" s="20" t="n">
-        <v>46784</v>
+        <v>46782</v>
       </c>
       <c r="V177" s="8" t="n">
         <v>5</v>
@@ -46254,10 +46254,10 @@
         <v/>
       </c>
       <c r="T178" s="20" t="n">
-        <v>46698</v>
+        <v>46694</v>
       </c>
       <c r="U178" s="20" t="n">
-        <v>46772</v>
+        <v>46770</v>
       </c>
       <c r="V178" s="8" t="n">
         <v>55</v>
@@ -46347,10 +46347,10 @@
         <v/>
       </c>
       <c r="T179" s="20" t="n">
-        <v>46747</v>
+        <v>46743</v>
       </c>
       <c r="U179" s="20" t="n">
-        <v>46812</v>
+        <v>46810</v>
       </c>
       <c r="V179" s="8" t="n">
         <v>43</v>
@@ -46440,10 +46440,10 @@
         <v/>
       </c>
       <c r="T180" s="20" t="n">
-        <v>46785</v>
+        <v>46783</v>
       </c>
       <c r="U180" s="20" t="n">
-        <v>46799</v>
+        <v>46797</v>
       </c>
       <c r="V180" s="8" t="n">
         <v>11</v>
@@ -46533,10 +46533,10 @@
         <v/>
       </c>
       <c r="T181" s="20" t="n">
-        <v>46791</v>
+        <v>46789</v>
       </c>
       <c r="U181" s="20" t="n">
-        <v>46824</v>
+        <v>46820</v>
       </c>
       <c r="V181" s="8" t="n">
         <v>19</v>
@@ -46626,10 +46626,10 @@
         <v/>
       </c>
       <c r="T182" s="20" t="n">
-        <v>46825</v>
+        <v>46821</v>
       </c>
       <c r="U182" s="20" t="n">
-        <v>46845</v>
+        <v>46841</v>
       </c>
       <c r="V182" s="8" t="n">
         <v>15</v>
@@ -46719,10 +46719,10 @@
         <v/>
       </c>
       <c r="T183" s="20" t="n">
-        <v>46800</v>
+        <v>46798</v>
       </c>
       <c r="U183" s="20" t="n">
-        <v>46825</v>
+        <v>46821</v>
       </c>
       <c r="V183" s="8" t="n">
         <v>13</v>
@@ -46812,10 +46812,10 @@
         <v/>
       </c>
       <c r="T184" s="20" t="n">
-        <v>46813</v>
+        <v>46811</v>
       </c>
       <c r="U184" s="20" t="n">
-        <v>46827</v>
+        <v>46825</v>
       </c>
       <c r="V184" s="8" t="n">
         <v>11</v>
@@ -46905,10 +46905,10 @@
         <v/>
       </c>
       <c r="T185" s="20" t="n">
-        <v>46846</v>
+        <v>46842</v>
       </c>
       <c r="U185" s="20" t="n">
-        <v>46852</v>
+        <v>46848</v>
       </c>
       <c r="V185" s="8" t="n">
         <v>5</v>
@@ -46998,10 +46998,10 @@
         <v/>
       </c>
       <c r="T186" s="20" t="n">
-        <v>46853</v>
+        <v>46849</v>
       </c>
       <c r="U186" s="20" t="n">
-        <v>46861</v>
+        <v>46859</v>
       </c>
       <c r="V186" s="8" t="n">
         <v>7</v>
@@ -47091,10 +47091,10 @@
         <v/>
       </c>
       <c r="T187" s="20" t="n">
-        <v>46862</v>
+        <v>46860</v>
       </c>
       <c r="U187" s="20" t="n">
-        <v>46882</v>
+        <v>46880</v>
       </c>
       <c r="V187" s="8" t="n">
         <v>10</v>
@@ -47184,10 +47184,10 @@
         <v/>
       </c>
       <c r="T188" s="20" t="n">
-        <v>46862</v>
+        <v>46860</v>
       </c>
       <c r="U188" s="20" t="n">
-        <v>46910</v>
+        <v>46908</v>
       </c>
       <c r="V188" s="8" t="n">
         <v>30</v>
@@ -47277,13 +47277,13 @@
         <v/>
       </c>
       <c r="T189" s="20" t="n">
-        <v>46911</v>
+        <v>46909</v>
       </c>
       <c r="U189" s="20" t="n">
-        <v>46931</v>
+        <v>46938</v>
       </c>
       <c r="V189" s="8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="190">
@@ -47370,10 +47370,10 @@
         <v/>
       </c>
       <c r="T190" s="20" t="n">
-        <v>46609</v>
+        <v>46603</v>
       </c>
       <c r="U190" s="20" t="n">
-        <v>46618</v>
+        <v>46614</v>
       </c>
       <c r="V190" s="8" t="n">
         <v>8</v>
@@ -47463,10 +47463,10 @@
         <v/>
       </c>
       <c r="T191" s="20" t="n">
-        <v>46621</v>
+        <v>46615</v>
       </c>
       <c r="U191" s="20" t="n">
-        <v>46639</v>
+        <v>46635</v>
       </c>
       <c r="V191" s="8" t="n">
         <v>15</v>
@@ -47549,20 +47549,20 @@
         </is>
       </c>
       <c r="R192" s="9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S192" s="19">
         <f>R192/1000</f>
         <v/>
       </c>
       <c r="T192" s="20" t="n">
-        <v>46621</v>
+        <v>46615</v>
       </c>
       <c r="U192" s="20" t="n">
-        <v>46632</v>
+        <v>46625</v>
       </c>
       <c r="V192" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="193">
@@ -47642,17 +47642,17 @@
         </is>
       </c>
       <c r="R193" s="9" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S193" s="19">
         <f>R193/1000</f>
         <v/>
       </c>
       <c r="T193" s="20" t="n">
-        <v>46635</v>
+        <v>46628</v>
       </c>
       <c r="U193" s="20" t="n">
-        <v>46656</v>
+        <v>46646</v>
       </c>
       <c r="V193" s="8" t="n">
         <v>15</v>
@@ -47742,10 +47742,10 @@
         <v/>
       </c>
       <c r="T194" s="20" t="n">
-        <v>46635</v>
+        <v>46628</v>
       </c>
       <c r="U194" s="20" t="n">
-        <v>46657</v>
+        <v>46649</v>
       </c>
       <c r="V194" s="8" t="n">
         <v>16</v>
@@ -47835,10 +47835,10 @@
         <v/>
       </c>
       <c r="T195" s="20" t="n">
-        <v>46658</v>
+        <v>46650</v>
       </c>
       <c r="U195" s="20" t="n">
-        <v>46678</v>
+        <v>46671</v>
       </c>
       <c r="V195" s="8" t="n">
         <v>15</v>
@@ -47921,20 +47921,20 @@
         </is>
       </c>
       <c r="R196" s="9" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="S196" s="19">
         <f>R196/1000</f>
         <v/>
       </c>
       <c r="T196" s="20" t="n">
-        <v>46658</v>
+        <v>46650</v>
       </c>
       <c r="U196" s="20" t="n">
-        <v>46693</v>
+        <v>46685</v>
       </c>
       <c r="V196" s="8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="197">
@@ -48014,17 +48014,17 @@
         </is>
       </c>
       <c r="R197" s="9" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="S197" s="19">
         <f>R197/1000</f>
         <v/>
       </c>
       <c r="T197" s="20" t="n">
-        <v>46694</v>
+        <v>46686</v>
       </c>
       <c r="U197" s="20" t="n">
-        <v>46714</v>
+        <v>46706</v>
       </c>
       <c r="V197" s="8" t="n">
         <v>15</v>
@@ -48107,20 +48107,20 @@
         </is>
       </c>
       <c r="R198" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S198" s="19">
         <f>R198/1000</f>
         <v/>
       </c>
       <c r="T198" s="20" t="n">
-        <v>46694</v>
+        <v>46686</v>
       </c>
       <c r="U198" s="20" t="n">
-        <v>46709</v>
+        <v>46702</v>
       </c>
       <c r="V198" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="199">
@@ -48200,17 +48200,17 @@
         </is>
       </c>
       <c r="R199" s="9" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="S199" s="19">
         <f>R199/1000</f>
         <v/>
       </c>
       <c r="T199" s="20" t="n">
-        <v>46712</v>
+        <v>46705</v>
       </c>
       <c r="U199" s="20" t="n">
-        <v>46730</v>
+        <v>46723</v>
       </c>
       <c r="V199" s="8" t="n">
         <v>15</v>
@@ -48300,13 +48300,13 @@
         <v/>
       </c>
       <c r="T200" s="20" t="n">
-        <v>46672</v>
+        <v>46664</v>
       </c>
       <c r="U200" s="20" t="n">
-        <v>46709</v>
+        <v>46702</v>
       </c>
       <c r="V200" s="8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="201">
@@ -48393,10 +48393,10 @@
         <v/>
       </c>
       <c r="T201" s="20" t="n">
-        <v>46712</v>
+        <v>46705</v>
       </c>
       <c r="U201" s="20" t="n">
-        <v>46730</v>
+        <v>46723</v>
       </c>
       <c r="V201" s="8" t="n">
         <v>15</v>
@@ -48486,10 +48486,10 @@
         <v/>
       </c>
       <c r="T202" s="20" t="n">
-        <v>46925</v>
+        <v>46918</v>
       </c>
       <c r="U202" s="20" t="n">
-        <v>46964</v>
+        <v>46957</v>
       </c>
       <c r="V202" s="8" t="n">
         <v>28</v>
@@ -48579,10 +48579,10 @@
         <v/>
       </c>
       <c r="T203" s="20" t="n">
-        <v>46965</v>
+        <v>46958</v>
       </c>
       <c r="U203" s="20" t="n">
-        <v>46985</v>
+        <v>46978</v>
       </c>
       <c r="V203" s="8" t="n">
         <v>15</v>
@@ -48672,10 +48672,10 @@
         <v/>
       </c>
       <c r="T204" s="20" t="n">
-        <v>46733</v>
+        <v>46726</v>
       </c>
       <c r="U204" s="20" t="n">
-        <v>46737</v>
+        <v>46730</v>
       </c>
       <c r="V204" s="8" t="n">
         <v>5</v>
@@ -48765,10 +48765,10 @@
         <v/>
       </c>
       <c r="T205" s="20" t="n">
-        <v>46740</v>
+        <v>46733</v>
       </c>
       <c r="U205" s="20" t="n">
-        <v>46751</v>
+        <v>46744</v>
       </c>
       <c r="V205" s="8" t="n">
         <v>10</v>
@@ -48858,10 +48858,10 @@
         <v/>
       </c>
       <c r="T206" s="20" t="n">
-        <v>46733</v>
+        <v>46726</v>
       </c>
       <c r="U206" s="20" t="n">
-        <v>46797</v>
+        <v>46790</v>
       </c>
       <c r="V206" s="8" t="n">
         <v>47</v>
@@ -48951,10 +48951,10 @@
         <v/>
       </c>
       <c r="T207" s="20" t="n">
-        <v>46733</v>
+        <v>46726</v>
       </c>
       <c r="U207" s="20" t="n">
-        <v>46797</v>
+        <v>46790</v>
       </c>
       <c r="V207" s="8" t="n">
         <v>47</v>
@@ -49044,10 +49044,10 @@
         <v/>
       </c>
       <c r="T208" s="20" t="n">
-        <v>46733</v>
+        <v>46726</v>
       </c>
       <c r="U208" s="20" t="n">
-        <v>46797</v>
+        <v>46790</v>
       </c>
       <c r="V208" s="8" t="n">
         <v>47</v>
@@ -49137,10 +49137,10 @@
         <v/>
       </c>
       <c r="T209" s="20" t="n">
-        <v>46733</v>
+        <v>46726</v>
       </c>
       <c r="U209" s="20" t="n">
-        <v>46797</v>
+        <v>46790</v>
       </c>
       <c r="V209" s="8" t="n">
         <v>47</v>
@@ -49230,10 +49230,10 @@
         <v/>
       </c>
       <c r="T210" s="20" t="n">
-        <v>46798</v>
+        <v>46791</v>
       </c>
       <c r="U210" s="20" t="n">
-        <v>46818</v>
+        <v>46811</v>
       </c>
       <c r="V210" s="8" t="n">
         <v>10</v>
@@ -49323,10 +49323,10 @@
         <v/>
       </c>
       <c r="T211" s="20" t="n">
-        <v>46819</v>
+        <v>46812</v>
       </c>
       <c r="U211" s="20" t="n">
-        <v>46848</v>
+        <v>46841</v>
       </c>
       <c r="V211" s="8" t="n">
         <v>22</v>
@@ -49416,10 +49416,10 @@
         <v/>
       </c>
       <c r="T212" s="20" t="n">
-        <v>46849</v>
+        <v>46842</v>
       </c>
       <c r="U212" s="20" t="n">
-        <v>46855</v>
+        <v>46848</v>
       </c>
       <c r="V212" s="8" t="n">
         <v>5</v>
@@ -49509,10 +49509,10 @@
         <v/>
       </c>
       <c r="T213" s="20" t="n">
-        <v>46754</v>
+        <v>46747</v>
       </c>
       <c r="U213" s="20" t="n">
-        <v>46839</v>
+        <v>46832</v>
       </c>
       <c r="V213" s="8" t="n">
         <v>57</v>
@@ -49602,10 +49602,10 @@
         <v/>
       </c>
       <c r="T214" s="20" t="n">
-        <v>46812</v>
+        <v>46798</v>
       </c>
       <c r="U214" s="20" t="n">
-        <v>46881</v>
+        <v>46867</v>
       </c>
       <c r="V214" s="8" t="n">
         <v>45</v>
@@ -49695,10 +49695,10 @@
         <v/>
       </c>
       <c r="T215" s="20" t="n">
-        <v>46856</v>
+        <v>46849</v>
       </c>
       <c r="U215" s="20" t="n">
-        <v>46881</v>
+        <v>46867</v>
       </c>
       <c r="V215" s="8" t="n">
         <v>13</v>
@@ -49788,10 +49788,10 @@
         <v/>
       </c>
       <c r="T216" s="20" t="n">
-        <v>46862</v>
+        <v>46855</v>
       </c>
       <c r="U216" s="20" t="n">
-        <v>46898</v>
+        <v>46891</v>
       </c>
       <c r="V216" s="8" t="n">
         <v>22</v>
@@ -49881,10 +49881,10 @@
         <v/>
       </c>
       <c r="T217" s="20" t="n">
-        <v>46901</v>
+        <v>46894</v>
       </c>
       <c r="U217" s="20" t="n">
-        <v>46924</v>
+        <v>46917</v>
       </c>
       <c r="V217" s="8" t="n">
         <v>18</v>
@@ -49974,10 +49974,10 @@
         <v/>
       </c>
       <c r="T218" s="20" t="n">
-        <v>46882</v>
+        <v>46868</v>
       </c>
       <c r="U218" s="20" t="n">
-        <v>46902</v>
+        <v>46895</v>
       </c>
       <c r="V218" s="8" t="n">
         <v>15</v>
@@ -50067,10 +50067,10 @@
         <v/>
       </c>
       <c r="T219" s="20" t="n">
-        <v>46888</v>
+        <v>46881</v>
       </c>
       <c r="U219" s="20" t="n">
-        <v>46904</v>
+        <v>46897</v>
       </c>
       <c r="V219" s="8" t="n">
         <v>13</v>
@@ -50160,10 +50160,10 @@
         <v/>
       </c>
       <c r="T220" s="20" t="n">
-        <v>46925</v>
+        <v>46918</v>
       </c>
       <c r="U220" s="20" t="n">
-        <v>46931</v>
+        <v>46924</v>
       </c>
       <c r="V220" s="8" t="n">
         <v>5</v>
@@ -50253,10 +50253,10 @@
         <v/>
       </c>
       <c r="T221" s="20" t="n">
-        <v>46932</v>
+        <v>46925</v>
       </c>
       <c r="U221" s="20" t="n">
-        <v>46943</v>
+        <v>46936</v>
       </c>
       <c r="V221" s="8" t="n">
         <v>8</v>
@@ -50346,10 +50346,10 @@
         <v/>
       </c>
       <c r="T222" s="20" t="n">
-        <v>46944</v>
+        <v>46937</v>
       </c>
       <c r="U222" s="20" t="n">
-        <v>46957</v>
+        <v>46950</v>
       </c>
       <c r="V222" s="8" t="n">
         <v>10</v>
@@ -50439,10 +50439,10 @@
         <v/>
       </c>
       <c r="T223" s="20" t="n">
-        <v>46944</v>
+        <v>46937</v>
       </c>
       <c r="U223" s="20" t="n">
-        <v>46985</v>
+        <v>46978</v>
       </c>
       <c r="V223" s="8" t="n">
         <v>30</v>
@@ -50532,13 +50532,13 @@
         <v/>
       </c>
       <c r="T224" s="20" t="n">
-        <v>46986</v>
+        <v>46979</v>
       </c>
       <c r="U224" s="20" t="n">
-        <v>47006</v>
+        <v>47008</v>
       </c>
       <c r="V224" s="8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="225">
@@ -50625,10 +50625,10 @@
         <v/>
       </c>
       <c r="T225" s="20" t="n">
-        <v>46609</v>
+        <v>46603</v>
       </c>
       <c r="U225" s="20" t="n">
-        <v>46618</v>
+        <v>46614</v>
       </c>
       <c r="V225" s="8" t="n">
         <v>8</v>
@@ -50718,10 +50718,10 @@
         <v/>
       </c>
       <c r="T226" s="20" t="n">
-        <v>46621</v>
+        <v>46615</v>
       </c>
       <c r="U226" s="20" t="n">
-        <v>46639</v>
+        <v>46635</v>
       </c>
       <c r="V226" s="8" t="n">
         <v>15</v>
@@ -50804,20 +50804,20 @@
         </is>
       </c>
       <c r="R227" s="9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="S227" s="19">
         <f>R227/1000</f>
         <v/>
       </c>
       <c r="T227" s="20" t="n">
-        <v>46621</v>
+        <v>46615</v>
       </c>
       <c r="U227" s="20" t="n">
-        <v>46632</v>
+        <v>46625</v>
       </c>
       <c r="V227" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="228">
@@ -50897,17 +50897,17 @@
         </is>
       </c>
       <c r="R228" s="9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S228" s="19">
         <f>R228/1000</f>
         <v/>
       </c>
       <c r="T228" s="20" t="n">
-        <v>46635</v>
+        <v>46628</v>
       </c>
       <c r="U228" s="20" t="n">
-        <v>46656</v>
+        <v>46646</v>
       </c>
       <c r="V228" s="8" t="n">
         <v>15</v>
@@ -50997,10 +50997,10 @@
         <v/>
       </c>
       <c r="T229" s="20" t="n">
-        <v>46635</v>
+        <v>46628</v>
       </c>
       <c r="U229" s="20" t="n">
-        <v>46657</v>
+        <v>46649</v>
       </c>
       <c r="V229" s="8" t="n">
         <v>16</v>
@@ -51090,10 +51090,10 @@
         <v/>
       </c>
       <c r="T230" s="20" t="n">
-        <v>46658</v>
+        <v>46650</v>
       </c>
       <c r="U230" s="20" t="n">
-        <v>46678</v>
+        <v>46671</v>
       </c>
       <c r="V230" s="8" t="n">
         <v>15</v>
@@ -51176,20 +51176,20 @@
         </is>
       </c>
       <c r="R231" s="9" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S231" s="19">
         <f>R231/1000</f>
         <v/>
       </c>
       <c r="T231" s="20" t="n">
-        <v>46658</v>
+        <v>46650</v>
       </c>
       <c r="U231" s="20" t="n">
-        <v>46693</v>
+        <v>46685</v>
       </c>
       <c r="V231" s="8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="232">
@@ -51269,17 +51269,17 @@
         </is>
       </c>
       <c r="R232" s="9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S232" s="19">
         <f>R232/1000</f>
         <v/>
       </c>
       <c r="T232" s="20" t="n">
-        <v>46694</v>
+        <v>46686</v>
       </c>
       <c r="U232" s="20" t="n">
-        <v>46714</v>
+        <v>46706</v>
       </c>
       <c r="V232" s="8" t="n">
         <v>15</v>
@@ -51362,20 +51362,20 @@
         </is>
       </c>
       <c r="R233" s="9" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="S233" s="19">
         <f>R233/1000</f>
         <v/>
       </c>
       <c r="T233" s="20" t="n">
-        <v>46694</v>
+        <v>46686</v>
       </c>
       <c r="U233" s="20" t="n">
-        <v>46709</v>
+        <v>46702</v>
       </c>
       <c r="V233" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="234">
@@ -51455,17 +51455,17 @@
         </is>
       </c>
       <c r="R234" s="9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S234" s="19">
         <f>R234/1000</f>
         <v/>
       </c>
       <c r="T234" s="20" t="n">
-        <v>46712</v>
+        <v>46705</v>
       </c>
       <c r="U234" s="20" t="n">
-        <v>46730</v>
+        <v>46723</v>
       </c>
       <c r="V234" s="8" t="n">
         <v>15</v>
@@ -51555,13 +51555,13 @@
         <v/>
       </c>
       <c r="T235" s="20" t="n">
-        <v>46672</v>
+        <v>46664</v>
       </c>
       <c r="U235" s="20" t="n">
-        <v>46709</v>
+        <v>46702</v>
       </c>
       <c r="V235" s="8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="236">
@@ -51648,10 +51648,10 @@
         <v/>
       </c>
       <c r="T236" s="20" t="n">
-        <v>46712</v>
+        <v>46705</v>
       </c>
       <c r="U236" s="20" t="n">
-        <v>46730</v>
+        <v>46723</v>
       </c>
       <c r="V236" s="8" t="n">
         <v>15</v>
@@ -51741,10 +51741,10 @@
         <v/>
       </c>
       <c r="T237" s="20" t="n">
-        <v>46903</v>
+        <v>46896</v>
       </c>
       <c r="U237" s="20" t="n">
-        <v>46939</v>
+        <v>46932</v>
       </c>
       <c r="V237" s="8" t="n">
         <v>27</v>
@@ -51834,10 +51834,10 @@
         <v/>
       </c>
       <c r="T238" s="20" t="n">
-        <v>46940</v>
+        <v>46933</v>
       </c>
       <c r="U238" s="20" t="n">
-        <v>46960</v>
+        <v>46953</v>
       </c>
       <c r="V238" s="8" t="n">
         <v>15</v>
@@ -51927,10 +51927,10 @@
         <v/>
       </c>
       <c r="T239" s="20" t="n">
-        <v>46733</v>
+        <v>46726</v>
       </c>
       <c r="U239" s="20" t="n">
-        <v>46737</v>
+        <v>46730</v>
       </c>
       <c r="V239" s="8" t="n">
         <v>5</v>
@@ -52020,10 +52020,10 @@
         <v/>
       </c>
       <c r="T240" s="20" t="n">
-        <v>46740</v>
+        <v>46733</v>
       </c>
       <c r="U240" s="20" t="n">
-        <v>46751</v>
+        <v>46744</v>
       </c>
       <c r="V240" s="8" t="n">
         <v>10</v>
@@ -52113,10 +52113,10 @@
         <v/>
       </c>
       <c r="T241" s="20" t="n">
-        <v>46733</v>
+        <v>46726</v>
       </c>
       <c r="U241" s="20" t="n">
-        <v>46789</v>
+        <v>46782</v>
       </c>
       <c r="V241" s="8" t="n">
         <v>41</v>
@@ -52206,10 +52206,10 @@
         <v/>
       </c>
       <c r="T242" s="20" t="n">
-        <v>46733</v>
+        <v>46726</v>
       </c>
       <c r="U242" s="20" t="n">
-        <v>46789</v>
+        <v>46782</v>
       </c>
       <c r="V242" s="8" t="n">
         <v>41</v>
@@ -52299,10 +52299,10 @@
         <v/>
       </c>
       <c r="T243" s="20" t="n">
-        <v>46733</v>
+        <v>46726</v>
       </c>
       <c r="U243" s="20" t="n">
-        <v>46789</v>
+        <v>46782</v>
       </c>
       <c r="V243" s="8" t="n">
         <v>41</v>
@@ -52392,10 +52392,10 @@
         <v/>
       </c>
       <c r="T244" s="20" t="n">
-        <v>46733</v>
+        <v>46726</v>
       </c>
       <c r="U244" s="20" t="n">
-        <v>46789</v>
+        <v>46782</v>
       </c>
       <c r="V244" s="8" t="n">
         <v>41</v>
@@ -52485,10 +52485,10 @@
         <v/>
       </c>
       <c r="T245" s="20" t="n">
-        <v>46790</v>
+        <v>46783</v>
       </c>
       <c r="U245" s="20" t="n">
-        <v>46810</v>
+        <v>46796</v>
       </c>
       <c r="V245" s="8" t="n">
         <v>10</v>
@@ -52578,10 +52578,10 @@
         <v/>
       </c>
       <c r="T246" s="20" t="n">
-        <v>46811</v>
+        <v>46797</v>
       </c>
       <c r="U246" s="20" t="n">
-        <v>46838</v>
+        <v>46831</v>
       </c>
       <c r="V246" s="8" t="n">
         <v>20</v>
@@ -52671,10 +52671,10 @@
         <v/>
       </c>
       <c r="T247" s="20" t="n">
-        <v>46839</v>
+        <v>46832</v>
       </c>
       <c r="U247" s="20" t="n">
-        <v>46845</v>
+        <v>46838</v>
       </c>
       <c r="V247" s="8" t="n">
         <v>5</v>
@@ -52764,10 +52764,10 @@
         <v/>
       </c>
       <c r="T248" s="20" t="n">
-        <v>46754</v>
+        <v>46747</v>
       </c>
       <c r="U248" s="20" t="n">
-        <v>46833</v>
+        <v>46826</v>
       </c>
       <c r="V248" s="8" t="n">
         <v>53</v>
@@ -52857,10 +52857,10 @@
         <v/>
       </c>
       <c r="T249" s="20" t="n">
-        <v>46800</v>
+        <v>46793</v>
       </c>
       <c r="U249" s="20" t="n">
-        <v>46863</v>
+        <v>46856</v>
       </c>
       <c r="V249" s="8" t="n">
         <v>41</v>
@@ -52950,10 +52950,10 @@
         <v/>
       </c>
       <c r="T250" s="20" t="n">
-        <v>46846</v>
+        <v>46839</v>
       </c>
       <c r="U250" s="20" t="n">
-        <v>46860</v>
+        <v>46853</v>
       </c>
       <c r="V250" s="8" t="n">
         <v>11</v>
@@ -53043,10 +53043,10 @@
         <v/>
       </c>
       <c r="T251" s="20" t="n">
-        <v>46852</v>
+        <v>46845</v>
       </c>
       <c r="U251" s="20" t="n">
-        <v>46882</v>
+        <v>46868</v>
       </c>
       <c r="V251" s="8" t="n">
         <v>18</v>
@@ -53136,10 +53136,10 @@
         <v/>
       </c>
       <c r="T252" s="20" t="n">
-        <v>46883</v>
+        <v>46869</v>
       </c>
       <c r="U252" s="20" t="n">
-        <v>46902</v>
+        <v>46895</v>
       </c>
       <c r="V252" s="8" t="n">
         <v>14</v>
@@ -53229,10 +53229,10 @@
         <v/>
       </c>
       <c r="T253" s="20" t="n">
-        <v>46861</v>
+        <v>46854</v>
       </c>
       <c r="U253" s="20" t="n">
-        <v>46883</v>
+        <v>46869</v>
       </c>
       <c r="V253" s="8" t="n">
         <v>12</v>
@@ -53322,10 +53322,10 @@
         <v/>
       </c>
       <c r="T254" s="20" t="n">
-        <v>46867</v>
+        <v>46860</v>
       </c>
       <c r="U254" s="20" t="n">
-        <v>46888</v>
+        <v>46881</v>
       </c>
       <c r="V254" s="8" t="n">
         <v>11</v>
@@ -53415,10 +53415,10 @@
         <v/>
       </c>
       <c r="T255" s="20" t="n">
-        <v>46903</v>
+        <v>46896</v>
       </c>
       <c r="U255" s="20" t="n">
-        <v>46909</v>
+        <v>46902</v>
       </c>
       <c r="V255" s="8" t="n">
         <v>5</v>
@@ -53508,10 +53508,10 @@
         <v/>
       </c>
       <c r="T256" s="20" t="n">
-        <v>46910</v>
+        <v>46903</v>
       </c>
       <c r="U256" s="20" t="n">
-        <v>46918</v>
+        <v>46911</v>
       </c>
       <c r="V256" s="8" t="n">
         <v>7</v>
@@ -53601,10 +53601,10 @@
         <v/>
       </c>
       <c r="T257" s="20" t="n">
-        <v>46919</v>
+        <v>46912</v>
       </c>
       <c r="U257" s="20" t="n">
-        <v>46932</v>
+        <v>46925</v>
       </c>
       <c r="V257" s="8" t="n">
         <v>10</v>
@@ -53694,10 +53694,10 @@
         <v/>
       </c>
       <c r="T258" s="20" t="n">
-        <v>46919</v>
+        <v>46912</v>
       </c>
       <c r="U258" s="20" t="n">
-        <v>46960</v>
+        <v>46953</v>
       </c>
       <c r="V258" s="8" t="n">
         <v>30</v>
@@ -53787,13 +53787,13 @@
         <v/>
       </c>
       <c r="T259" s="20" t="n">
-        <v>46961</v>
+        <v>46954</v>
       </c>
       <c r="U259" s="20" t="n">
-        <v>46981</v>
+        <v>46985</v>
       </c>
       <c r="V259" s="8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="260">
@@ -53880,10 +53880,10 @@
         <v/>
       </c>
       <c r="T260" s="20" t="n">
-        <v>46658</v>
+        <v>46650</v>
       </c>
       <c r="U260" s="20" t="n">
-        <v>46667</v>
+        <v>46660</v>
       </c>
       <c r="V260" s="8" t="n">
         <v>8</v>
@@ -53973,10 +53973,10 @@
         <v/>
       </c>
       <c r="T261" s="20" t="n">
-        <v>46670</v>
+        <v>46663</v>
       </c>
       <c r="U261" s="20" t="n">
-        <v>46688</v>
+        <v>46681</v>
       </c>
       <c r="V261" s="8" t="n">
         <v>15</v>
@@ -54066,10 +54066,10 @@
         <v/>
       </c>
       <c r="T262" s="20" t="n">
-        <v>46670</v>
+        <v>46663</v>
       </c>
       <c r="U262" s="20" t="n">
-        <v>46681</v>
+        <v>46674</v>
       </c>
       <c r="V262" s="8" t="n">
         <v>10</v>
@@ -54159,10 +54159,10 @@
         <v/>
       </c>
       <c r="T263" s="20" t="n">
-        <v>46684</v>
+        <v>46677</v>
       </c>
       <c r="U263" s="20" t="n">
-        <v>46702</v>
+        <v>46695</v>
       </c>
       <c r="V263" s="8" t="n">
         <v>15</v>
@@ -54252,10 +54252,10 @@
         <v/>
       </c>
       <c r="T264" s="20" t="n">
-        <v>46684</v>
+        <v>46677</v>
       </c>
       <c r="U264" s="20" t="n">
-        <v>46705</v>
+        <v>46698</v>
       </c>
       <c r="V264" s="8" t="n">
         <v>16</v>
@@ -54345,10 +54345,10 @@
         <v/>
       </c>
       <c r="T265" s="20" t="n">
-        <v>46706</v>
+        <v>46699</v>
       </c>
       <c r="U265" s="20" t="n">
-        <v>46726</v>
+        <v>46719</v>
       </c>
       <c r="V265" s="8" t="n">
         <v>15</v>
@@ -54438,10 +54438,10 @@
         <v/>
       </c>
       <c r="T266" s="20" t="n">
-        <v>46706</v>
+        <v>46699</v>
       </c>
       <c r="U266" s="20" t="n">
-        <v>46741</v>
+        <v>46734</v>
       </c>
       <c r="V266" s="8" t="n">
         <v>26</v>
@@ -54531,10 +54531,10 @@
         <v/>
       </c>
       <c r="T267" s="20" t="n">
-        <v>46742</v>
+        <v>46735</v>
       </c>
       <c r="U267" s="20" t="n">
-        <v>46762</v>
+        <v>46755</v>
       </c>
       <c r="V267" s="8" t="n">
         <v>15</v>
@@ -54617,20 +54617,20 @@
         </is>
       </c>
       <c r="R268" s="9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S268" s="19">
         <f>R268/1000</f>
         <v/>
       </c>
       <c r="T268" s="20" t="n">
-        <v>46742</v>
+        <v>46735</v>
       </c>
       <c r="U268" s="20" t="n">
-        <v>46758</v>
+        <v>46750</v>
       </c>
       <c r="V268" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="269">
@@ -54710,17 +54710,17 @@
         </is>
       </c>
       <c r="R269" s="9" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="S269" s="19">
         <f>R269/1000</f>
         <v/>
       </c>
       <c r="T269" s="20" t="n">
-        <v>46761</v>
+        <v>46751</v>
       </c>
       <c r="U269" s="20" t="n">
-        <v>46779</v>
+        <v>46771</v>
       </c>
       <c r="V269" s="8" t="n">
         <v>15</v>
@@ -54810,13 +54810,13 @@
         <v/>
       </c>
       <c r="T270" s="20" t="n">
-        <v>46720</v>
+        <v>46713</v>
       </c>
       <c r="U270" s="20" t="n">
-        <v>46758</v>
+        <v>46750</v>
       </c>
       <c r="V270" s="8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="271">
@@ -54903,10 +54903,10 @@
         <v/>
       </c>
       <c r="T271" s="20" t="n">
-        <v>46761</v>
+        <v>46751</v>
       </c>
       <c r="U271" s="20" t="n">
-        <v>46779</v>
+        <v>46771</v>
       </c>
       <c r="V271" s="8" t="n">
         <v>15</v>
@@ -54996,10 +54996,10 @@
         <v/>
       </c>
       <c r="T272" s="20" t="n">
-        <v>46974</v>
+        <v>46966</v>
       </c>
       <c r="U272" s="20" t="n">
-        <v>47013</v>
+        <v>47003</v>
       </c>
       <c r="V272" s="8" t="n">
         <v>28</v>
@@ -55089,10 +55089,10 @@
         <v/>
       </c>
       <c r="T273" s="20" t="n">
-        <v>47014</v>
+        <v>47006</v>
       </c>
       <c r="U273" s="20" t="n">
-        <v>47034</v>
+        <v>47024</v>
       </c>
       <c r="V273" s="8" t="n">
         <v>15</v>
@@ -55182,10 +55182,10 @@
         <v/>
       </c>
       <c r="T274" s="20" t="n">
-        <v>46782</v>
+        <v>46772</v>
       </c>
       <c r="U274" s="20" t="n">
-        <v>46786</v>
+        <v>46778</v>
       </c>
       <c r="V274" s="8" t="n">
         <v>5</v>
@@ -55275,10 +55275,10 @@
         <v/>
       </c>
       <c r="T275" s="20" t="n">
-        <v>46789</v>
+        <v>46779</v>
       </c>
       <c r="U275" s="20" t="n">
-        <v>46800</v>
+        <v>46792</v>
       </c>
       <c r="V275" s="8" t="n">
         <v>10</v>
@@ -55368,10 +55368,10 @@
         <v/>
       </c>
       <c r="T276" s="20" t="n">
-        <v>46782</v>
+        <v>46772</v>
       </c>
       <c r="U276" s="20" t="n">
-        <v>46853</v>
+        <v>46845</v>
       </c>
       <c r="V276" s="8" t="n">
         <v>47</v>
@@ -55461,10 +55461,10 @@
         <v/>
       </c>
       <c r="T277" s="20" t="n">
-        <v>46782</v>
+        <v>46772</v>
       </c>
       <c r="U277" s="20" t="n">
-        <v>46853</v>
+        <v>46845</v>
       </c>
       <c r="V277" s="8" t="n">
         <v>47</v>
@@ -55554,10 +55554,10 @@
         <v/>
       </c>
       <c r="T278" s="20" t="n">
-        <v>46782</v>
+        <v>46772</v>
       </c>
       <c r="U278" s="20" t="n">
-        <v>46853</v>
+        <v>46845</v>
       </c>
       <c r="V278" s="8" t="n">
         <v>47</v>
@@ -55647,10 +55647,10 @@
         <v/>
       </c>
       <c r="T279" s="20" t="n">
-        <v>46782</v>
+        <v>46772</v>
       </c>
       <c r="U279" s="20" t="n">
-        <v>46853</v>
+        <v>46845</v>
       </c>
       <c r="V279" s="8" t="n">
         <v>47</v>
@@ -55740,10 +55740,10 @@
         <v/>
       </c>
       <c r="T280" s="20" t="n">
-        <v>46854</v>
+        <v>46846</v>
       </c>
       <c r="U280" s="20" t="n">
-        <v>46867</v>
+        <v>46859</v>
       </c>
       <c r="V280" s="8" t="n">
         <v>10</v>
@@ -55833,10 +55833,10 @@
         <v/>
       </c>
       <c r="T281" s="20" t="n">
-        <v>46868</v>
+        <v>46860</v>
       </c>
       <c r="U281" s="20" t="n">
-        <v>46904</v>
+        <v>46896</v>
       </c>
       <c r="V281" s="8" t="n">
         <v>22</v>
@@ -55926,10 +55926,10 @@
         <v/>
       </c>
       <c r="T282" s="20" t="n">
-        <v>46905</v>
+        <v>46897</v>
       </c>
       <c r="U282" s="20" t="n">
-        <v>46911</v>
+        <v>46903</v>
       </c>
       <c r="V282" s="8" t="n">
         <v>5</v>
@@ -56019,10 +56019,10 @@
         <v/>
       </c>
       <c r="T283" s="20" t="n">
-        <v>46810</v>
+        <v>46793</v>
       </c>
       <c r="U283" s="20" t="n">
-        <v>46895</v>
+        <v>46887</v>
       </c>
       <c r="V283" s="8" t="n">
         <v>57</v>
@@ -56112,10 +56112,10 @@
         <v/>
       </c>
       <c r="T284" s="20" t="n">
-        <v>46861</v>
+        <v>46853</v>
       </c>
       <c r="U284" s="20" t="n">
-        <v>46930</v>
+        <v>46922</v>
       </c>
       <c r="V284" s="8" t="n">
         <v>45</v>
@@ -56205,10 +56205,10 @@
         <v/>
       </c>
       <c r="T285" s="20" t="n">
-        <v>46912</v>
+        <v>46904</v>
       </c>
       <c r="U285" s="20" t="n">
-        <v>46930</v>
+        <v>46922</v>
       </c>
       <c r="V285" s="8" t="n">
         <v>13</v>
@@ -56298,10 +56298,10 @@
         <v/>
       </c>
       <c r="T286" s="20" t="n">
-        <v>46918</v>
+        <v>46910</v>
       </c>
       <c r="U286" s="20" t="n">
-        <v>46947</v>
+        <v>46939</v>
       </c>
       <c r="V286" s="8" t="n">
         <v>22</v>
@@ -56391,10 +56391,10 @@
         <v/>
       </c>
       <c r="T287" s="20" t="n">
-        <v>46950</v>
+        <v>46940</v>
       </c>
       <c r="U287" s="20" t="n">
-        <v>46973</v>
+        <v>46965</v>
       </c>
       <c r="V287" s="8" t="n">
         <v>18</v>
@@ -56484,10 +56484,10 @@
         <v/>
       </c>
       <c r="T288" s="20" t="n">
-        <v>46931</v>
+        <v>46923</v>
       </c>
       <c r="U288" s="20" t="n">
-        <v>46951</v>
+        <v>46943</v>
       </c>
       <c r="V288" s="8" t="n">
         <v>15</v>
@@ -56577,10 +56577,10 @@
         <v/>
       </c>
       <c r="T289" s="20" t="n">
-        <v>46937</v>
+        <v>46929</v>
       </c>
       <c r="U289" s="20" t="n">
-        <v>46953</v>
+        <v>46945</v>
       </c>
       <c r="V289" s="8" t="n">
         <v>13</v>
@@ -56670,10 +56670,10 @@
         <v/>
       </c>
       <c r="T290" s="20" t="n">
-        <v>46974</v>
+        <v>46966</v>
       </c>
       <c r="U290" s="20" t="n">
-        <v>46980</v>
+        <v>46972</v>
       </c>
       <c r="V290" s="8" t="n">
         <v>5</v>
@@ -56763,10 +56763,10 @@
         <v/>
       </c>
       <c r="T291" s="20" t="n">
-        <v>46981</v>
+        <v>46973</v>
       </c>
       <c r="U291" s="20" t="n">
-        <v>46992</v>
+        <v>46982</v>
       </c>
       <c r="V291" s="8" t="n">
         <v>8</v>
@@ -56856,10 +56856,10 @@
         <v/>
       </c>
       <c r="T292" s="20" t="n">
-        <v>46993</v>
+        <v>46985</v>
       </c>
       <c r="U292" s="20" t="n">
-        <v>47006</v>
+        <v>46996</v>
       </c>
       <c r="V292" s="8" t="n">
         <v>10</v>
@@ -56949,10 +56949,10 @@
         <v/>
       </c>
       <c r="T293" s="20" t="n">
-        <v>46993</v>
+        <v>46985</v>
       </c>
       <c r="U293" s="20" t="n">
-        <v>47034</v>
+        <v>47024</v>
       </c>
       <c r="V293" s="8" t="n">
         <v>30</v>
@@ -57042,13 +57042,13 @@
         <v/>
       </c>
       <c r="T294" s="20" t="n">
-        <v>47035</v>
+        <v>47027</v>
       </c>
       <c r="U294" s="20" t="n">
-        <v>47055</v>
+        <v>47056</v>
       </c>
       <c r="V294" s="8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="295">
@@ -57135,10 +57135,10 @@
         <v/>
       </c>
       <c r="T295" s="20" t="n">
-        <v>46777</v>
+        <v>46768</v>
       </c>
       <c r="U295" s="20" t="n">
-        <v>46797</v>
+        <v>46786</v>
       </c>
       <c r="V295" s="8" t="n">
         <v>15</v>
@@ -57228,10 +57228,10 @@
         <v/>
       </c>
       <c r="T296" s="20" t="n">
-        <v>46798</v>
+        <v>46789</v>
       </c>
       <c r="U296" s="20" t="n">
-        <v>46825</v>
+        <v>46814</v>
       </c>
       <c r="V296" s="8" t="n">
         <v>15</v>
@@ -57321,10 +57321,10 @@
         <v/>
       </c>
       <c r="T297" s="20" t="n">
-        <v>46798</v>
+        <v>46789</v>
       </c>
       <c r="U297" s="20" t="n">
-        <v>46813</v>
+        <v>46797</v>
       </c>
       <c r="V297" s="8" t="n">
         <v>7</v>
@@ -57414,10 +57414,10 @@
         <v/>
       </c>
       <c r="T298" s="20" t="n">
-        <v>46814</v>
+        <v>46798</v>
       </c>
       <c r="U298" s="20" t="n">
-        <v>46834</v>
+        <v>46825</v>
       </c>
       <c r="V298" s="8" t="n">
         <v>15</v>
@@ -57507,10 +57507,10 @@
         <v/>
       </c>
       <c r="T299" s="20" t="n">
-        <v>46814</v>
+        <v>46798</v>
       </c>
       <c r="U299" s="20" t="n">
-        <v>46831</v>
+        <v>46820</v>
       </c>
       <c r="V299" s="8" t="n">
         <v>12</v>
@@ -57600,10 +57600,10 @@
         <v/>
       </c>
       <c r="T300" s="20" t="n">
-        <v>46832</v>
+        <v>46821</v>
       </c>
       <c r="U300" s="20" t="n">
-        <v>46852</v>
+        <v>46841</v>
       </c>
       <c r="V300" s="8" t="n">
         <v>15</v>
@@ -57693,10 +57693,10 @@
         <v/>
       </c>
       <c r="T301" s="20" t="n">
-        <v>46832</v>
+        <v>46821</v>
       </c>
       <c r="U301" s="20" t="n">
-        <v>46856</v>
+        <v>46847</v>
       </c>
       <c r="V301" s="8" t="n">
         <v>19</v>
@@ -57786,10 +57786,10 @@
         <v/>
       </c>
       <c r="T302" s="20" t="n">
-        <v>46859</v>
+        <v>46848</v>
       </c>
       <c r="U302" s="20" t="n">
-        <v>46884</v>
+        <v>46868</v>
       </c>
       <c r="V302" s="8" t="n">
         <v>15</v>
@@ -57879,10 +57879,10 @@
         <v/>
       </c>
       <c r="T303" s="20" t="n">
-        <v>46859</v>
+        <v>46848</v>
       </c>
       <c r="U303" s="20" t="n">
-        <v>46869</v>
+        <v>46860</v>
       </c>
       <c r="V303" s="8" t="n">
         <v>9</v>
@@ -57972,10 +57972,10 @@
         <v/>
       </c>
       <c r="T304" s="20" t="n">
-        <v>46870</v>
+        <v>46861</v>
       </c>
       <c r="U304" s="20" t="n">
-        <v>46897</v>
+        <v>46888</v>
       </c>
       <c r="V304" s="8" t="n">
         <v>15</v>
@@ -58065,10 +58065,10 @@
         <v/>
       </c>
       <c r="T305" s="20" t="n">
-        <v>46841</v>
+        <v>46832</v>
       </c>
       <c r="U305" s="20" t="n">
-        <v>46869</v>
+        <v>46860</v>
       </c>
       <c r="V305" s="8" t="n">
         <v>21</v>
@@ -58158,10 +58158,10 @@
         <v/>
       </c>
       <c r="T306" s="20" t="n">
-        <v>46870</v>
+        <v>46861</v>
       </c>
       <c r="U306" s="20" t="n">
-        <v>46897</v>
+        <v>46888</v>
       </c>
       <c r="V306" s="8" t="n">
         <v>15</v>
@@ -58251,10 +58251,10 @@
         <v/>
       </c>
       <c r="T307" s="20" t="n">
-        <v>47136</v>
+        <v>47127</v>
       </c>
       <c r="U307" s="20" t="n">
-        <v>47192</v>
+        <v>47183</v>
       </c>
       <c r="V307" s="8" t="n">
         <v>35</v>
@@ -58344,10 +58344,10 @@
         <v/>
       </c>
       <c r="T308" s="20" t="n">
-        <v>47195</v>
+        <v>47184</v>
       </c>
       <c r="U308" s="20" t="n">
-        <v>47213</v>
+        <v>47204</v>
       </c>
       <c r="V308" s="8" t="n">
         <v>15</v>
@@ -58437,10 +58437,10 @@
         <v/>
       </c>
       <c r="T309" s="20" t="n">
-        <v>46898</v>
+        <v>46889</v>
       </c>
       <c r="U309" s="20" t="n">
-        <v>46904</v>
+        <v>46895</v>
       </c>
       <c r="V309" s="8" t="n">
         <v>5</v>
@@ -58530,10 +58530,10 @@
         <v/>
       </c>
       <c r="T310" s="20" t="n">
-        <v>46905</v>
+        <v>46896</v>
       </c>
       <c r="U310" s="20" t="n">
-        <v>46918</v>
+        <v>46909</v>
       </c>
       <c r="V310" s="8" t="n">
         <v>10</v>
@@ -58623,10 +58623,10 @@
         <v/>
       </c>
       <c r="T311" s="20" t="n">
-        <v>46898</v>
+        <v>46889</v>
       </c>
       <c r="U311" s="20" t="n">
-        <v>46981</v>
+        <v>46972</v>
       </c>
       <c r="V311" s="8" t="n">
         <v>60</v>
@@ -58716,10 +58716,10 @@
         <v/>
       </c>
       <c r="T312" s="20" t="n">
-        <v>46898</v>
+        <v>46889</v>
       </c>
       <c r="U312" s="20" t="n">
-        <v>46981</v>
+        <v>46972</v>
       </c>
       <c r="V312" s="8" t="n">
         <v>60</v>
@@ -58809,10 +58809,10 @@
         <v/>
       </c>
       <c r="T313" s="20" t="n">
-        <v>46898</v>
+        <v>46889</v>
       </c>
       <c r="U313" s="20" t="n">
-        <v>46981</v>
+        <v>46972</v>
       </c>
       <c r="V313" s="8" t="n">
         <v>60</v>
@@ -58895,17 +58895,17 @@
         </is>
       </c>
       <c r="R314" s="9" t="n">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="S314" s="19">
         <f>R314/1000</f>
         <v/>
       </c>
       <c r="T314" s="20" t="n">
-        <v>46898</v>
+        <v>46889</v>
       </c>
       <c r="U314" s="20" t="n">
-        <v>46981</v>
+        <v>46972</v>
       </c>
       <c r="V314" s="8" t="n">
         <v>60</v>
@@ -58995,10 +58995,10 @@
         <v/>
       </c>
       <c r="T315" s="20" t="n">
-        <v>46982</v>
+        <v>46973</v>
       </c>
       <c r="U315" s="20" t="n">
-        <v>46995</v>
+        <v>46986</v>
       </c>
       <c r="V315" s="8" t="n">
         <v>10</v>
@@ -59088,10 +59088,10 @@
         <v/>
       </c>
       <c r="T316" s="20" t="n">
-        <v>46996</v>
+        <v>46987</v>
       </c>
       <c r="U316" s="20" t="n">
-        <v>47034</v>
+        <v>47023</v>
       </c>
       <c r="V316" s="8" t="n">
         <v>27</v>
@@ -59181,10 +59181,10 @@
         <v/>
       </c>
       <c r="T317" s="20" t="n">
-        <v>47035</v>
+        <v>47024</v>
       </c>
       <c r="U317" s="20" t="n">
-        <v>47041</v>
+        <v>47030</v>
       </c>
       <c r="V317" s="8" t="n">
         <v>5</v>
@@ -59274,10 +59274,10 @@
         <v/>
       </c>
       <c r="T318" s="20" t="n">
-        <v>46919</v>
+        <v>46910</v>
       </c>
       <c r="U318" s="20" t="n">
-        <v>46953</v>
+        <v>46944</v>
       </c>
       <c r="V318" s="8" t="n">
         <v>25</v>
@@ -59367,10 +59367,10 @@
         <v/>
       </c>
       <c r="T319" s="20" t="n">
-        <v>46943</v>
+        <v>46932</v>
       </c>
       <c r="U319" s="20" t="n">
-        <v>46968</v>
+        <v>46959</v>
       </c>
       <c r="V319" s="8" t="n">
         <v>20</v>
@@ -59460,10 +59460,10 @@
         <v/>
       </c>
       <c r="T320" s="20" t="n">
-        <v>47042</v>
+        <v>47031</v>
       </c>
       <c r="U320" s="20" t="n">
-        <v>47069</v>
+        <v>47058</v>
       </c>
       <c r="V320" s="8" t="n">
         <v>20</v>
@@ -59553,10 +59553,10 @@
         <v/>
       </c>
       <c r="T321" s="20" t="n">
-        <v>47051</v>
+        <v>47042</v>
       </c>
       <c r="U321" s="20" t="n">
-        <v>47098</v>
+        <v>47087</v>
       </c>
       <c r="V321" s="8" t="n">
         <v>34</v>
@@ -59646,10 +59646,10 @@
         <v/>
       </c>
       <c r="T322" s="20" t="n">
-        <v>47099</v>
+        <v>47090</v>
       </c>
       <c r="U322" s="20" t="n">
-        <v>47135</v>
+        <v>47126</v>
       </c>
       <c r="V322" s="8" t="n">
         <v>27</v>
@@ -59739,10 +59739,10 @@
         <v/>
       </c>
       <c r="T323" s="20" t="n">
-        <v>47070</v>
+        <v>47059</v>
       </c>
       <c r="U323" s="20" t="n">
-        <v>47100</v>
+        <v>47091</v>
       </c>
       <c r="V323" s="8" t="n">
         <v>23</v>
@@ -59832,10 +59832,10 @@
         <v/>
       </c>
       <c r="T324" s="20" t="n">
-        <v>47079</v>
+        <v>47070</v>
       </c>
       <c r="U324" s="20" t="n">
-        <v>47106</v>
+        <v>47097</v>
       </c>
       <c r="V324" s="8" t="n">
         <v>20</v>
@@ -59925,10 +59925,10 @@
         <v/>
       </c>
       <c r="T325" s="20" t="n">
+        <v>47127</v>
+      </c>
+      <c r="U325" s="20" t="n">
         <v>47136</v>
-      </c>
-      <c r="U325" s="20" t="n">
-        <v>47147</v>
       </c>
       <c r="V325" s="8" t="n">
         <v>8</v>
@@ -60018,10 +60018,10 @@
         <v/>
       </c>
       <c r="T326" s="20" t="n">
-        <v>47148</v>
+        <v>47139</v>
       </c>
       <c r="U326" s="20" t="n">
-        <v>47170</v>
+        <v>47154</v>
       </c>
       <c r="V326" s="8" t="n">
         <v>12</v>
@@ -60111,10 +60111,10 @@
         <v/>
       </c>
       <c r="T327" s="20" t="n">
-        <v>47174</v>
+        <v>47155</v>
       </c>
       <c r="U327" s="20" t="n">
-        <v>47185</v>
+        <v>47176</v>
       </c>
       <c r="V327" s="8" t="n">
         <v>10</v>
@@ -60204,10 +60204,10 @@
         <v/>
       </c>
       <c r="T328" s="20" t="n">
-        <v>47174</v>
+        <v>47155</v>
       </c>
       <c r="U328" s="20" t="n">
-        <v>47213</v>
+        <v>47204</v>
       </c>
       <c r="V328" s="8" t="n">
         <v>30</v>
@@ -60297,13 +60297,13 @@
         <v/>
       </c>
       <c r="T329" s="20" t="n">
-        <v>47216</v>
+        <v>47205</v>
       </c>
       <c r="U329" s="20" t="n">
         <v>47241</v>
       </c>
       <c r="V329" s="8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="330">
@@ -60390,10 +60390,10 @@
         <v/>
       </c>
       <c r="T330" s="20" t="n">
-        <v>46777</v>
+        <v>46768</v>
       </c>
       <c r="U330" s="20" t="n">
-        <v>46798</v>
+        <v>46789</v>
       </c>
       <c r="V330" s="8" t="n">
         <v>16</v>
@@ -60483,10 +60483,10 @@
         <v/>
       </c>
       <c r="T331" s="20" t="n">
-        <v>46799</v>
+        <v>46790</v>
       </c>
       <c r="U331" s="20" t="n">
-        <v>46826</v>
+        <v>46817</v>
       </c>
       <c r="V331" s="8" t="n">
         <v>15</v>
@@ -60576,10 +60576,10 @@
         <v/>
       </c>
       <c r="T332" s="20" t="n">
-        <v>46799</v>
+        <v>46790</v>
       </c>
       <c r="U332" s="20" t="n">
-        <v>46814</v>
+        <v>46798</v>
       </c>
       <c r="V332" s="8" t="n">
         <v>7</v>
@@ -60669,10 +60669,10 @@
         <v/>
       </c>
       <c r="T333" s="20" t="n">
-        <v>46817</v>
+        <v>46799</v>
       </c>
       <c r="U333" s="20" t="n">
-        <v>46835</v>
+        <v>46826</v>
       </c>
       <c r="V333" s="8" t="n">
         <v>15</v>
@@ -60762,10 +60762,10 @@
         <v/>
       </c>
       <c r="T334" s="20" t="n">
-        <v>46817</v>
+        <v>46799</v>
       </c>
       <c r="U334" s="20" t="n">
-        <v>46832</v>
+        <v>46821</v>
       </c>
       <c r="V334" s="8" t="n">
         <v>12</v>
@@ -60855,10 +60855,10 @@
         <v/>
       </c>
       <c r="T335" s="20" t="n">
-        <v>46833</v>
+        <v>46824</v>
       </c>
       <c r="U335" s="20" t="n">
-        <v>46853</v>
+        <v>46842</v>
       </c>
       <c r="V335" s="8" t="n">
         <v>15</v>
@@ -60948,10 +60948,10 @@
         <v/>
       </c>
       <c r="T336" s="20" t="n">
-        <v>46833</v>
+        <v>46824</v>
       </c>
       <c r="U336" s="20" t="n">
-        <v>46856</v>
+        <v>46847</v>
       </c>
       <c r="V336" s="8" t="n">
         <v>18</v>
@@ -61041,10 +61041,10 @@
         <v/>
       </c>
       <c r="T337" s="20" t="n">
-        <v>46859</v>
+        <v>46848</v>
       </c>
       <c r="U337" s="20" t="n">
-        <v>46884</v>
+        <v>46868</v>
       </c>
       <c r="V337" s="8" t="n">
         <v>15</v>
@@ -61134,10 +61134,10 @@
         <v/>
       </c>
       <c r="T338" s="20" t="n">
-        <v>46859</v>
+        <v>46848</v>
       </c>
       <c r="U338" s="20" t="n">
-        <v>46869</v>
+        <v>46860</v>
       </c>
       <c r="V338" s="8" t="n">
         <v>9</v>
@@ -61227,10 +61227,10 @@
         <v/>
       </c>
       <c r="T339" s="20" t="n">
-        <v>46870</v>
+        <v>46861</v>
       </c>
       <c r="U339" s="20" t="n">
-        <v>46897</v>
+        <v>46888</v>
       </c>
       <c r="V339" s="8" t="n">
         <v>15</v>
@@ -61320,10 +61320,10 @@
         <v/>
       </c>
       <c r="T340" s="20" t="n">
-        <v>46842</v>
+        <v>46833</v>
       </c>
       <c r="U340" s="20" t="n">
-        <v>46869</v>
+        <v>46860</v>
       </c>
       <c r="V340" s="8" t="n">
         <v>20</v>
@@ -61413,10 +61413,10 @@
         <v/>
       </c>
       <c r="T341" s="20" t="n">
-        <v>46870</v>
+        <v>46861</v>
       </c>
       <c r="U341" s="20" t="n">
-        <v>46897</v>
+        <v>46888</v>
       </c>
       <c r="V341" s="8" t="n">
         <v>15</v>
@@ -61506,10 +61506,10 @@
         <v/>
       </c>
       <c r="T342" s="20" t="n">
-        <v>47141</v>
+        <v>47132</v>
       </c>
       <c r="U342" s="20" t="n">
-        <v>47198</v>
+        <v>47189</v>
       </c>
       <c r="V342" s="8" t="n">
         <v>36</v>
@@ -61599,10 +61599,10 @@
         <v/>
       </c>
       <c r="T343" s="20" t="n">
-        <v>47199</v>
+        <v>47190</v>
       </c>
       <c r="U343" s="20" t="n">
-        <v>47219</v>
+        <v>47210</v>
       </c>
       <c r="V343" s="8" t="n">
         <v>15</v>
@@ -61692,10 +61692,10 @@
         <v/>
       </c>
       <c r="T344" s="20" t="n">
-        <v>46898</v>
+        <v>46889</v>
       </c>
       <c r="U344" s="20" t="n">
-        <v>46904</v>
+        <v>46895</v>
       </c>
       <c r="V344" s="8" t="n">
         <v>5</v>
@@ -61785,10 +61785,10 @@
         <v/>
       </c>
       <c r="T345" s="20" t="n">
-        <v>46905</v>
+        <v>46896</v>
       </c>
       <c r="U345" s="20" t="n">
-        <v>46918</v>
+        <v>46909</v>
       </c>
       <c r="V345" s="8" t="n">
         <v>10</v>
@@ -61878,10 +61878,10 @@
         <v/>
       </c>
       <c r="T346" s="20" t="n">
-        <v>46898</v>
+        <v>46889</v>
       </c>
       <c r="U346" s="20" t="n">
-        <v>46980</v>
+        <v>46971</v>
       </c>
       <c r="V346" s="8" t="n">
         <v>59</v>
@@ -61971,10 +61971,10 @@
         <v/>
       </c>
       <c r="T347" s="20" t="n">
-        <v>46898</v>
+        <v>46889</v>
       </c>
       <c r="U347" s="20" t="n">
-        <v>46980</v>
+        <v>46971</v>
       </c>
       <c r="V347" s="8" t="n">
         <v>59</v>
@@ -62064,10 +62064,10 @@
         <v/>
       </c>
       <c r="T348" s="20" t="n">
-        <v>46898</v>
+        <v>46889</v>
       </c>
       <c r="U348" s="20" t="n">
-        <v>46980</v>
+        <v>46971</v>
       </c>
       <c r="V348" s="8" t="n">
         <v>59</v>
@@ -62157,10 +62157,10 @@
         <v/>
       </c>
       <c r="T349" s="20" t="n">
-        <v>46898</v>
+        <v>46889</v>
       </c>
       <c r="U349" s="20" t="n">
-        <v>46980</v>
+        <v>46971</v>
       </c>
       <c r="V349" s="8" t="n">
         <v>59</v>
@@ -62250,10 +62250,10 @@
         <v/>
       </c>
       <c r="T350" s="20" t="n">
-        <v>46981</v>
+        <v>46972</v>
       </c>
       <c r="U350" s="20" t="n">
-        <v>46994</v>
+        <v>46985</v>
       </c>
       <c r="V350" s="8" t="n">
         <v>10</v>
@@ -62343,10 +62343,10 @@
         <v/>
       </c>
       <c r="T351" s="20" t="n">
-        <v>46995</v>
+        <v>46986</v>
       </c>
       <c r="U351" s="20" t="n">
-        <v>47031</v>
+        <v>47022</v>
       </c>
       <c r="V351" s="8" t="n">
         <v>27</v>
@@ -62436,10 +62436,10 @@
         <v/>
       </c>
       <c r="T352" s="20" t="n">
-        <v>47034</v>
+        <v>47023</v>
       </c>
       <c r="U352" s="20" t="n">
-        <v>47038</v>
+        <v>47029</v>
       </c>
       <c r="V352" s="8" t="n">
         <v>5</v>
@@ -62529,10 +62529,10 @@
         <v/>
       </c>
       <c r="T353" s="20" t="n">
-        <v>46919</v>
+        <v>46910</v>
       </c>
       <c r="U353" s="20" t="n">
-        <v>46961</v>
+        <v>46952</v>
       </c>
       <c r="V353" s="8" t="n">
         <v>31</v>
@@ -62622,10 +62622,10 @@
         <v/>
       </c>
       <c r="T354" s="20" t="n">
-        <v>46947</v>
+        <v>46938</v>
       </c>
       <c r="U354" s="20" t="n">
-        <v>46980</v>
+        <v>46971</v>
       </c>
       <c r="V354" s="8" t="n">
         <v>24</v>
@@ -62715,10 +62715,10 @@
         <v/>
       </c>
       <c r="T355" s="20" t="n">
-        <v>47041</v>
+        <v>47030</v>
       </c>
       <c r="U355" s="20" t="n">
-        <v>47070</v>
+        <v>47059</v>
       </c>
       <c r="V355" s="8" t="n">
         <v>22</v>
@@ -62808,10 +62808,10 @@
         <v/>
       </c>
       <c r="T356" s="20" t="n">
-        <v>47050</v>
+        <v>47041</v>
       </c>
       <c r="U356" s="20" t="n">
-        <v>47099</v>
+        <v>47090</v>
       </c>
       <c r="V356" s="8" t="n">
         <v>36</v>
@@ -62901,10 +62901,10 @@
         <v/>
       </c>
       <c r="T357" s="20" t="n">
-        <v>47100</v>
+        <v>47091</v>
       </c>
       <c r="U357" s="20" t="n">
-        <v>47140</v>
+        <v>47129</v>
       </c>
       <c r="V357" s="8" t="n">
         <v>29</v>
@@ -62994,10 +62994,10 @@
         <v/>
       </c>
       <c r="T358" s="20" t="n">
-        <v>47071</v>
+        <v>47062</v>
       </c>
       <c r="U358" s="20" t="n">
-        <v>47105</v>
+        <v>47094</v>
       </c>
       <c r="V358" s="8" t="n">
         <v>25</v>
@@ -63087,10 +63087,10 @@
         <v/>
       </c>
       <c r="T359" s="20" t="n">
-        <v>47080</v>
+        <v>47071</v>
       </c>
       <c r="U359" s="20" t="n">
-        <v>47111</v>
+        <v>47100</v>
       </c>
       <c r="V359" s="8" t="n">
         <v>22</v>
@@ -63180,10 +63180,10 @@
         <v/>
       </c>
       <c r="T360" s="20" t="n">
+        <v>47132</v>
+      </c>
+      <c r="U360" s="20" t="n">
         <v>47141</v>
-      </c>
-      <c r="U360" s="20" t="n">
-        <v>47150</v>
       </c>
       <c r="V360" s="8" t="n">
         <v>8</v>
@@ -63273,10 +63273,10 @@
         <v/>
       </c>
       <c r="T361" s="20" t="n">
-        <v>47153</v>
+        <v>47142</v>
       </c>
       <c r="U361" s="20" t="n">
-        <v>47177</v>
+        <v>47167</v>
       </c>
       <c r="V361" s="8" t="n">
         <v>13</v>
@@ -63366,10 +63366,10 @@
         <v/>
       </c>
       <c r="T362" s="20" t="n">
-        <v>47178</v>
+        <v>47168</v>
       </c>
       <c r="U362" s="20" t="n">
-        <v>47191</v>
+        <v>47182</v>
       </c>
       <c r="V362" s="8" t="n">
         <v>10</v>
@@ -63459,10 +63459,10 @@
         <v/>
       </c>
       <c r="T363" s="20" t="n">
-        <v>47178</v>
+        <v>47168</v>
       </c>
       <c r="U363" s="20" t="n">
-        <v>47219</v>
+        <v>47210</v>
       </c>
       <c r="V363" s="8" t="n">
         <v>30</v>
@@ -63552,13 +63552,13 @@
         <v/>
       </c>
       <c r="T364" s="20" t="n">
-        <v>47220</v>
+        <v>47211</v>
       </c>
       <c r="U364" s="20" t="n">
         <v>47247</v>
       </c>
       <c r="V364" s="8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="365">
@@ -63645,10 +63645,10 @@
         <v/>
       </c>
       <c r="T365" s="20" t="n">
-        <v>46832</v>
+        <v>46820</v>
       </c>
       <c r="U365" s="20" t="n">
-        <v>46841</v>
+        <v>46831</v>
       </c>
       <c r="V365" s="8" t="n">
         <v>8</v>
@@ -63738,10 +63738,10 @@
         <v/>
       </c>
       <c r="T366" s="20" t="n">
-        <v>46842</v>
+        <v>46832</v>
       </c>
       <c r="U366" s="20" t="n">
-        <v>46862</v>
+        <v>46852</v>
       </c>
       <c r="V366" s="8" t="n">
         <v>15</v>
@@ -63831,10 +63831,10 @@
         <v/>
       </c>
       <c r="T367" s="20" t="n">
+        <v>46832</v>
+      </c>
+      <c r="U367" s="20" t="n">
         <v>46842</v>
-      </c>
-      <c r="U367" s="20" t="n">
-        <v>46854</v>
       </c>
       <c r="V367" s="8" t="n">
         <v>9</v>
@@ -63924,10 +63924,10 @@
         <v/>
       </c>
       <c r="T368" s="20" t="n">
-        <v>46855</v>
+        <v>46845</v>
       </c>
       <c r="U368" s="20" t="n">
-        <v>46882</v>
+        <v>46863</v>
       </c>
       <c r="V368" s="8" t="n">
         <v>15</v>
@@ -64017,10 +64017,10 @@
         <v/>
       </c>
       <c r="T369" s="20" t="n">
-        <v>46855</v>
+        <v>46845</v>
       </c>
       <c r="U369" s="20" t="n">
-        <v>46882</v>
+        <v>46863</v>
       </c>
       <c r="V369" s="8" t="n">
         <v>15</v>
@@ -64110,10 +64110,10 @@
         <v/>
       </c>
       <c r="T370" s="20" t="n">
-        <v>46883</v>
+        <v>46866</v>
       </c>
       <c r="U370" s="20" t="n">
-        <v>46903</v>
+        <v>46891</v>
       </c>
       <c r="V370" s="8" t="n">
         <v>15</v>
@@ -64203,10 +64203,10 @@
         <v/>
       </c>
       <c r="T371" s="20" t="n">
-        <v>46883</v>
+        <v>46866</v>
       </c>
       <c r="U371" s="20" t="n">
-        <v>46916</v>
+        <v>46904</v>
       </c>
       <c r="V371" s="8" t="n">
         <v>24</v>
@@ -64296,10 +64296,10 @@
         <v/>
       </c>
       <c r="T372" s="20" t="n">
-        <v>46917</v>
+        <v>46905</v>
       </c>
       <c r="U372" s="20" t="n">
-        <v>46937</v>
+        <v>46925</v>
       </c>
       <c r="V372" s="8" t="n">
         <v>15</v>
@@ -64382,20 +64382,20 @@
         </is>
       </c>
       <c r="R373" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S373" s="19">
         <f>R373/1000</f>
         <v/>
       </c>
       <c r="T373" s="20" t="n">
-        <v>46917</v>
+        <v>46905</v>
       </c>
       <c r="U373" s="20" t="n">
-        <v>46932</v>
+        <v>46919</v>
       </c>
       <c r="V373" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="374">
@@ -64475,17 +64475,17 @@
         </is>
       </c>
       <c r="R374" s="9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S374" s="19">
         <f>R374/1000</f>
         <v/>
       </c>
       <c r="T374" s="20" t="n">
-        <v>46933</v>
+        <v>46922</v>
       </c>
       <c r="U374" s="20" t="n">
-        <v>46953</v>
+        <v>46940</v>
       </c>
       <c r="V374" s="8" t="n">
         <v>15</v>
@@ -64575,13 +64575,13 @@
         <v/>
       </c>
       <c r="T375" s="20" t="n">
-        <v>46896</v>
+        <v>46884</v>
       </c>
       <c r="U375" s="20" t="n">
-        <v>46932</v>
+        <v>46919</v>
       </c>
       <c r="V375" s="8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="376">
@@ -64668,10 +64668,10 @@
         <v/>
       </c>
       <c r="T376" s="20" t="n">
-        <v>46933</v>
+        <v>46922</v>
       </c>
       <c r="U376" s="20" t="n">
-        <v>46953</v>
+        <v>46940</v>
       </c>
       <c r="V376" s="8" t="n">
         <v>15</v>
@@ -64761,10 +64761,10 @@
         <v/>
       </c>
       <c r="T377" s="20" t="n">
-        <v>47093</v>
+        <v>47080</v>
       </c>
       <c r="U377" s="20" t="n">
-        <v>47128</v>
+        <v>47115</v>
       </c>
       <c r="V377" s="8" t="n">
         <v>26</v>
@@ -64854,10 +64854,10 @@
         <v/>
       </c>
       <c r="T378" s="20" t="n">
-        <v>47129</v>
+        <v>47118</v>
       </c>
       <c r="U378" s="20" t="n">
-        <v>47149</v>
+        <v>47136</v>
       </c>
       <c r="V378" s="8" t="n">
         <v>15</v>
@@ -64947,10 +64947,10 @@
         <v/>
       </c>
       <c r="T379" s="20" t="n">
-        <v>46954</v>
+        <v>46943</v>
       </c>
       <c r="U379" s="20" t="n">
-        <v>46960</v>
+        <v>46947</v>
       </c>
       <c r="V379" s="8" t="n">
         <v>5</v>
@@ -65040,10 +65040,10 @@
         <v/>
       </c>
       <c r="T380" s="20" t="n">
+        <v>46950</v>
+      </c>
+      <c r="U380" s="20" t="n">
         <v>46961</v>
-      </c>
-      <c r="U380" s="20" t="n">
-        <v>46974</v>
       </c>
       <c r="V380" s="8" t="n">
         <v>10</v>
@@ -65133,10 +65133,10 @@
         <v/>
       </c>
       <c r="T381" s="20" t="n">
-        <v>46954</v>
+        <v>46943</v>
       </c>
       <c r="U381" s="20" t="n">
-        <v>47008</v>
+        <v>46995</v>
       </c>
       <c r="V381" s="8" t="n">
         <v>39</v>
@@ -65226,10 +65226,10 @@
         <v/>
       </c>
       <c r="T382" s="20" t="n">
-        <v>46954</v>
+        <v>46943</v>
       </c>
       <c r="U382" s="20" t="n">
-        <v>47008</v>
+        <v>46995</v>
       </c>
       <c r="V382" s="8" t="n">
         <v>39</v>
@@ -65319,10 +65319,10 @@
         <v/>
       </c>
       <c r="T383" s="20" t="n">
-        <v>46954</v>
+        <v>46943</v>
       </c>
       <c r="U383" s="20" t="n">
-        <v>47008</v>
+        <v>46995</v>
       </c>
       <c r="V383" s="8" t="n">
         <v>39</v>
@@ -65412,10 +65412,10 @@
         <v/>
       </c>
       <c r="T384" s="20" t="n">
-        <v>46954</v>
+        <v>46943</v>
       </c>
       <c r="U384" s="20" t="n">
-        <v>47008</v>
+        <v>46995</v>
       </c>
       <c r="V384" s="8" t="n">
         <v>39</v>
@@ -65505,10 +65505,10 @@
         <v/>
       </c>
       <c r="T385" s="20" t="n">
+        <v>46996</v>
+      </c>
+      <c r="U385" s="20" t="n">
         <v>47009</v>
-      </c>
-      <c r="U385" s="20" t="n">
-        <v>47022</v>
       </c>
       <c r="V385" s="8" t="n">
         <v>10</v>
@@ -65598,10 +65598,10 @@
         <v/>
       </c>
       <c r="T386" s="20" t="n">
-        <v>47023</v>
+        <v>47010</v>
       </c>
       <c r="U386" s="20" t="n">
-        <v>47049</v>
+        <v>47036</v>
       </c>
       <c r="V386" s="8" t="n">
         <v>19</v>
@@ -65691,10 +65691,10 @@
         <v/>
       </c>
       <c r="T387" s="20" t="n">
-        <v>47050</v>
+        <v>47037</v>
       </c>
       <c r="U387" s="20" t="n">
-        <v>47056</v>
+        <v>47043</v>
       </c>
       <c r="V387" s="8" t="n">
         <v>5</v>
@@ -65784,10 +65784,10 @@
         <v/>
       </c>
       <c r="T388" s="20" t="n">
-        <v>46975</v>
+        <v>46964</v>
       </c>
       <c r="U388" s="20" t="n">
-        <v>47024</v>
+        <v>47013</v>
       </c>
       <c r="V388" s="8" t="n">
         <v>36</v>
@@ -65877,10 +65877,10 @@
         <v/>
       </c>
       <c r="T389" s="20" t="n">
-        <v>47008</v>
+        <v>46995</v>
       </c>
       <c r="U389" s="20" t="n">
-        <v>47045</v>
+        <v>47034</v>
       </c>
       <c r="V389" s="8" t="n">
         <v>28</v>
@@ -65970,10 +65970,10 @@
         <v/>
       </c>
       <c r="T390" s="20" t="n">
-        <v>47057</v>
+        <v>47044</v>
       </c>
       <c r="U390" s="20" t="n">
-        <v>47066</v>
+        <v>47055</v>
       </c>
       <c r="V390" s="8" t="n">
         <v>8</v>
@@ -66063,10 +66063,10 @@
         <v/>
       </c>
       <c r="T391" s="20" t="n">
-        <v>47062</v>
+        <v>47049</v>
       </c>
       <c r="U391" s="20" t="n">
-        <v>47078</v>
+        <v>47065</v>
       </c>
       <c r="V391" s="8" t="n">
         <v>13</v>
@@ -66156,10 +66156,10 @@
         <v/>
       </c>
       <c r="T392" s="20" t="n">
+        <v>47066</v>
+      </c>
+      <c r="U392" s="20" t="n">
         <v>47079</v>
-      </c>
-      <c r="U392" s="20" t="n">
-        <v>47092</v>
       </c>
       <c r="V392" s="8" t="n">
         <v>10</v>
@@ -66249,10 +66249,10 @@
         <v/>
       </c>
       <c r="T393" s="20" t="n">
-        <v>47069</v>
+        <v>47056</v>
       </c>
       <c r="U393" s="20" t="n">
-        <v>47079</v>
+        <v>47066</v>
       </c>
       <c r="V393" s="8" t="n">
         <v>9</v>
@@ -66342,10 +66342,10 @@
         <v/>
       </c>
       <c r="T394" s="20" t="n">
-        <v>47072</v>
+        <v>47059</v>
       </c>
       <c r="U394" s="20" t="n">
-        <v>47083</v>
+        <v>47070</v>
       </c>
       <c r="V394" s="8" t="n">
         <v>8</v>
@@ -66435,10 +66435,10 @@
         <v/>
       </c>
       <c r="T395" s="20" t="n">
-        <v>47093</v>
+        <v>47080</v>
       </c>
       <c r="U395" s="20" t="n">
-        <v>47098</v>
+        <v>47085</v>
       </c>
       <c r="V395" s="8" t="n">
         <v>4</v>
@@ -66528,10 +66528,10 @@
         <v/>
       </c>
       <c r="T396" s="20" t="n">
-        <v>47099</v>
+        <v>47086</v>
       </c>
       <c r="U396" s="20" t="n">
-        <v>47107</v>
+        <v>47094</v>
       </c>
       <c r="V396" s="8" t="n">
         <v>7</v>
@@ -66621,10 +66621,10 @@
         <v/>
       </c>
       <c r="T397" s="20" t="n">
+        <v>47097</v>
+      </c>
+      <c r="U397" s="20" t="n">
         <v>47108</v>
-      </c>
-      <c r="U397" s="20" t="n">
-        <v>47121</v>
       </c>
       <c r="V397" s="8" t="n">
         <v>10</v>
@@ -66714,10 +66714,10 @@
         <v/>
       </c>
       <c r="T398" s="20" t="n">
-        <v>47108</v>
+        <v>47097</v>
       </c>
       <c r="U398" s="20" t="n">
-        <v>47149</v>
+        <v>47136</v>
       </c>
       <c r="V398" s="8" t="n">
         <v>30</v>
@@ -66807,13 +66807,13 @@
         <v/>
       </c>
       <c r="T399" s="20" t="n">
-        <v>47150</v>
+        <v>47139</v>
       </c>
       <c r="U399" s="20" t="n">
-        <v>47178</v>
+        <v>47176</v>
       </c>
       <c r="V399" s="8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="400">
@@ -66900,10 +66900,10 @@
         <v/>
       </c>
       <c r="T400" s="20" t="n">
-        <v>46855</v>
+        <v>46845</v>
       </c>
       <c r="U400" s="20" t="n">
-        <v>46866</v>
+        <v>46854</v>
       </c>
       <c r="V400" s="8" t="n">
         <v>8</v>
@@ -66993,10 +66993,10 @@
         <v/>
       </c>
       <c r="T401" s="20" t="n">
-        <v>46867</v>
+        <v>46855</v>
       </c>
       <c r="U401" s="20" t="n">
-        <v>46894</v>
+        <v>46882</v>
       </c>
       <c r="V401" s="8" t="n">
         <v>15</v>
@@ -67086,10 +67086,10 @@
         <v/>
       </c>
       <c r="T402" s="20" t="n">
+        <v>46855</v>
+      </c>
+      <c r="U402" s="20" t="n">
         <v>46867</v>
-      </c>
-      <c r="U402" s="20" t="n">
-        <v>46884</v>
       </c>
       <c r="V402" s="8" t="n">
         <v>9</v>
@@ -67179,10 +67179,10 @@
         <v/>
       </c>
       <c r="T403" s="20" t="n">
-        <v>46887</v>
+        <v>46868</v>
       </c>
       <c r="U403" s="20" t="n">
-        <v>46905</v>
+        <v>46895</v>
       </c>
       <c r="V403" s="8" t="n">
         <v>15</v>
@@ -67272,10 +67272,10 @@
         <v/>
       </c>
       <c r="T404" s="20" t="n">
-        <v>46887</v>
+        <v>46868</v>
       </c>
       <c r="U404" s="20" t="n">
-        <v>46905</v>
+        <v>46895</v>
       </c>
       <c r="V404" s="8" t="n">
         <v>15</v>
@@ -67365,10 +67365,10 @@
         <v/>
       </c>
       <c r="T405" s="20" t="n">
-        <v>46908</v>
+        <v>46896</v>
       </c>
       <c r="U405" s="20" t="n">
-        <v>46926</v>
+        <v>46916</v>
       </c>
       <c r="V405" s="8" t="n">
         <v>15</v>
@@ -67458,10 +67458,10 @@
         <v/>
       </c>
       <c r="T406" s="20" t="n">
-        <v>46908</v>
+        <v>46896</v>
       </c>
       <c r="U406" s="20" t="n">
-        <v>46939</v>
+        <v>46929</v>
       </c>
       <c r="V406" s="8" t="n">
         <v>24</v>
@@ -67551,10 +67551,10 @@
         <v/>
       </c>
       <c r="T407" s="20" t="n">
-        <v>46940</v>
+        <v>46930</v>
       </c>
       <c r="U407" s="20" t="n">
-        <v>46960</v>
+        <v>46950</v>
       </c>
       <c r="V407" s="8" t="n">
         <v>15</v>
@@ -67637,20 +67637,20 @@
         </is>
       </c>
       <c r="R408" s="9" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="S408" s="19">
         <f>R408/1000</f>
         <v/>
       </c>
       <c r="T408" s="20" t="n">
-        <v>46940</v>
+        <v>46930</v>
       </c>
       <c r="U408" s="20" t="n">
-        <v>46954</v>
+        <v>46945</v>
       </c>
       <c r="V408" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="409">
@@ -67730,17 +67730,17 @@
         </is>
       </c>
       <c r="R409" s="9" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="S409" s="19">
         <f>R409/1000</f>
         <v/>
       </c>
       <c r="T409" s="20" t="n">
-        <v>46957</v>
+        <v>46946</v>
       </c>
       <c r="U409" s="20" t="n">
-        <v>46975</v>
+        <v>46966</v>
       </c>
       <c r="V409" s="8" t="n">
         <v>15</v>
@@ -67830,13 +67830,13 @@
         <v/>
       </c>
       <c r="T410" s="20" t="n">
-        <v>46919</v>
+        <v>46909</v>
       </c>
       <c r="U410" s="20" t="n">
-        <v>46954</v>
+        <v>46945</v>
       </c>
       <c r="V410" s="8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="411">
@@ -67916,17 +67916,17 @@
         </is>
       </c>
       <c r="R411" s="9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S411" s="19">
         <f>R411/1000</f>
         <v/>
       </c>
       <c r="T411" s="20" t="n">
-        <v>46957</v>
+        <v>46946</v>
       </c>
       <c r="U411" s="20" t="n">
-        <v>46975</v>
+        <v>46966</v>
       </c>
       <c r="V411" s="8" t="n">
         <v>15</v>
@@ -68016,10 +68016,10 @@
         <v/>
       </c>
       <c r="T412" s="20" t="n">
-        <v>47156</v>
+        <v>47147</v>
       </c>
       <c r="U412" s="20" t="n">
-        <v>47203</v>
+        <v>47192</v>
       </c>
       <c r="V412" s="8" t="n">
         <v>28</v>
@@ -68109,10 +68109,10 @@
         <v/>
       </c>
       <c r="T413" s="20" t="n">
-        <v>47204</v>
+        <v>47195</v>
       </c>
       <c r="U413" s="20" t="n">
-        <v>47224</v>
+        <v>47213</v>
       </c>
       <c r="V413" s="8" t="n">
         <v>15</v>
@@ -68202,10 +68202,10 @@
         <v/>
       </c>
       <c r="T414" s="20" t="n">
-        <v>46978</v>
+        <v>46967</v>
       </c>
       <c r="U414" s="20" t="n">
-        <v>46982</v>
+        <v>46973</v>
       </c>
       <c r="V414" s="8" t="n">
         <v>5</v>
@@ -68295,10 +68295,10 @@
         <v/>
       </c>
       <c r="T415" s="20" t="n">
-        <v>46985</v>
+        <v>46974</v>
       </c>
       <c r="U415" s="20" t="n">
-        <v>46996</v>
+        <v>46987</v>
       </c>
       <c r="V415" s="8" t="n">
         <v>10</v>
@@ -68388,10 +68388,10 @@
         <v/>
       </c>
       <c r="T416" s="20" t="n">
-        <v>46978</v>
+        <v>46967</v>
       </c>
       <c r="U416" s="20" t="n">
-        <v>47042</v>
+        <v>47031</v>
       </c>
       <c r="V416" s="8" t="n">
         <v>47</v>
@@ -68481,10 +68481,10 @@
         <v/>
       </c>
       <c r="T417" s="20" t="n">
-        <v>46978</v>
+        <v>46967</v>
       </c>
       <c r="U417" s="20" t="n">
-        <v>47042</v>
+        <v>47031</v>
       </c>
       <c r="V417" s="8" t="n">
         <v>47</v>
@@ -68574,10 +68574,10 @@
         <v/>
       </c>
       <c r="T418" s="20" t="n">
-        <v>46978</v>
+        <v>46967</v>
       </c>
       <c r="U418" s="20" t="n">
-        <v>47042</v>
+        <v>47031</v>
       </c>
       <c r="V418" s="8" t="n">
         <v>47</v>
@@ -68667,10 +68667,10 @@
         <v/>
       </c>
       <c r="T419" s="20" t="n">
-        <v>46978</v>
+        <v>46967</v>
       </c>
       <c r="U419" s="20" t="n">
-        <v>47042</v>
+        <v>47031</v>
       </c>
       <c r="V419" s="8" t="n">
         <v>47</v>
@@ -68760,10 +68760,10 @@
         <v/>
       </c>
       <c r="T420" s="20" t="n">
-        <v>47043</v>
+        <v>47034</v>
       </c>
       <c r="U420" s="20" t="n">
-        <v>47056</v>
+        <v>47045</v>
       </c>
       <c r="V420" s="8" t="n">
         <v>10</v>
@@ -68853,10 +68853,10 @@
         <v/>
       </c>
       <c r="T421" s="20" t="n">
-        <v>47057</v>
+        <v>47048</v>
       </c>
       <c r="U421" s="20" t="n">
-        <v>47086</v>
+        <v>47077</v>
       </c>
       <c r="V421" s="8" t="n">
         <v>22</v>
@@ -68946,10 +68946,10 @@
         <v/>
       </c>
       <c r="T422" s="20" t="n">
-        <v>47087</v>
+        <v>47078</v>
       </c>
       <c r="U422" s="20" t="n">
-        <v>47093</v>
+        <v>47084</v>
       </c>
       <c r="V422" s="8" t="n">
         <v>5</v>
@@ -69039,10 +69039,10 @@
         <v/>
       </c>
       <c r="T423" s="20" t="n">
-        <v>46999</v>
+        <v>46988</v>
       </c>
       <c r="U423" s="20" t="n">
-        <v>47077</v>
+        <v>47066</v>
       </c>
       <c r="V423" s="8" t="n">
         <v>57</v>
@@ -69132,10 +69132,10 @@
         <v/>
       </c>
       <c r="T424" s="20" t="n">
-        <v>47050</v>
+        <v>47041</v>
       </c>
       <c r="U424" s="20" t="n">
-        <v>47112</v>
+        <v>47101</v>
       </c>
       <c r="V424" s="8" t="n">
         <v>45</v>
@@ -69225,10 +69225,10 @@
         <v/>
       </c>
       <c r="T425" s="20" t="n">
-        <v>47094</v>
+        <v>47085</v>
       </c>
       <c r="U425" s="20" t="n">
-        <v>47112</v>
+        <v>47101</v>
       </c>
       <c r="V425" s="8" t="n">
         <v>13</v>
@@ -69318,10 +69318,10 @@
         <v/>
       </c>
       <c r="T426" s="20" t="n">
-        <v>47100</v>
+        <v>47091</v>
       </c>
       <c r="U426" s="20" t="n">
-        <v>47129</v>
+        <v>47120</v>
       </c>
       <c r="V426" s="8" t="n">
         <v>22</v>
@@ -69411,10 +69411,10 @@
         <v/>
       </c>
       <c r="T427" s="20" t="n">
-        <v>47132</v>
+        <v>47121</v>
       </c>
       <c r="U427" s="20" t="n">
-        <v>47155</v>
+        <v>47146</v>
       </c>
       <c r="V427" s="8" t="n">
         <v>18</v>
@@ -69504,10 +69504,10 @@
         <v/>
       </c>
       <c r="T428" s="20" t="n">
-        <v>47113</v>
+        <v>47104</v>
       </c>
       <c r="U428" s="20" t="n">
-        <v>47133</v>
+        <v>47122</v>
       </c>
       <c r="V428" s="8" t="n">
         <v>15</v>
@@ -69597,10 +69597,10 @@
         <v/>
       </c>
       <c r="T429" s="20" t="n">
-        <v>47119</v>
+        <v>47108</v>
       </c>
       <c r="U429" s="20" t="n">
-        <v>47135</v>
+        <v>47126</v>
       </c>
       <c r="V429" s="8" t="n">
         <v>13</v>
@@ -69690,10 +69690,10 @@
         <v/>
       </c>
       <c r="T430" s="20" t="n">
-        <v>47156</v>
+        <v>47147</v>
       </c>
       <c r="U430" s="20" t="n">
-        <v>47169</v>
+        <v>47153</v>
       </c>
       <c r="V430" s="8" t="n">
         <v>5</v>
@@ -69783,10 +69783,10 @@
         <v/>
       </c>
       <c r="T431" s="20" t="n">
+        <v>47154</v>
+      </c>
+      <c r="U431" s="20" t="n">
         <v>47170</v>
-      </c>
-      <c r="U431" s="20" t="n">
-        <v>47182</v>
       </c>
       <c r="V431" s="8" t="n">
         <v>8</v>
@@ -69876,10 +69876,10 @@
         <v/>
       </c>
       <c r="T432" s="20" t="n">
-        <v>47183</v>
+        <v>47174</v>
       </c>
       <c r="U432" s="20" t="n">
-        <v>47196</v>
+        <v>47185</v>
       </c>
       <c r="V432" s="8" t="n">
         <v>10</v>
@@ -69969,10 +69969,10 @@
         <v/>
       </c>
       <c r="T433" s="20" t="n">
-        <v>47183</v>
+        <v>47174</v>
       </c>
       <c r="U433" s="20" t="n">
-        <v>47224</v>
+        <v>47213</v>
       </c>
       <c r="V433" s="8" t="n">
         <v>30</v>
@@ -70062,13 +70062,13 @@
         <v/>
       </c>
       <c r="T434" s="20" t="n">
-        <v>47225</v>
+        <v>47216</v>
       </c>
       <c r="U434" s="20" t="n">
         <v>47252</v>
       </c>
       <c r="V434" s="8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="435">
@@ -70155,10 +70155,10 @@
         <v/>
       </c>
       <c r="T435" s="20" t="n">
-        <v>46933</v>
+        <v>46922</v>
       </c>
       <c r="U435" s="20" t="n">
-        <v>46944</v>
+        <v>46931</v>
       </c>
       <c r="V435" s="8" t="n">
         <v>8</v>
@@ -70248,10 +70248,10 @@
         <v/>
       </c>
       <c r="T436" s="20" t="n">
-        <v>46945</v>
+        <v>46932</v>
       </c>
       <c r="U436" s="20" t="n">
-        <v>46965</v>
+        <v>46952</v>
       </c>
       <c r="V436" s="8" t="n">
         <v>15</v>
@@ -70334,20 +70334,20 @@
         </is>
       </c>
       <c r="R437" s="9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S437" s="19">
         <f>R437/1000</f>
         <v/>
       </c>
       <c r="T437" s="20" t="n">
+        <v>46932</v>
+      </c>
+      <c r="U437" s="20" t="n">
         <v>46945</v>
       </c>
-      <c r="U437" s="20" t="n">
-        <v>46957</v>
-      </c>
       <c r="V437" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="438">
@@ -70427,17 +70427,17 @@
         </is>
       </c>
       <c r="R438" s="9" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="S438" s="19">
         <f>R438/1000</f>
         <v/>
       </c>
       <c r="T438" s="20" t="n">
-        <v>46958</v>
+        <v>46946</v>
       </c>
       <c r="U438" s="20" t="n">
-        <v>46978</v>
+        <v>46966</v>
       </c>
       <c r="V438" s="8" t="n">
         <v>15</v>
@@ -70527,10 +70527,10 @@
         <v/>
       </c>
       <c r="T439" s="20" t="n">
-        <v>46958</v>
+        <v>46946</v>
       </c>
       <c r="U439" s="20" t="n">
-        <v>46979</v>
+        <v>46967</v>
       </c>
       <c r="V439" s="8" t="n">
         <v>16</v>
@@ -70620,10 +70620,10 @@
         <v/>
       </c>
       <c r="T440" s="20" t="n">
-        <v>46980</v>
+        <v>46968</v>
       </c>
       <c r="U440" s="20" t="n">
-        <v>47000</v>
+        <v>46988</v>
       </c>
       <c r="V440" s="8" t="n">
         <v>15</v>
@@ -70706,20 +70706,20 @@
         </is>
       </c>
       <c r="R441" s="9" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="S441" s="19">
         <f>R441/1000</f>
         <v/>
       </c>
       <c r="T441" s="20" t="n">
-        <v>46980</v>
+        <v>46968</v>
       </c>
       <c r="U441" s="20" t="n">
-        <v>47014</v>
+        <v>47003</v>
       </c>
       <c r="V441" s="8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="442">
@@ -70799,17 +70799,17 @@
         </is>
       </c>
       <c r="R442" s="9" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="S442" s="19">
         <f>R442/1000</f>
         <v/>
       </c>
       <c r="T442" s="20" t="n">
-        <v>47015</v>
+        <v>47006</v>
       </c>
       <c r="U442" s="20" t="n">
-        <v>47035</v>
+        <v>47024</v>
       </c>
       <c r="V442" s="8" t="n">
         <v>15</v>
@@ -70899,10 +70899,10 @@
         <v/>
       </c>
       <c r="T443" s="20" t="n">
-        <v>47015</v>
+        <v>47006</v>
       </c>
       <c r="U443" s="20" t="n">
-        <v>47031</v>
+        <v>47022</v>
       </c>
       <c r="V443" s="8" t="n">
         <v>13</v>
@@ -70992,10 +70992,10 @@
         <v/>
       </c>
       <c r="T444" s="20" t="n">
-        <v>47034</v>
+        <v>47023</v>
       </c>
       <c r="U444" s="20" t="n">
-        <v>47052</v>
+        <v>47043</v>
       </c>
       <c r="V444" s="8" t="n">
         <v>15</v>
@@ -71085,10 +71085,10 @@
         <v/>
       </c>
       <c r="T445" s="20" t="n">
-        <v>46993</v>
+        <v>46982</v>
       </c>
       <c r="U445" s="20" t="n">
-        <v>47031</v>
+        <v>47022</v>
       </c>
       <c r="V445" s="8" t="n">
         <v>29</v>
@@ -71178,10 +71178,10 @@
         <v/>
       </c>
       <c r="T446" s="20" t="n">
-        <v>47034</v>
+        <v>47023</v>
       </c>
       <c r="U446" s="20" t="n">
-        <v>47052</v>
+        <v>47043</v>
       </c>
       <c r="V446" s="8" t="n">
         <v>15</v>
@@ -71271,10 +71271,10 @@
         <v/>
       </c>
       <c r="T447" s="20" t="n">
-        <v>47248</v>
+        <v>47239</v>
       </c>
       <c r="U447" s="20" t="n">
-        <v>47287</v>
+        <v>47276</v>
       </c>
       <c r="V447" s="8" t="n">
         <v>28</v>
@@ -71364,10 +71364,10 @@
         <v/>
       </c>
       <c r="T448" s="20" t="n">
-        <v>47288</v>
+        <v>47279</v>
       </c>
       <c r="U448" s="20" t="n">
-        <v>47308</v>
+        <v>47297</v>
       </c>
       <c r="V448" s="8" t="n">
         <v>15</v>
@@ -71457,10 +71457,10 @@
         <v/>
       </c>
       <c r="T449" s="20" t="n">
-        <v>47055</v>
+        <v>47044</v>
       </c>
       <c r="U449" s="20" t="n">
-        <v>47059</v>
+        <v>47050</v>
       </c>
       <c r="V449" s="8" t="n">
         <v>5</v>
@@ -71550,10 +71550,10 @@
         <v/>
       </c>
       <c r="T450" s="20" t="n">
-        <v>47062</v>
+        <v>47051</v>
       </c>
       <c r="U450" s="20" t="n">
-        <v>47073</v>
+        <v>47064</v>
       </c>
       <c r="V450" s="8" t="n">
         <v>10</v>
@@ -71643,10 +71643,10 @@
         <v/>
       </c>
       <c r="T451" s="20" t="n">
-        <v>47055</v>
+        <v>47044</v>
       </c>
       <c r="U451" s="20" t="n">
-        <v>47119</v>
+        <v>47108</v>
       </c>
       <c r="V451" s="8" t="n">
         <v>47</v>
@@ -71736,10 +71736,10 @@
         <v/>
       </c>
       <c r="T452" s="20" t="n">
-        <v>47055</v>
+        <v>47044</v>
       </c>
       <c r="U452" s="20" t="n">
-        <v>47119</v>
+        <v>47108</v>
       </c>
       <c r="V452" s="8" t="n">
         <v>47</v>
@@ -71829,10 +71829,10 @@
         <v/>
       </c>
       <c r="T453" s="20" t="n">
-        <v>47055</v>
+        <v>47044</v>
       </c>
       <c r="U453" s="20" t="n">
-        <v>47119</v>
+        <v>47108</v>
       </c>
       <c r="V453" s="8" t="n">
         <v>47</v>
@@ -71922,10 +71922,10 @@
         <v/>
       </c>
       <c r="T454" s="20" t="n">
-        <v>47055</v>
+        <v>47044</v>
       </c>
       <c r="U454" s="20" t="n">
-        <v>47119</v>
+        <v>47108</v>
       </c>
       <c r="V454" s="8" t="n">
         <v>47</v>
@@ -72015,10 +72015,10 @@
         <v/>
       </c>
       <c r="T455" s="20" t="n">
-        <v>47120</v>
+        <v>47111</v>
       </c>
       <c r="U455" s="20" t="n">
-        <v>47133</v>
+        <v>47122</v>
       </c>
       <c r="V455" s="8" t="n">
         <v>10</v>
@@ -72108,10 +72108,10 @@
         <v/>
       </c>
       <c r="T456" s="20" t="n">
-        <v>47134</v>
+        <v>47125</v>
       </c>
       <c r="U456" s="20" t="n">
-        <v>47170</v>
+        <v>47154</v>
       </c>
       <c r="V456" s="8" t="n">
         <v>22</v>
@@ -72201,10 +72201,10 @@
         <v/>
       </c>
       <c r="T457" s="20" t="n">
-        <v>47174</v>
+        <v>47155</v>
       </c>
       <c r="U457" s="20" t="n">
-        <v>47178</v>
+        <v>47168</v>
       </c>
       <c r="V457" s="8" t="n">
         <v>5</v>
@@ -72294,10 +72294,10 @@
         <v/>
       </c>
       <c r="T458" s="20" t="n">
-        <v>47076</v>
+        <v>47065</v>
       </c>
       <c r="U458" s="20" t="n">
-        <v>47154</v>
+        <v>47143</v>
       </c>
       <c r="V458" s="8" t="n">
         <v>57</v>
@@ -72387,10 +72387,10 @@
         <v/>
       </c>
       <c r="T459" s="20" t="n">
-        <v>47127</v>
+        <v>47118</v>
       </c>
       <c r="U459" s="20" t="n">
-        <v>47197</v>
+        <v>47188</v>
       </c>
       <c r="V459" s="8" t="n">
         <v>45</v>
@@ -72480,10 +72480,10 @@
         <v/>
       </c>
       <c r="T460" s="20" t="n">
-        <v>47181</v>
+        <v>47169</v>
       </c>
       <c r="U460" s="20" t="n">
-        <v>47197</v>
+        <v>47188</v>
       </c>
       <c r="V460" s="8" t="n">
         <v>13</v>
@@ -72573,10 +72573,10 @@
         <v/>
       </c>
       <c r="T461" s="20" t="n">
-        <v>47185</v>
+        <v>47176</v>
       </c>
       <c r="U461" s="20" t="n">
-        <v>47216</v>
+        <v>47205</v>
       </c>
       <c r="V461" s="8" t="n">
         <v>22</v>
@@ -72666,10 +72666,10 @@
         <v/>
       </c>
       <c r="T462" s="20" t="n">
-        <v>47217</v>
+        <v>47206</v>
       </c>
       <c r="U462" s="20" t="n">
-        <v>47247</v>
+        <v>47238</v>
       </c>
       <c r="V462" s="8" t="n">
         <v>18</v>
@@ -72759,10 +72759,10 @@
         <v/>
       </c>
       <c r="T463" s="20" t="n">
-        <v>47198</v>
+        <v>47189</v>
       </c>
       <c r="U463" s="20" t="n">
-        <v>47218</v>
+        <v>47209</v>
       </c>
       <c r="V463" s="8" t="n">
         <v>15</v>
@@ -72852,10 +72852,10 @@
         <v/>
       </c>
       <c r="T464" s="20" t="n">
-        <v>47204</v>
+        <v>47195</v>
       </c>
       <c r="U464" s="20" t="n">
-        <v>47220</v>
+        <v>47211</v>
       </c>
       <c r="V464" s="8" t="n">
         <v>13</v>
@@ -72945,10 +72945,10 @@
         <v/>
       </c>
       <c r="T465" s="20" t="n">
-        <v>47248</v>
+        <v>47239</v>
       </c>
       <c r="U465" s="20" t="n">
-        <v>47254</v>
+        <v>47245</v>
       </c>
       <c r="V465" s="8" t="n">
         <v>5</v>
@@ -73038,10 +73038,10 @@
         <v/>
       </c>
       <c r="T466" s="20" t="n">
+        <v>47246</v>
+      </c>
+      <c r="U466" s="20" t="n">
         <v>47255</v>
-      </c>
-      <c r="U466" s="20" t="n">
-        <v>47266</v>
       </c>
       <c r="V466" s="8" t="n">
         <v>8</v>
@@ -73131,10 +73131,10 @@
         <v/>
       </c>
       <c r="T467" s="20" t="n">
-        <v>47267</v>
+        <v>47258</v>
       </c>
       <c r="U467" s="20" t="n">
-        <v>47280</v>
+        <v>47269</v>
       </c>
       <c r="V467" s="8" t="n">
         <v>10</v>
@@ -73224,10 +73224,10 @@
         <v/>
       </c>
       <c r="T468" s="20" t="n">
-        <v>47267</v>
+        <v>47258</v>
       </c>
       <c r="U468" s="20" t="n">
-        <v>47308</v>
+        <v>47297</v>
       </c>
       <c r="V468" s="8" t="n">
         <v>30</v>
@@ -73317,13 +73317,13 @@
         <v/>
       </c>
       <c r="T469" s="20" t="n">
-        <v>47309</v>
+        <v>47300</v>
       </c>
       <c r="U469" s="20" t="n">
         <v>47329</v>
       </c>
       <c r="V469" s="8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="470">
@@ -73410,10 +73410,10 @@
         <v/>
       </c>
       <c r="T470" s="20" t="n">
-        <v>46981</v>
+        <v>46967</v>
       </c>
       <c r="U470" s="20" t="n">
-        <v>46992</v>
+        <v>46978</v>
       </c>
       <c r="V470" s="8" t="n">
         <v>8</v>
@@ -73503,10 +73503,10 @@
         <v/>
       </c>
       <c r="T471" s="20" t="n">
-        <v>46993</v>
+        <v>46979</v>
       </c>
       <c r="U471" s="20" t="n">
-        <v>47013</v>
+        <v>46999</v>
       </c>
       <c r="V471" s="8" t="n">
         <v>15</v>
@@ -73596,10 +73596,10 @@
         <v/>
       </c>
       <c r="T472" s="20" t="n">
-        <v>46993</v>
+        <v>46979</v>
       </c>
       <c r="U472" s="20" t="n">
-        <v>47006</v>
+        <v>46992</v>
       </c>
       <c r="V472" s="8" t="n">
         <v>10</v>
@@ -73689,10 +73689,10 @@
         <v/>
       </c>
       <c r="T473" s="20" t="n">
-        <v>47007</v>
+        <v>46993</v>
       </c>
       <c r="U473" s="20" t="n">
-        <v>47027</v>
+        <v>47013</v>
       </c>
       <c r="V473" s="8" t="n">
         <v>15</v>
@@ -73782,10 +73782,10 @@
         <v/>
       </c>
       <c r="T474" s="20" t="n">
-        <v>47007</v>
+        <v>46993</v>
       </c>
       <c r="U474" s="20" t="n">
-        <v>47028</v>
+        <v>47014</v>
       </c>
       <c r="V474" s="8" t="n">
         <v>16</v>
@@ -73875,10 +73875,10 @@
         <v/>
       </c>
       <c r="T475" s="20" t="n">
-        <v>47029</v>
+        <v>47015</v>
       </c>
       <c r="U475" s="20" t="n">
-        <v>47049</v>
+        <v>47035</v>
       </c>
       <c r="V475" s="8" t="n">
         <v>15</v>
@@ -73968,10 +73968,10 @@
         <v/>
       </c>
       <c r="T476" s="20" t="n">
-        <v>47029</v>
+        <v>47015</v>
       </c>
       <c r="U476" s="20" t="n">
-        <v>47064</v>
+        <v>47050</v>
       </c>
       <c r="V476" s="8" t="n">
         <v>26</v>
@@ -74061,10 +74061,10 @@
         <v/>
       </c>
       <c r="T477" s="20" t="n">
-        <v>47065</v>
+        <v>47051</v>
       </c>
       <c r="U477" s="20" t="n">
-        <v>47085</v>
+        <v>47071</v>
       </c>
       <c r="V477" s="8" t="n">
         <v>15</v>
@@ -74154,10 +74154,10 @@
         <v/>
       </c>
       <c r="T478" s="20" t="n">
-        <v>47065</v>
+        <v>47051</v>
       </c>
       <c r="U478" s="20" t="n">
-        <v>47080</v>
+        <v>47066</v>
       </c>
       <c r="V478" s="8" t="n">
         <v>12</v>
@@ -74247,10 +74247,10 @@
         <v/>
       </c>
       <c r="T479" s="20" t="n">
-        <v>47083</v>
+        <v>47069</v>
       </c>
       <c r="U479" s="20" t="n">
-        <v>47101</v>
+        <v>47087</v>
       </c>
       <c r="V479" s="8" t="n">
         <v>15</v>
@@ -74340,10 +74340,10 @@
         <v/>
       </c>
       <c r="T480" s="20" t="n">
-        <v>47043</v>
+        <v>47029</v>
       </c>
       <c r="U480" s="20" t="n">
-        <v>47080</v>
+        <v>47066</v>
       </c>
       <c r="V480" s="8" t="n">
         <v>28</v>
@@ -74433,10 +74433,10 @@
         <v/>
       </c>
       <c r="T481" s="20" t="n">
-        <v>47083</v>
+        <v>47069</v>
       </c>
       <c r="U481" s="20" t="n">
-        <v>47101</v>
+        <v>47087</v>
       </c>
       <c r="V481" s="8" t="n">
         <v>15</v>
@@ -74526,10 +74526,10 @@
         <v/>
       </c>
       <c r="T482" s="20" t="n">
-        <v>47297</v>
+        <v>47283</v>
       </c>
       <c r="U482" s="20" t="n">
-        <v>47336</v>
+        <v>47322</v>
       </c>
       <c r="V482" s="8" t="n">
         <v>28</v>
@@ -74619,10 +74619,10 @@
         <v/>
       </c>
       <c r="T483" s="20" t="n">
-        <v>47337</v>
+        <v>47323</v>
       </c>
       <c r="U483" s="20" t="n">
-        <v>47357</v>
+        <v>47343</v>
       </c>
       <c r="V483" s="8" t="n">
         <v>15</v>
@@ -74712,10 +74712,10 @@
         <v/>
       </c>
       <c r="T484" s="20" t="n">
-        <v>47104</v>
+        <v>47090</v>
       </c>
       <c r="U484" s="20" t="n">
-        <v>47108</v>
+        <v>47094</v>
       </c>
       <c r="V484" s="8" t="n">
         <v>5</v>
@@ -74805,10 +74805,10 @@
         <v/>
       </c>
       <c r="T485" s="20" t="n">
-        <v>47111</v>
+        <v>47097</v>
       </c>
       <c r="U485" s="20" t="n">
-        <v>47122</v>
+        <v>47108</v>
       </c>
       <c r="V485" s="8" t="n">
         <v>10</v>
@@ -74898,10 +74898,10 @@
         <v/>
       </c>
       <c r="T486" s="20" t="n">
-        <v>47104</v>
+        <v>47090</v>
       </c>
       <c r="U486" s="20" t="n">
-        <v>47176</v>
+        <v>47154</v>
       </c>
       <c r="V486" s="8" t="n">
         <v>47</v>
@@ -74991,10 +74991,10 @@
         <v/>
       </c>
       <c r="T487" s="20" t="n">
-        <v>47104</v>
+        <v>47090</v>
       </c>
       <c r="U487" s="20" t="n">
-        <v>47176</v>
+        <v>47154</v>
       </c>
       <c r="V487" s="8" t="n">
         <v>47</v>
@@ -75084,10 +75084,10 @@
         <v/>
       </c>
       <c r="T488" s="20" t="n">
-        <v>47104</v>
+        <v>47090</v>
       </c>
       <c r="U488" s="20" t="n">
-        <v>47176</v>
+        <v>47154</v>
       </c>
       <c r="V488" s="8" t="n">
         <v>47</v>
@@ -75177,10 +75177,10 @@
         <v/>
       </c>
       <c r="T489" s="20" t="n">
-        <v>47104</v>
+        <v>47090</v>
       </c>
       <c r="U489" s="20" t="n">
-        <v>47176</v>
+        <v>47154</v>
       </c>
       <c r="V489" s="8" t="n">
         <v>47</v>
@@ -75270,10 +75270,10 @@
         <v/>
       </c>
       <c r="T490" s="20" t="n">
-        <v>47177</v>
+        <v>47155</v>
       </c>
       <c r="U490" s="20" t="n">
-        <v>47190</v>
+        <v>47176</v>
       </c>
       <c r="V490" s="8" t="n">
         <v>10</v>
@@ -75363,10 +75363,10 @@
         <v/>
       </c>
       <c r="T491" s="20" t="n">
-        <v>47191</v>
+        <v>47177</v>
       </c>
       <c r="U491" s="20" t="n">
-        <v>47220</v>
+        <v>47206</v>
       </c>
       <c r="V491" s="8" t="n">
         <v>22</v>
@@ -75456,10 +75456,10 @@
         <v/>
       </c>
       <c r="T492" s="20" t="n">
-        <v>47223</v>
+        <v>47209</v>
       </c>
       <c r="U492" s="20" t="n">
-        <v>47227</v>
+        <v>47213</v>
       </c>
       <c r="V492" s="8" t="n">
         <v>5</v>
@@ -75549,10 +75549,10 @@
         <v/>
       </c>
       <c r="T493" s="20" t="n">
-        <v>47125</v>
+        <v>47111</v>
       </c>
       <c r="U493" s="20" t="n">
-        <v>47211</v>
+        <v>47197</v>
       </c>
       <c r="V493" s="8" t="n">
         <v>57</v>
@@ -75642,10 +75642,10 @@
         <v/>
       </c>
       <c r="T494" s="20" t="n">
-        <v>47184</v>
+        <v>47169</v>
       </c>
       <c r="U494" s="20" t="n">
-        <v>47253</v>
+        <v>47239</v>
       </c>
       <c r="V494" s="8" t="n">
         <v>45</v>
@@ -75735,10 +75735,10 @@
         <v/>
       </c>
       <c r="T495" s="20" t="n">
-        <v>47237</v>
+        <v>47216</v>
       </c>
       <c r="U495" s="20" t="n">
-        <v>47253</v>
+        <v>47239</v>
       </c>
       <c r="V495" s="8" t="n">
         <v>13</v>
@@ -75828,10 +75828,10 @@
         <v/>
       </c>
       <c r="T496" s="20" t="n">
-        <v>47241</v>
+        <v>47220</v>
       </c>
       <c r="U496" s="20" t="n">
-        <v>47272</v>
+        <v>47258</v>
       </c>
       <c r="V496" s="8" t="n">
         <v>22</v>
@@ -75921,10 +75921,10 @@
         <v/>
       </c>
       <c r="T497" s="20" t="n">
-        <v>47273</v>
+        <v>47259</v>
       </c>
       <c r="U497" s="20" t="n">
-        <v>47296</v>
+        <v>47282</v>
       </c>
       <c r="V497" s="8" t="n">
         <v>18</v>
@@ -76014,10 +76014,10 @@
         <v/>
       </c>
       <c r="T498" s="20" t="n">
-        <v>47254</v>
+        <v>47240</v>
       </c>
       <c r="U498" s="20" t="n">
-        <v>47274</v>
+        <v>47260</v>
       </c>
       <c r="V498" s="8" t="n">
         <v>15</v>
@@ -76107,10 +76107,10 @@
         <v/>
       </c>
       <c r="T499" s="20" t="n">
-        <v>47260</v>
+        <v>47246</v>
       </c>
       <c r="U499" s="20" t="n">
-        <v>47276</v>
+        <v>47262</v>
       </c>
       <c r="V499" s="8" t="n">
         <v>13</v>
@@ -76200,10 +76200,10 @@
         <v/>
       </c>
       <c r="T500" s="20" t="n">
-        <v>47297</v>
+        <v>47283</v>
       </c>
       <c r="U500" s="20" t="n">
-        <v>47303</v>
+        <v>47289</v>
       </c>
       <c r="V500" s="8" t="n">
         <v>5</v>
@@ -76293,10 +76293,10 @@
         <v/>
       </c>
       <c r="T501" s="20" t="n">
-        <v>47304</v>
+        <v>47290</v>
       </c>
       <c r="U501" s="20" t="n">
-        <v>47315</v>
+        <v>47301</v>
       </c>
       <c r="V501" s="8" t="n">
         <v>8</v>
@@ -76386,10 +76386,10 @@
         <v/>
       </c>
       <c r="T502" s="20" t="n">
-        <v>47316</v>
+        <v>47302</v>
       </c>
       <c r="U502" s="20" t="n">
-        <v>47329</v>
+        <v>47315</v>
       </c>
       <c r="V502" s="8" t="n">
         <v>10</v>
@@ -76479,10 +76479,10 @@
         <v/>
       </c>
       <c r="T503" s="20" t="n">
-        <v>47316</v>
+        <v>47302</v>
       </c>
       <c r="U503" s="20" t="n">
-        <v>47357</v>
+        <v>47343</v>
       </c>
       <c r="V503" s="8" t="n">
         <v>30</v>
@@ -76572,13 +76572,13 @@
         <v/>
       </c>
       <c r="T504" s="20" t="n">
-        <v>47358</v>
+        <v>47344</v>
       </c>
       <c r="U504" s="20" t="n">
-        <v>47378</v>
+        <v>47373</v>
       </c>
       <c r="V504" s="8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="505">
@@ -77022,7 +77022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -77146,7 +77146,7 @@
         <v>46419</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>722198.3775224768</v>
+        <v>728474.6632367625</v>
       </c>
       <c r="C7" s="9">
         <f>SUM(B$4:B7)</f>
@@ -77157,7 +77157,7 @@
         <v/>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.007351435298035299</v>
+        <v>0.007462863869463869</v>
       </c>
       <c r="F7" s="23">
         <f>SUM(E$4:E7)</f>
@@ -77192,7 +77192,7 @@
         <v>46478</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>1628197.492027584</v>
+        <v>1744434.854352513</v>
       </c>
       <c r="C9" s="9">
         <f>SUM(B$4:B9)</f>
@@ -77203,7 +77203,7 @@
         <v/>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.01287862486533075</v>
+        <v>0.01375275511743159</v>
       </c>
       <c r="F9" s="23">
         <f>SUM(E$4:E9)</f>
@@ -77215,7 +77215,7 @@
         <v>46508</v>
       </c>
       <c r="B10" s="9" t="n">
-        <v>1359773.798666298</v>
+        <v>1442176.554135854</v>
       </c>
       <c r="C10" s="9">
         <f>SUM(B$4:B10)</f>
@@ -77226,7 +77226,7 @@
         <v/>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0.02678590646167296</v>
+        <v>0.02705279728076855</v>
       </c>
       <c r="F10" s="23">
         <f>SUM(E$4:E10)</f>
@@ -77238,7 +77238,7 @@
         <v>46539</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>1796308.819662572</v>
+        <v>1684819.121709355</v>
       </c>
       <c r="C11" s="9">
         <f>SUM(B$4:B11)</f>
@@ -77249,7 +77249,7 @@
         <v/>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.03464160657540269</v>
+        <v>0.03651208285870351</v>
       </c>
       <c r="F11" s="23">
         <f>SUM(E$4:E11)</f>
@@ -77261,7 +77261,7 @@
         <v>46569</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>1303669.89269185</v>
+        <v>1309023.699548881</v>
       </c>
       <c r="C12" s="9">
         <f>SUM(B$4:B12)</f>
@@ -77272,7 +77272,7 @@
         <v/>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.0423125577926599</v>
+        <v>0.04200348333008542</v>
       </c>
       <c r="F12" s="23">
         <f>SUM(E$4:E12)</f>
@@ -77284,7 +77284,7 @@
         <v>46600</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>1625994.299509653</v>
+        <v>1682555.487055444</v>
       </c>
       <c r="C13" s="9">
         <f>SUM(B$4:B13)</f>
@@ -77295,7 +77295,7 @@
         <v/>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.05127385094940848</v>
+        <v>0.05261762879841147</v>
       </c>
       <c r="F13" s="23">
         <f>SUM(E$4:E13)</f>
@@ -77307,7 +77307,7 @@
         <v>46631</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>1766294.476016181</v>
+        <v>1807538.688054143</v>
       </c>
       <c r="C14" s="9">
         <f>SUM(B$4:B14)</f>
@@ -77318,7 +77318,7 @@
         <v/>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.04624741568241361</v>
+        <v>0.04574256036273347</v>
       </c>
       <c r="F14" s="23">
         <f>SUM(E$4:E14)</f>
@@ -77330,7 +77330,7 @@
         <v>46661</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>1682512.409514225</v>
+        <v>1709704.999157467</v>
       </c>
       <c r="C15" s="9">
         <f>SUM(B$4:B15)</f>
@@ -77341,7 +77341,7 @@
         <v/>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0.03804258329654849</v>
+        <v>0.03860120845928342</v>
       </c>
       <c r="F15" s="23">
         <f>SUM(E$4:E15)</f>
@@ -77353,7 +77353,7 @@
         <v>46692</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>2266493.398056921</v>
+        <v>2195829.207635707</v>
       </c>
       <c r="C16" s="9">
         <f>SUM(B$4:B16)</f>
@@ -77364,7 +77364,7 @@
         <v/>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.040261234551001</v>
+        <v>0.0389041078859994</v>
       </c>
       <c r="F16" s="23">
         <f>SUM(E$4:E16)</f>
@@ -77376,7 +77376,7 @@
         <v>46722</v>
       </c>
       <c r="B17" s="9" t="n">
-        <v>1919790.529655363</v>
+        <v>2036383.828373213</v>
       </c>
       <c r="C17" s="9">
         <f>SUM(B$4:B17)</f>
@@ -77387,7 +77387,7 @@
         <v/>
       </c>
       <c r="E17" s="10" t="n">
-        <v>0.04396941864266432</v>
+        <v>0.04597599538580423</v>
       </c>
       <c r="F17" s="23">
         <f>SUM(E$4:E17)</f>
@@ -77399,7 +77399,7 @@
         <v>46753</v>
       </c>
       <c r="B18" s="9" t="n">
-        <v>2252018.442109223</v>
+        <v>2321339.034130303</v>
       </c>
       <c r="C18" s="9">
         <f>SUM(B$4:B18)</f>
@@ -77410,7 +77410,7 @@
         <v/>
       </c>
       <c r="E18" s="10" t="n">
-        <v>0.04414193284532374</v>
+        <v>0.0473868773634063</v>
       </c>
       <c r="F18" s="23">
         <f>SUM(E$4:E18)</f>
@@ -77422,7 +77422,7 @@
         <v>46784</v>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1577811.5641617</v>
+        <v>1753077.853186866</v>
       </c>
       <c r="C19" s="9">
         <f>SUM(B$4:B19)</f>
@@ -77433,7 +77433,7 @@
         <v/>
       </c>
       <c r="E19" s="10" t="n">
-        <v>0.03387268475375258</v>
+        <v>0.0356343565895648</v>
       </c>
       <c r="F19" s="23">
         <f>SUM(E$4:E19)</f>
@@ -77445,7 +77445,7 @@
         <v>46813</v>
       </c>
       <c r="B20" s="9" t="n">
-        <v>2762045.924319129</v>
+        <v>2801838.178148763</v>
       </c>
       <c r="C20" s="9">
         <f>SUM(B$4:B20)</f>
@@ -77456,7 +77456,7 @@
         <v/>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.04891604069128763</v>
+        <v>0.04776536341214186</v>
       </c>
       <c r="F20" s="23">
         <f>SUM(E$4:E20)</f>
@@ -77468,7 +77468,7 @@
         <v>46844</v>
       </c>
       <c r="B21" s="9" t="n">
-        <v>3379027.264459413</v>
+        <v>3549570.864585011</v>
       </c>
       <c r="C21" s="9">
         <f>SUM(B$4:B21)</f>
@@ -77479,7 +77479,7 @@
         <v/>
       </c>
       <c r="E21" s="10" t="n">
-        <v>0.04714948391141734</v>
+        <v>0.04825021981851738</v>
       </c>
       <c r="F21" s="23">
         <f>SUM(E$4:E21)</f>
@@ -77491,7 +77491,7 @@
         <v>46874</v>
       </c>
       <c r="B22" s="9" t="n">
-        <v>2513138.951734432</v>
+        <v>2433062.051112088</v>
       </c>
       <c r="C22" s="9">
         <f>SUM(B$4:B22)</f>
@@ -77502,7 +77502,7 @@
         <v/>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.04005261921522792</v>
+        <v>0.04450836194221248</v>
       </c>
       <c r="F22" s="23">
         <f>SUM(E$4:E22)</f>
@@ -77514,7 +77514,7 @@
         <v>46905</v>
       </c>
       <c r="B23" s="9" t="n">
-        <v>2704699.365968495</v>
+        <v>2658079.104260592</v>
       </c>
       <c r="C23" s="9">
         <f>SUM(B$4:B23)</f>
@@ -77525,7 +77525,7 @@
         <v/>
       </c>
       <c r="E23" s="10" t="n">
-        <v>0.05173817961155595</v>
+        <v>0.04993787928039982</v>
       </c>
       <c r="F23" s="23">
         <f>SUM(E$4:E23)</f>
@@ -77537,7 +77537,7 @@
         <v>46935</v>
       </c>
       <c r="B24" s="9" t="n">
-        <v>2217277.2476068</v>
+        <v>2078816.258658892</v>
       </c>
       <c r="C24" s="9">
         <f>SUM(B$4:B24)</f>
@@ -77548,7 +77548,7 @@
         <v/>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.04932846789795158</v>
+        <v>0.04807558768855531</v>
       </c>
       <c r="F24" s="23">
         <f>SUM(E$4:E24)</f>
@@ -77560,7 +77560,7 @@
         <v>46966</v>
       </c>
       <c r="B25" s="9" t="n">
-        <v>1794009.798878804</v>
+        <v>1769603.581993361</v>
       </c>
       <c r="C25" s="9">
         <f>SUM(B$4:B25)</f>
@@ -77571,7 +77571,7 @@
         <v/>
       </c>
       <c r="E25" s="10" t="n">
-        <v>0.04022412844901042</v>
+        <v>0.03932438538839055</v>
       </c>
       <c r="F25" s="23">
         <f>SUM(E$4:E25)</f>
@@ -77583,7 +77583,7 @@
         <v>46997</v>
       </c>
       <c r="B26" s="9" t="n">
-        <v>1146711.540434802</v>
+        <v>1167986.950932274</v>
       </c>
       <c r="C26" s="9">
         <f>SUM(B$4:B26)</f>
@@ -77594,7 +77594,7 @@
         <v/>
       </c>
       <c r="E26" s="10" t="n">
-        <v>0.02698557164857578</v>
+        <v>0.02733037734003094</v>
       </c>
       <c r="F26" s="23">
         <f>SUM(E$4:E26)</f>
@@ -77606,7 +77606,7 @@
         <v>47027</v>
       </c>
       <c r="B27" s="9" t="n">
-        <v>1391672.180772132</v>
+        <v>1551041.255409049</v>
       </c>
       <c r="C27" s="9">
         <f>SUM(B$4:B27)</f>
@@ -77617,7 +77617,7 @@
         <v/>
       </c>
       <c r="E27" s="10" t="n">
-        <v>0.03215077325385727</v>
+        <v>0.03271893999619224</v>
       </c>
       <c r="F27" s="23">
         <f>SUM(E$4:E27)</f>
@@ -77629,7 +77629,7 @@
         <v>47058</v>
       </c>
       <c r="B28" s="9" t="n">
-        <v>1762471.077165564</v>
+        <v>1780674.564930941</v>
       </c>
       <c r="C28" s="9">
         <f>SUM(B$4:B28)</f>
@@ -77640,7 +77640,7 @@
         <v/>
       </c>
       <c r="E28" s="10" t="n">
-        <v>0.03381267162841844</v>
+        <v>0.03438694887302739</v>
       </c>
       <c r="F28" s="23">
         <f>SUM(E$4:E28)</f>
@@ -77652,7 +77652,7 @@
         <v>47088</v>
       </c>
       <c r="B29" s="9" t="n">
-        <v>1652866.22105302</v>
+        <v>1461766.122250995</v>
       </c>
       <c r="C29" s="9">
         <f>SUM(B$4:B29)</f>
@@ -77663,7 +77663,7 @@
         <v/>
       </c>
       <c r="E29" s="10" t="n">
-        <v>0.03240318125079989</v>
+        <v>0.03099316622745991</v>
       </c>
       <c r="F29" s="23">
         <f>SUM(E$4:E29)</f>
@@ -77675,7 +77675,7 @@
         <v>47119</v>
       </c>
       <c r="B30" s="9" t="n">
-        <v>1573399.130516641</v>
+        <v>1856103.654370385</v>
       </c>
       <c r="C30" s="9">
         <f>SUM(B$4:B30)</f>
@@ -77686,7 +77686,7 @@
         <v/>
       </c>
       <c r="E30" s="10" t="n">
-        <v>0.03158243279882086</v>
+        <v>0.03257295860400283</v>
       </c>
       <c r="F30" s="23">
         <f>SUM(E$4:E30)</f>
@@ -77698,7 +77698,7 @@
         <v>47150</v>
       </c>
       <c r="B31" s="9" t="n">
-        <v>1404924.737162054</v>
+        <v>1182733.661194291</v>
       </c>
       <c r="C31" s="9">
         <f>SUM(B$4:B31)</f>
@@ -77709,7 +77709,7 @@
         <v/>
       </c>
       <c r="E31" s="10" t="n">
-        <v>0.02189683675702795</v>
+        <v>0.02071289476599052</v>
       </c>
       <c r="F31" s="23">
         <f>SUM(E$4:E31)</f>
@@ -77721,7 +77721,7 @@
         <v>47178</v>
       </c>
       <c r="B32" s="9" t="n">
-        <v>1167993.26587433</v>
+        <v>990317.0318856585</v>
       </c>
       <c r="C32" s="9">
         <f>SUM(B$4:B32)</f>
@@ -77732,7 +77732,7 @@
         <v/>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.02294207534132536</v>
+        <v>0.01972113730713734</v>
       </c>
       <c r="F32" s="23">
         <f>SUM(E$4:E32)</f>
@@ -77744,7 +77744,7 @@
         <v>47209</v>
       </c>
       <c r="B33" s="9" t="n">
-        <v>752189.6030752873</v>
+        <v>671679.4717171721</v>
       </c>
       <c r="C33" s="9">
         <f>SUM(B$4:B33)</f>
@@ -77755,7 +77755,7 @@
         <v/>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0.01584903729603731</v>
+        <v>0.01372771328671328</v>
       </c>
       <c r="F33" s="23">
         <f>SUM(E$4:E33)</f>
@@ -77767,7 +77767,7 @@
         <v>47239</v>
       </c>
       <c r="B34" s="9" t="n">
-        <v>943718.3298701313</v>
+        <v>872432.099372851</v>
       </c>
       <c r="C34" s="9">
         <f>SUM(B$4:B34)</f>
@@ -77778,7 +77778,7 @@
         <v/>
       </c>
       <c r="E34" s="10" t="n">
-        <v>0.01513150405150403</v>
+        <v>0.0136635868020868</v>
       </c>
       <c r="F34" s="23">
         <f>SUM(E$4:E34)</f>
@@ -77790,7 +77790,7 @@
         <v>47270</v>
       </c>
       <c r="B35" s="9" t="n">
-        <v>331699.1529137526</v>
+        <v>473709.738095238</v>
       </c>
       <c r="C35" s="9">
         <f>SUM(B$4:B35)</f>
@@ -77801,7 +77801,7 @@
         <v/>
       </c>
       <c r="E35" s="10" t="n">
-        <v>0.005918815850815849</v>
+        <v>0.005987857142857143</v>
       </c>
       <c r="F35" s="23">
         <f>SUM(E$4:E35)</f>
@@ -77813,7 +77813,7 @@
         <v>47300</v>
       </c>
       <c r="B36" s="9" t="n">
-        <v>587808.5809523811</v>
+        <v>325678.7214285717</v>
       </c>
       <c r="C36" s="9">
         <f>SUM(B$4:B36)</f>
@@ -77824,7 +77824,7 @@
         <v/>
       </c>
       <c r="E36" s="10" t="n">
-        <v>0.007395571428571425</v>
+        <v>0.004604357142857137</v>
       </c>
       <c r="F36" s="23">
         <f>SUM(E$4:E36)</f>
@@ -77836,7 +77836,7 @@
         <v>47331</v>
       </c>
       <c r="B37" s="9" t="n">
-        <v>120014.4285714286</v>
+        <v>106138.8272727272</v>
       </c>
       <c r="C37" s="9">
         <f>SUM(B$4:B37)</f>
@@ -77847,7 +77847,7 @@
         <v/>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0.001593809523809523</v>
+        <v>0.001539636363636364</v>
       </c>
       <c r="F37" s="23">
         <f>SUM(E$4:E37)</f>
@@ -77859,7 +77859,7 @@
         <v>47362</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>81573.60000000002</v>
+        <v>41713.77272727272</v>
       </c>
       <c r="C38" s="9">
         <f>SUM(B$4:B38)</f>
@@ -77870,33 +77870,10 @@
         <v/>
       </c>
       <c r="E38" s="10" t="n">
-        <v>0.01167199999999999</v>
+        <v>0.01365636363636364</v>
       </c>
       <c r="F38" s="23">
         <f>SUM(E$4:E38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="22" t="n">
-        <v>47392</v>
-      </c>
-      <c r="B39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="9">
-        <f>SUM(B$4:B39)</f>
-        <v/>
-      </c>
-      <c r="D39" s="23">
-        <f>C39/62000000</f>
-        <v/>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0.002602</v>
-      </c>
-      <c r="F39" s="23">
-        <f>SUM(E$4:E39)</f>
         <v/>
       </c>
     </row>
